--- a/evaluaciones-frontend/src/assets/formato_banco_preguntas_asig_EF_1P.xlsx
+++ b/evaluaciones-frontend/src/assets/formato_banco_preguntas_asig_EF_1P.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACIONES" sheetId="1" r:id="R4ccd1658397c47f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R2f0378918c9b400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banco" sheetId="3" r:id="Rbbe8df63bda14fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplo" sheetId="4" r:id="R82ed93b90a7d4b55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACIONES" sheetId="1" r:id="R721bf4c968bd488d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R2e747ac7fb7f4cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banco" sheetId="3" r:id="R789fa267d11d4b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplo" sheetId="4" r:id="R200a87eec9204f6e"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="LISTA_TIPOS_2P">VALIDACIONES!$A$1:$A$8</x:definedName>
@@ -41,9 +41,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EF</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">A: 1, 2 y 3 son verdaderas</x:t>
@@ -121,9 +118,6 @@
     <x:t xml:space="preserve">opcion_a, opcion_b y respuesta_correcta se preparan automaticamente. Cambie la respuesta si el enunciado es falso.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Use opcion_a a opcion_d para los incisos 1-4; opcion_e queda deshabilitada. La respuesta usa la lista A-E.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Pregunta objetiva con 5 opciones donde se selecciona la mejor respuesta.</x:t>
   </x:si>
   <x:si>
@@ -184,19 +178,10 @@
     <x:t xml:space="preserve">Parcial activo</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">EF (Examen Final)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Registro por grupo</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">En Examen Final el banco se organiza y se valida individualmente por grupo teorico.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Columna observaciones</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">La columna L se completa automaticamente y te dira si la fila esta OK o que campos faltan/revisar.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">NOTAS IMPORTANTES</x:t>
@@ -206,9 +191,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">- IMPORTANTE: Respuesta A/B/Ambas/Ninguna usa solo las premisas I. y II. en enunciado; opcion_a a opcion_d lleva las respuestas fijas y opcion_e no se usa.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">- IMPORTANTE: Verdadero o Falso Complejas usa solo los incisos 1, 2, 3 y 4 en opcion_a a opcion_d. No llene opcion_e.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">- IMPORTANTE: Casos/problemas y Emparejamiento Ampliado son encabezados y no deben tener dificultad.</x:t>
@@ -438,9 +420,6 @@
     <x:t xml:space="preserve">Precipitacion</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Infiltracion</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Proceso por el cual el vapor de agua se transforma en gotas.</x:t>
   </x:si>
   <x:si>
@@ -451,7 +430,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -487,8 +466,19 @@
       <x:color rgb="FF3B1A75"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF92400E"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -538,6 +528,56 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF3EEFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7D6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -595,7 +635,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -719,6 +759,29 @@
     <x:xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1021,26 +1084,26 @@
       <x:c r="F1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G1" t="s">
+      <x:c r="G1" t="str">
+        <x:v>1P</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H1" t="s">
+      <x:c r="I1" t="s">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>6</x:v>
       </x:c>
       <x:c r="J1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L1" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="M1" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N1" t="s">
         <x:v>0</x:v>
@@ -1049,192 +1112,192 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R1" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="Q1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="R1" t="s">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K2" t="s">
+      <x:c r="L2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L2" t="s">
+      <x:c r="M2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="M2" t="s">
+      <x:c r="N2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="N2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="O2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="P2" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="Q2" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="R2" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C3" t="s">
+      <x:c r="D3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" t="s">
+      <x:c r="H3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H3" t="s">
+      <x:c r="J3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="J3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K3" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="L3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="N3" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="O3" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="P3" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="Q3" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="R3" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H4" t="s">
+      <x:c r="J4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K4" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K4" t="s">
+      <x:c r="L4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L4" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="N4" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O4" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="P4" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="Q4" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H5" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H5" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="J5" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="N5" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O5" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P5" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N5" t="s">
+      <x:c r="Q5" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="O5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="Q5" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J6" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K6" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N6" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="O6" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1252,12 +1315,12 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="2" customFormat="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1265,100 +1328,100 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Use opcion_a a opcion_d para las proposiciones 1-4; opcion_e debe quedar vacia. respuesta_correcta acepta A-E: la letra E es valida como combinacion de proposiciones, no como texto de opcion_e.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="2" customFormat="1">
       <x:c r="A13" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1366,60 +1429,60 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="2" customFormat="1">
       <x:c r="A22" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B24" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>1P (1er Parcial)</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B25" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>En el 1er Parcial el banco se organiza y se valida individualmente por grupo teorico.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B26" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>La columna L se completa automaticamente y te dira si la fila esta OK o que campos faltan/revisar.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1432,37 +1495,37 @@
     </x:row>
     <x:row r="28" s="2" customFormat="1">
       <x:c r="A28" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="5" customFormat="1">
       <x:c r="A29" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="4" customFormat="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="4" customFormat="1">
-      <x:c r="A31" s="4" t="s">
-        <x:v>59</x:v>
+      <x:c r="A31" s="4" t="str">
+        <x:v>- IMPORTANTE: Verdadero o Falso Complejas usa los incisos 1, 2, 3 y 4 en opcion_a a opcion_d. opcion_e debe quedar vacia; respuesta_correcta puede ser A, B, C, D o E, porque E representa una combinacion.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="4" customFormat="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="33" s="4" customFormat="1">
       <x:c r="A33" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1474,167 +1537,128 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" customWidth="1"/>
-    <x:col min="2" max="2" width="18" customWidth="1"/>
-    <x:col min="3" max="3" width="60" style="6" customWidth="1"/>
-    <x:col min="4" max="8" width="25" style="6" customWidth="1"/>
-    <x:col min="9" max="9" width="20" customWidth="1"/>
-    <x:col min="10" max="11" width="12" customWidth="1"/>
-    <x:col min="12" max="12" width="28" style="6" hidden="0" customWidth="1"/>
-    <x:col min="13" max="36" width="3" hidden="1" customWidth="1"/>
-    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="3" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="11" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="30" max="30" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="31" max="31" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="32" max="32" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="33" max="33" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="34" max="34" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="35" max="35" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="36" max="36" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="37" max="37" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="38" max="38" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="39" max="39" width="0.10000000149011612" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="0.10000000149011612" hidden="0" customWidth="1"/>
+    <x:col min="14" max="40" width="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D1" s="7" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E1" s="7" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G1" s="7" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="s">
+      <x:c r="H1" s="7" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="s">
+      <x:c r="I1" s="7" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="s">
+      <x:c r="J1" s="7" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E1" s="7" t="s">
+      <x:c r="K1" s="7" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="F1" s="7" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G1" s="7" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H1" s="7" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I1" s="7" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J1" s="7" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K1" s="7" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="L1" s="7" t="str">
         <x:v>observaciones</x:v>
       </x:c>
-      <x:c r="M1" t="str">
+      <x:c r="M1" s="66" t="str">
         <x:v>imagen_base64</x:v>
       </x:c>
       <x:c r="N1"/>
       <x:c r="O1"/>
       <x:c r="P1"/>
       <x:c r="Q1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="R1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="T1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="U1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="V1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="W1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="X1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Y1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Z1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AA1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AB1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AC1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AD1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AE1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AF1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AG1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AI1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AJ1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AK1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AL1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AM1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AN1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A2" s="8"/>
+      <x:c r="B2" s="8"/>
       <x:c r="C2" s="9" t="str">
         <x:f>IF($A2="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A2="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -1650,9 +1674,7 @@
       <x:c r="G2" s="8" t="str">
         <x:f>IF($A2="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H2" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H2" s="8"/>
       <x:c r="I2" s="8" t="str">
         <x:f>IF($A2="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -1664,9 +1686,8 @@
       </x:c>
       <x:c r="L2" s="10" t="str">
         <x:f>IF(TRIM($A2)="","",IF(COUNTIF($Q2:$AK2,"?*")=0,"OK","Falta revisar: "&amp;$Q2&amp;$R2&amp;$S2&amp;$T2&amp;$U2&amp;$V2&amp;$W2&amp;$X2&amp;$Y2&amp;$Z2&amp;$AA2&amp;$AB2&amp;$AC2&amp;$AD2&amp;$AE2&amp;$AF2&amp;$AG2&amp;$AH2&amp;$AI2&amp;$AJ2&amp;$AK2))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M2"/>
+      </x:c>
+      <x:c r="M2" s="67"/>
       <x:c r="N2"/>
       <x:c r="O2"/>
       <x:c r="P2"/>
@@ -1747,12 +1768,8 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A3" s="8"/>
+      <x:c r="B3" s="8"/>
       <x:c r="C3" s="9" t="str">
         <x:f>IF($A3="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A3="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -1768,9 +1785,7 @@
       <x:c r="G3" s="8" t="str">
         <x:f>IF($A3="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H3" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H3" s="8"/>
       <x:c r="I3" s="8" t="str">
         <x:f>IF($A3="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -1782,9 +1797,8 @@
       </x:c>
       <x:c r="L3" s="10" t="str">
         <x:f>IF(TRIM($A3)="","",IF(COUNTIF($Q3:$AK3,"?*")=0,"OK","Falta revisar: "&amp;$Q3&amp;$R3&amp;$S3&amp;$T3&amp;$U3&amp;$V3&amp;$W3&amp;$X3&amp;$Y3&amp;$Z3&amp;$AA3&amp;$AB3&amp;$AC3&amp;$AD3&amp;$AE3&amp;$AF3&amp;$AG3&amp;$AH3&amp;$AI3&amp;$AJ3&amp;$AK3))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M3"/>
+      </x:c>
+      <x:c r="M3" s="67"/>
       <x:c r="N3"/>
       <x:c r="O3"/>
       <x:c r="P3"/>
@@ -1865,12 +1879,8 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A4" s="8"/>
+      <x:c r="B4" s="8"/>
       <x:c r="C4" s="9" t="str">
         <x:f>IF($A4="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A4="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -1886,9 +1896,7 @@
       <x:c r="G4" s="8" t="str">
         <x:f>IF($A4="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H4" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H4" s="8"/>
       <x:c r="I4" s="8" t="str">
         <x:f>IF($A4="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -1900,9 +1908,8 @@
       </x:c>
       <x:c r="L4" s="10" t="str">
         <x:f>IF(TRIM($A4)="","",IF(COUNTIF($Q4:$AK4,"?*")=0,"OK","Falta revisar: "&amp;$Q4&amp;$R4&amp;$S4&amp;$T4&amp;$U4&amp;$V4&amp;$W4&amp;$X4&amp;$Y4&amp;$Z4&amp;$AA4&amp;$AB4&amp;$AC4&amp;$AD4&amp;$AE4&amp;$AF4&amp;$AG4&amp;$AH4&amp;$AI4&amp;$AJ4&amp;$AK4))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M4"/>
+      </x:c>
+      <x:c r="M4" s="67"/>
       <x:c r="N4"/>
       <x:c r="O4"/>
       <x:c r="P4"/>
@@ -1983,12 +1990,8 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A5" s="8"/>
+      <x:c r="B5" s="8"/>
       <x:c r="C5" s="9" t="str">
         <x:f>IF($A5="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A5="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2004,9 +2007,7 @@
       <x:c r="G5" s="8" t="str">
         <x:f>IF($A5="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H5" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H5" s="8"/>
       <x:c r="I5" s="8" t="str">
         <x:f>IF($A5="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2018,9 +2019,8 @@
       </x:c>
       <x:c r="L5" s="10" t="str">
         <x:f>IF(TRIM($A5)="","",IF(COUNTIF($Q5:$AK5,"?*")=0,"OK","Falta revisar: "&amp;$Q5&amp;$R5&amp;$S5&amp;$T5&amp;$U5&amp;$V5&amp;$W5&amp;$X5&amp;$Y5&amp;$Z5&amp;$AA5&amp;$AB5&amp;$AC5&amp;$AD5&amp;$AE5&amp;$AF5&amp;$AG5&amp;$AH5&amp;$AI5&amp;$AJ5&amp;$AK5))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M5"/>
+      </x:c>
+      <x:c r="M5" s="67"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
       <x:c r="P5"/>
@@ -2101,12 +2101,8 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A6" s="8"/>
+      <x:c r="B6" s="8"/>
       <x:c r="C6" s="9" t="str">
         <x:f>IF($A6="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A6="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2122,9 +2118,7 @@
       <x:c r="G6" s="8" t="str">
         <x:f>IF($A6="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H6" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H6" s="8"/>
       <x:c r="I6" s="8" t="str">
         <x:f>IF($A6="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2136,9 +2130,8 @@
       </x:c>
       <x:c r="L6" s="10" t="str">
         <x:f>IF(TRIM($A6)="","",IF(COUNTIF($Q6:$AK6,"?*")=0,"OK","Falta revisar: "&amp;$Q6&amp;$R6&amp;$S6&amp;$T6&amp;$U6&amp;$V6&amp;$W6&amp;$X6&amp;$Y6&amp;$Z6&amp;$AA6&amp;$AB6&amp;$AC6&amp;$AD6&amp;$AE6&amp;$AF6&amp;$AG6&amp;$AH6&amp;$AI6&amp;$AJ6&amp;$AK6))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M6"/>
+      </x:c>
+      <x:c r="M6" s="67"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
       <x:c r="P6"/>
@@ -2219,12 +2212,8 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="8"/>
       <x:c r="C7" s="9" t="str">
         <x:f>IF($A7="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A7="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2240,9 +2229,7 @@
       <x:c r="G7" s="8" t="str">
         <x:f>IF($A7="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H7" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H7" s="8"/>
       <x:c r="I7" s="8" t="str">
         <x:f>IF($A7="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2254,9 +2241,8 @@
       </x:c>
       <x:c r="L7" s="10" t="str">
         <x:f>IF(TRIM($A7)="","",IF(COUNTIF($Q7:$AK7,"?*")=0,"OK","Falta revisar: "&amp;$Q7&amp;$R7&amp;$S7&amp;$T7&amp;$U7&amp;$V7&amp;$W7&amp;$X7&amp;$Y7&amp;$Z7&amp;$AA7&amp;$AB7&amp;$AC7&amp;$AD7&amp;$AE7&amp;$AF7&amp;$AG7&amp;$AH7&amp;$AI7&amp;$AJ7&amp;$AK7))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M7"/>
+      </x:c>
+      <x:c r="M7" s="67"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
       <x:c r="P7"/>
@@ -2337,12 +2323,8 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="8"/>
       <x:c r="C8" s="9" t="str">
         <x:f>IF($A8="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A8="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2358,9 +2340,7 @@
       <x:c r="G8" s="8" t="str">
         <x:f>IF($A8="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H8" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H8" s="8"/>
       <x:c r="I8" s="8" t="str">
         <x:f>IF($A8="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2372,9 +2352,8 @@
       </x:c>
       <x:c r="L8" s="10" t="str">
         <x:f>IF(TRIM($A8)="","",IF(COUNTIF($Q8:$AK8,"?*")=0,"OK","Falta revisar: "&amp;$Q8&amp;$R8&amp;$S8&amp;$T8&amp;$U8&amp;$V8&amp;$W8&amp;$X8&amp;$Y8&amp;$Z8&amp;$AA8&amp;$AB8&amp;$AC8&amp;$AD8&amp;$AE8&amp;$AF8&amp;$AG8&amp;$AH8&amp;$AI8&amp;$AJ8&amp;$AK8))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M8"/>
+      </x:c>
+      <x:c r="M8" s="67"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
       <x:c r="P8"/>
@@ -2455,12 +2434,8 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="8"/>
       <x:c r="C9" s="9" t="str">
         <x:f>IF($A9="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A9="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2476,9 +2451,7 @@
       <x:c r="G9" s="8" t="str">
         <x:f>IF($A9="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H9" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H9" s="8"/>
       <x:c r="I9" s="8" t="str">
         <x:f>IF($A9="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2490,9 +2463,8 @@
       </x:c>
       <x:c r="L9" s="10" t="str">
         <x:f>IF(TRIM($A9)="","",IF(COUNTIF($Q9:$AK9,"?*")=0,"OK","Falta revisar: "&amp;$Q9&amp;$R9&amp;$S9&amp;$T9&amp;$U9&amp;$V9&amp;$W9&amp;$X9&amp;$Y9&amp;$Z9&amp;$AA9&amp;$AB9&amp;$AC9&amp;$AD9&amp;$AE9&amp;$AF9&amp;$AG9&amp;$AH9&amp;$AI9&amp;$AJ9&amp;$AK9))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M9"/>
+      </x:c>
+      <x:c r="M9" s="67"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
@@ -2573,12 +2545,8 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="8"/>
       <x:c r="C10" s="9" t="str">
         <x:f>IF($A10="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A10="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2594,9 +2562,7 @@
       <x:c r="G10" s="8" t="str">
         <x:f>IF($A10="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H10" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H10" s="8"/>
       <x:c r="I10" s="8" t="str">
         <x:f>IF($A10="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2608,9 +2574,8 @@
       </x:c>
       <x:c r="L10" s="10" t="str">
         <x:f>IF(TRIM($A10)="","",IF(COUNTIF($Q10:$AK10,"?*")=0,"OK","Falta revisar: "&amp;$Q10&amp;$R10&amp;$S10&amp;$T10&amp;$U10&amp;$V10&amp;$W10&amp;$X10&amp;$Y10&amp;$Z10&amp;$AA10&amp;$AB10&amp;$AC10&amp;$AD10&amp;$AE10&amp;$AF10&amp;$AG10&amp;$AH10&amp;$AI10&amp;$AJ10&amp;$AK10))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M10"/>
+      </x:c>
+      <x:c r="M10" s="67"/>
       <x:c r="N10"/>
       <x:c r="O10"/>
       <x:c r="P10"/>
@@ -2691,12 +2656,8 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="8"/>
       <x:c r="C11" s="9" t="str">
         <x:f>IF($A11="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A11="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2712,9 +2673,7 @@
       <x:c r="G11" s="8" t="str">
         <x:f>IF($A11="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H11" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H11" s="8"/>
       <x:c r="I11" s="8" t="str">
         <x:f>IF($A11="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2726,9 +2685,8 @@
       </x:c>
       <x:c r="L11" s="10" t="str">
         <x:f>IF(TRIM($A11)="","",IF(COUNTIF($Q11:$AK11,"?*")=0,"OK","Falta revisar: "&amp;$Q11&amp;$R11&amp;$S11&amp;$T11&amp;$U11&amp;$V11&amp;$W11&amp;$X11&amp;$Y11&amp;$Z11&amp;$AA11&amp;$AB11&amp;$AC11&amp;$AD11&amp;$AE11&amp;$AF11&amp;$AG11&amp;$AH11&amp;$AI11&amp;$AJ11&amp;$AK11))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M11"/>
+      </x:c>
+      <x:c r="M11" s="67"/>
       <x:c r="N11"/>
       <x:c r="O11"/>
       <x:c r="P11"/>
@@ -2809,12 +2767,8 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B12" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="8"/>
       <x:c r="C12" s="9" t="str">
         <x:f>IF($A12="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A12="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2830,9 +2784,7 @@
       <x:c r="G12" s="8" t="str">
         <x:f>IF($A12="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H12" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H12" s="8"/>
       <x:c r="I12" s="8" t="str">
         <x:f>IF($A12="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2844,9 +2796,8 @@
       </x:c>
       <x:c r="L12" s="10" t="str">
         <x:f>IF(TRIM($A12)="","",IF(COUNTIF($Q12:$AK12,"?*")=0,"OK","Falta revisar: "&amp;$Q12&amp;$R12&amp;$S12&amp;$T12&amp;$U12&amp;$V12&amp;$W12&amp;$X12&amp;$Y12&amp;$Z12&amp;$AA12&amp;$AB12&amp;$AC12&amp;$AD12&amp;$AE12&amp;$AF12&amp;$AG12&amp;$AH12&amp;$AI12&amp;$AJ12&amp;$AK12))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M12"/>
+      </x:c>
+      <x:c r="M12" s="67"/>
       <x:c r="N12"/>
       <x:c r="O12"/>
       <x:c r="P12"/>
@@ -2927,12 +2878,8 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B13" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="8"/>
       <x:c r="C13" s="9" t="str">
         <x:f>IF($A13="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A13="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -2948,9 +2895,7 @@
       <x:c r="G13" s="8" t="str">
         <x:f>IF($A13="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H13" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H13" s="8"/>
       <x:c r="I13" s="8" t="str">
         <x:f>IF($A13="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -2962,9 +2907,8 @@
       </x:c>
       <x:c r="L13" s="10" t="str">
         <x:f>IF(TRIM($A13)="","",IF(COUNTIF($Q13:$AK13,"?*")=0,"OK","Falta revisar: "&amp;$Q13&amp;$R13&amp;$S13&amp;$T13&amp;$U13&amp;$V13&amp;$W13&amp;$X13&amp;$Y13&amp;$Z13&amp;$AA13&amp;$AB13&amp;$AC13&amp;$AD13&amp;$AE13&amp;$AF13&amp;$AG13&amp;$AH13&amp;$AI13&amp;$AJ13&amp;$AK13))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M13"/>
+      </x:c>
+      <x:c r="M13" s="67"/>
       <x:c r="N13"/>
       <x:c r="O13"/>
       <x:c r="P13"/>
@@ -3045,12 +2989,8 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A14" s="8"/>
+      <x:c r="B14" s="8"/>
       <x:c r="C14" s="9" t="str">
         <x:f>IF($A14="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A14="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3066,9 +3006,7 @@
       <x:c r="G14" s="8" t="str">
         <x:f>IF($A14="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H14" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H14" s="8"/>
       <x:c r="I14" s="8" t="str">
         <x:f>IF($A14="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3080,9 +3018,8 @@
       </x:c>
       <x:c r="L14" s="10" t="str">
         <x:f>IF(TRIM($A14)="","",IF(COUNTIF($Q14:$AK14,"?*")=0,"OK","Falta revisar: "&amp;$Q14&amp;$R14&amp;$S14&amp;$T14&amp;$U14&amp;$V14&amp;$W14&amp;$X14&amp;$Y14&amp;$Z14&amp;$AA14&amp;$AB14&amp;$AC14&amp;$AD14&amp;$AE14&amp;$AF14&amp;$AG14&amp;$AH14&amp;$AI14&amp;$AJ14&amp;$AK14))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M14"/>
+      </x:c>
+      <x:c r="M14" s="67"/>
       <x:c r="N14"/>
       <x:c r="O14"/>
       <x:c r="P14"/>
@@ -3163,12 +3100,8 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B15" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A15" s="8"/>
+      <x:c r="B15" s="8"/>
       <x:c r="C15" s="9" t="str">
         <x:f>IF($A15="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A15="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3184,9 +3117,7 @@
       <x:c r="G15" s="8" t="str">
         <x:f>IF($A15="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H15" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H15" s="8"/>
       <x:c r="I15" s="8" t="str">
         <x:f>IF($A15="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3198,9 +3129,8 @@
       </x:c>
       <x:c r="L15" s="10" t="str">
         <x:f>IF(TRIM($A15)="","",IF(COUNTIF($Q15:$AK15,"?*")=0,"OK","Falta revisar: "&amp;$Q15&amp;$R15&amp;$S15&amp;$T15&amp;$U15&amp;$V15&amp;$W15&amp;$X15&amp;$Y15&amp;$Z15&amp;$AA15&amp;$AB15&amp;$AC15&amp;$AD15&amp;$AE15&amp;$AF15&amp;$AG15&amp;$AH15&amp;$AI15&amp;$AJ15&amp;$AK15))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M15"/>
+      </x:c>
+      <x:c r="M15" s="67"/>
       <x:c r="N15"/>
       <x:c r="O15"/>
       <x:c r="P15"/>
@@ -3281,12 +3211,8 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B16" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A16" s="8"/>
+      <x:c r="B16" s="8"/>
       <x:c r="C16" s="9" t="str">
         <x:f>IF($A16="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A16="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3302,9 +3228,7 @@
       <x:c r="G16" s="8" t="str">
         <x:f>IF($A16="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H16" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H16" s="8"/>
       <x:c r="I16" s="8" t="str">
         <x:f>IF($A16="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3316,9 +3240,8 @@
       </x:c>
       <x:c r="L16" s="10" t="str">
         <x:f>IF(TRIM($A16)="","",IF(COUNTIF($Q16:$AK16,"?*")=0,"OK","Falta revisar: "&amp;$Q16&amp;$R16&amp;$S16&amp;$T16&amp;$U16&amp;$V16&amp;$W16&amp;$X16&amp;$Y16&amp;$Z16&amp;$AA16&amp;$AB16&amp;$AC16&amp;$AD16&amp;$AE16&amp;$AF16&amp;$AG16&amp;$AH16&amp;$AI16&amp;$AJ16&amp;$AK16))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M16"/>
+      </x:c>
+      <x:c r="M16" s="67"/>
       <x:c r="N16"/>
       <x:c r="O16"/>
       <x:c r="P16"/>
@@ -3399,12 +3322,8 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A17" s="8"/>
+      <x:c r="B17" s="8"/>
       <x:c r="C17" s="9" t="str">
         <x:f>IF($A17="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A17="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3420,9 +3339,7 @@
       <x:c r="G17" s="8" t="str">
         <x:f>IF($A17="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H17" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H17" s="8"/>
       <x:c r="I17" s="8" t="str">
         <x:f>IF($A17="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3434,9 +3351,8 @@
       </x:c>
       <x:c r="L17" s="10" t="str">
         <x:f>IF(TRIM($A17)="","",IF(COUNTIF($Q17:$AK17,"?*")=0,"OK","Falta revisar: "&amp;$Q17&amp;$R17&amp;$S17&amp;$T17&amp;$U17&amp;$V17&amp;$W17&amp;$X17&amp;$Y17&amp;$Z17&amp;$AA17&amp;$AB17&amp;$AC17&amp;$AD17&amp;$AE17&amp;$AF17&amp;$AG17&amp;$AH17&amp;$AI17&amp;$AJ17&amp;$AK17))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M17"/>
+      </x:c>
+      <x:c r="M17" s="67"/>
       <x:c r="N17"/>
       <x:c r="O17"/>
       <x:c r="P17"/>
@@ -3517,12 +3433,8 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A18" s="8"/>
+      <x:c r="B18" s="8"/>
       <x:c r="C18" s="9" t="str">
         <x:f>IF($A18="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A18="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3538,9 +3450,7 @@
       <x:c r="G18" s="8" t="str">
         <x:f>IF($A18="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H18" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H18" s="8"/>
       <x:c r="I18" s="8" t="str">
         <x:f>IF($A18="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3552,9 +3462,8 @@
       </x:c>
       <x:c r="L18" s="10" t="str">
         <x:f>IF(TRIM($A18)="","",IF(COUNTIF($Q18:$AK18,"?*")=0,"OK","Falta revisar: "&amp;$Q18&amp;$R18&amp;$S18&amp;$T18&amp;$U18&amp;$V18&amp;$W18&amp;$X18&amp;$Y18&amp;$Z18&amp;$AA18&amp;$AB18&amp;$AC18&amp;$AD18&amp;$AE18&amp;$AF18&amp;$AG18&amp;$AH18&amp;$AI18&amp;$AJ18&amp;$AK18))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M18"/>
+      </x:c>
+      <x:c r="M18" s="67"/>
       <x:c r="N18"/>
       <x:c r="O18"/>
       <x:c r="P18"/>
@@ -3635,12 +3544,8 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B19" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A19" s="8"/>
+      <x:c r="B19" s="8"/>
       <x:c r="C19" s="9" t="str">
         <x:f>IF($A19="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A19="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3656,9 +3561,7 @@
       <x:c r="G19" s="8" t="str">
         <x:f>IF($A19="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H19" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H19" s="8"/>
       <x:c r="I19" s="8" t="str">
         <x:f>IF($A19="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3670,9 +3573,8 @@
       </x:c>
       <x:c r="L19" s="10" t="str">
         <x:f>IF(TRIM($A19)="","",IF(COUNTIF($Q19:$AK19,"?*")=0,"OK","Falta revisar: "&amp;$Q19&amp;$R19&amp;$S19&amp;$T19&amp;$U19&amp;$V19&amp;$W19&amp;$X19&amp;$Y19&amp;$Z19&amp;$AA19&amp;$AB19&amp;$AC19&amp;$AD19&amp;$AE19&amp;$AF19&amp;$AG19&amp;$AH19&amp;$AI19&amp;$AJ19&amp;$AK19))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M19"/>
+      </x:c>
+      <x:c r="M19" s="67"/>
       <x:c r="N19"/>
       <x:c r="O19"/>
       <x:c r="P19"/>
@@ -3753,12 +3655,8 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B20" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="8"/>
       <x:c r="C20" s="9" t="str">
         <x:f>IF($A20="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A20="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3774,9 +3672,7 @@
       <x:c r="G20" s="8" t="str">
         <x:f>IF($A20="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H20" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H20" s="8"/>
       <x:c r="I20" s="8" t="str">
         <x:f>IF($A20="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3788,9 +3684,8 @@
       </x:c>
       <x:c r="L20" s="10" t="str">
         <x:f>IF(TRIM($A20)="","",IF(COUNTIF($Q20:$AK20,"?*")=0,"OK","Falta revisar: "&amp;$Q20&amp;$R20&amp;$S20&amp;$T20&amp;$U20&amp;$V20&amp;$W20&amp;$X20&amp;$Y20&amp;$Z20&amp;$AA20&amp;$AB20&amp;$AC20&amp;$AD20&amp;$AE20&amp;$AF20&amp;$AG20&amp;$AH20&amp;$AI20&amp;$AJ20&amp;$AK20))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M20"/>
+      </x:c>
+      <x:c r="M20" s="67"/>
       <x:c r="N20"/>
       <x:c r="O20"/>
       <x:c r="P20"/>
@@ -3871,12 +3766,8 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B21" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A21" s="8"/>
+      <x:c r="B21" s="8"/>
       <x:c r="C21" s="9" t="str">
         <x:f>IF($A21="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A21="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -3892,9 +3783,7 @@
       <x:c r="G21" s="8" t="str">
         <x:f>IF($A21="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H21" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H21" s="8"/>
       <x:c r="I21" s="8" t="str">
         <x:f>IF($A21="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -3906,9 +3795,8 @@
       </x:c>
       <x:c r="L21" s="10" t="str">
         <x:f>IF(TRIM($A21)="","",IF(COUNTIF($Q21:$AK21,"?*")=0,"OK","Falta revisar: "&amp;$Q21&amp;$R21&amp;$S21&amp;$T21&amp;$U21&amp;$V21&amp;$W21&amp;$X21&amp;$Y21&amp;$Z21&amp;$AA21&amp;$AB21&amp;$AC21&amp;$AD21&amp;$AE21&amp;$AF21&amp;$AG21&amp;$AH21&amp;$AI21&amp;$AJ21&amp;$AK21))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M21"/>
+      </x:c>
+      <x:c r="M21" s="67"/>
       <x:c r="N21"/>
       <x:c r="O21"/>
       <x:c r="P21"/>
@@ -3989,12 +3877,8 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B22" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A22" s="8"/>
+      <x:c r="B22" s="8"/>
       <x:c r="C22" s="9" t="str">
         <x:f>IF($A22="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A22="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4010,9 +3894,7 @@
       <x:c r="G22" s="8" t="str">
         <x:f>IF($A22="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H22" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H22" s="8"/>
       <x:c r="I22" s="8" t="str">
         <x:f>IF($A22="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4024,9 +3906,8 @@
       </x:c>
       <x:c r="L22" s="10" t="str">
         <x:f>IF(TRIM($A22)="","",IF(COUNTIF($Q22:$AK22,"?*")=0,"OK","Falta revisar: "&amp;$Q22&amp;$R22&amp;$S22&amp;$T22&amp;$U22&amp;$V22&amp;$W22&amp;$X22&amp;$Y22&amp;$Z22&amp;$AA22&amp;$AB22&amp;$AC22&amp;$AD22&amp;$AE22&amp;$AF22&amp;$AG22&amp;$AH22&amp;$AI22&amp;$AJ22&amp;$AK22))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M22"/>
+      </x:c>
+      <x:c r="M22" s="67"/>
       <x:c r="N22"/>
       <x:c r="O22"/>
       <x:c r="P22"/>
@@ -4107,12 +3988,8 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B23" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A23" s="8"/>
+      <x:c r="B23" s="8"/>
       <x:c r="C23" s="9" t="str">
         <x:f>IF($A23="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A23="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4128,9 +4005,7 @@
       <x:c r="G23" s="8" t="str">
         <x:f>IF($A23="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H23" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H23" s="8"/>
       <x:c r="I23" s="8" t="str">
         <x:f>IF($A23="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4142,9 +4017,8 @@
       </x:c>
       <x:c r="L23" s="10" t="str">
         <x:f>IF(TRIM($A23)="","",IF(COUNTIF($Q23:$AK23,"?*")=0,"OK","Falta revisar: "&amp;$Q23&amp;$R23&amp;$S23&amp;$T23&amp;$U23&amp;$V23&amp;$W23&amp;$X23&amp;$Y23&amp;$Z23&amp;$AA23&amp;$AB23&amp;$AC23&amp;$AD23&amp;$AE23&amp;$AF23&amp;$AG23&amp;$AH23&amp;$AI23&amp;$AJ23&amp;$AK23))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M23"/>
+      </x:c>
+      <x:c r="M23" s="67"/>
       <x:c r="N23"/>
       <x:c r="O23"/>
       <x:c r="P23"/>
@@ -4225,12 +4099,8 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B24" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A24" s="8"/>
+      <x:c r="B24" s="8"/>
       <x:c r="C24" s="9" t="str">
         <x:f>IF($A24="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A24="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4246,9 +4116,7 @@
       <x:c r="G24" s="8" t="str">
         <x:f>IF($A24="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H24" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H24" s="8"/>
       <x:c r="I24" s="8" t="str">
         <x:f>IF($A24="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4260,9 +4128,8 @@
       </x:c>
       <x:c r="L24" s="10" t="str">
         <x:f>IF(TRIM($A24)="","",IF(COUNTIF($Q24:$AK24,"?*")=0,"OK","Falta revisar: "&amp;$Q24&amp;$R24&amp;$S24&amp;$T24&amp;$U24&amp;$V24&amp;$W24&amp;$X24&amp;$Y24&amp;$Z24&amp;$AA24&amp;$AB24&amp;$AC24&amp;$AD24&amp;$AE24&amp;$AF24&amp;$AG24&amp;$AH24&amp;$AI24&amp;$AJ24&amp;$AK24))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M24"/>
+      </x:c>
+      <x:c r="M24" s="67"/>
       <x:c r="N24"/>
       <x:c r="O24"/>
       <x:c r="P24"/>
@@ -4343,12 +4210,8 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B25" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A25" s="8"/>
+      <x:c r="B25" s="8"/>
       <x:c r="C25" s="9" t="str">
         <x:f>IF($A25="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A25="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4364,9 +4227,7 @@
       <x:c r="G25" s="8" t="str">
         <x:f>IF($A25="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H25" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H25" s="8"/>
       <x:c r="I25" s="8" t="str">
         <x:f>IF($A25="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4378,9 +4239,8 @@
       </x:c>
       <x:c r="L25" s="10" t="str">
         <x:f>IF(TRIM($A25)="","",IF(COUNTIF($Q25:$AK25,"?*")=0,"OK","Falta revisar: "&amp;$Q25&amp;$R25&amp;$S25&amp;$T25&amp;$U25&amp;$V25&amp;$W25&amp;$X25&amp;$Y25&amp;$Z25&amp;$AA25&amp;$AB25&amp;$AC25&amp;$AD25&amp;$AE25&amp;$AF25&amp;$AG25&amp;$AH25&amp;$AI25&amp;$AJ25&amp;$AK25))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M25"/>
+      </x:c>
+      <x:c r="M25" s="67"/>
       <x:c r="N25"/>
       <x:c r="O25"/>
       <x:c r="P25"/>
@@ -4461,12 +4321,8 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B26" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A26" s="8"/>
+      <x:c r="B26" s="8"/>
       <x:c r="C26" s="9" t="str">
         <x:f>IF($A26="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A26="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4482,9 +4338,7 @@
       <x:c r="G26" s="8" t="str">
         <x:f>IF($A26="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H26" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H26" s="8"/>
       <x:c r="I26" s="8" t="str">
         <x:f>IF($A26="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4496,9 +4350,8 @@
       </x:c>
       <x:c r="L26" s="10" t="str">
         <x:f>IF(TRIM($A26)="","",IF(COUNTIF($Q26:$AK26,"?*")=0,"OK","Falta revisar: "&amp;$Q26&amp;$R26&amp;$S26&amp;$T26&amp;$U26&amp;$V26&amp;$W26&amp;$X26&amp;$Y26&amp;$Z26&amp;$AA26&amp;$AB26&amp;$AC26&amp;$AD26&amp;$AE26&amp;$AF26&amp;$AG26&amp;$AH26&amp;$AI26&amp;$AJ26&amp;$AK26))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M26"/>
+      </x:c>
+      <x:c r="M26" s="67"/>
       <x:c r="N26"/>
       <x:c r="O26"/>
       <x:c r="P26"/>
@@ -4579,12 +4432,8 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B27" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A27" s="8"/>
+      <x:c r="B27" s="8"/>
       <x:c r="C27" s="9" t="str">
         <x:f>IF($A27="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A27="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4600,9 +4449,7 @@
       <x:c r="G27" s="8" t="str">
         <x:f>IF($A27="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H27" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H27" s="8"/>
       <x:c r="I27" s="8" t="str">
         <x:f>IF($A27="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4614,9 +4461,8 @@
       </x:c>
       <x:c r="L27" s="10" t="str">
         <x:f>IF(TRIM($A27)="","",IF(COUNTIF($Q27:$AK27,"?*")=0,"OK","Falta revisar: "&amp;$Q27&amp;$R27&amp;$S27&amp;$T27&amp;$U27&amp;$V27&amp;$W27&amp;$X27&amp;$Y27&amp;$Z27&amp;$AA27&amp;$AB27&amp;$AC27&amp;$AD27&amp;$AE27&amp;$AF27&amp;$AG27&amp;$AH27&amp;$AI27&amp;$AJ27&amp;$AK27))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M27"/>
+      </x:c>
+      <x:c r="M27" s="67"/>
       <x:c r="N27"/>
       <x:c r="O27"/>
       <x:c r="P27"/>
@@ -4697,12 +4543,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B28" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A28" s="8"/>
+      <x:c r="B28" s="8"/>
       <x:c r="C28" s="9" t="str">
         <x:f>IF($A28="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A28="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4718,9 +4560,7 @@
       <x:c r="G28" s="8" t="str">
         <x:f>IF($A28="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H28" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H28" s="8"/>
       <x:c r="I28" s="8" t="str">
         <x:f>IF($A28="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4732,9 +4572,8 @@
       </x:c>
       <x:c r="L28" s="10" t="str">
         <x:f>IF(TRIM($A28)="","",IF(COUNTIF($Q28:$AK28,"?*")=0,"OK","Falta revisar: "&amp;$Q28&amp;$R28&amp;$S28&amp;$T28&amp;$U28&amp;$V28&amp;$W28&amp;$X28&amp;$Y28&amp;$Z28&amp;$AA28&amp;$AB28&amp;$AC28&amp;$AD28&amp;$AE28&amp;$AF28&amp;$AG28&amp;$AH28&amp;$AI28&amp;$AJ28&amp;$AK28))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M28"/>
+      </x:c>
+      <x:c r="M28" s="67"/>
       <x:c r="N28"/>
       <x:c r="O28"/>
       <x:c r="P28"/>
@@ -4815,12 +4654,8 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B29" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A29" s="8"/>
+      <x:c r="B29" s="8"/>
       <x:c r="C29" s="9" t="str">
         <x:f>IF($A29="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A29="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4836,9 +4671,7 @@
       <x:c r="G29" s="8" t="str">
         <x:f>IF($A29="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H29" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H29" s="8"/>
       <x:c r="I29" s="8" t="str">
         <x:f>IF($A29="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4850,9 +4683,8 @@
       </x:c>
       <x:c r="L29" s="10" t="str">
         <x:f>IF(TRIM($A29)="","",IF(COUNTIF($Q29:$AK29,"?*")=0,"OK","Falta revisar: "&amp;$Q29&amp;$R29&amp;$S29&amp;$T29&amp;$U29&amp;$V29&amp;$W29&amp;$X29&amp;$Y29&amp;$Z29&amp;$AA29&amp;$AB29&amp;$AC29&amp;$AD29&amp;$AE29&amp;$AF29&amp;$AG29&amp;$AH29&amp;$AI29&amp;$AJ29&amp;$AK29))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M29"/>
+      </x:c>
+      <x:c r="M29" s="67"/>
       <x:c r="N29"/>
       <x:c r="O29"/>
       <x:c r="P29"/>
@@ -4933,12 +4765,8 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B30" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A30" s="8"/>
+      <x:c r="B30" s="8"/>
       <x:c r="C30" s="9" t="str">
         <x:f>IF($A30="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A30="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -4954,9 +4782,7 @@
       <x:c r="G30" s="8" t="str">
         <x:f>IF($A30="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H30" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H30" s="8"/>
       <x:c r="I30" s="8" t="str">
         <x:f>IF($A30="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -4968,9 +4794,8 @@
       </x:c>
       <x:c r="L30" s="10" t="str">
         <x:f>IF(TRIM($A30)="","",IF(COUNTIF($Q30:$AK30,"?*")=0,"OK","Falta revisar: "&amp;$Q30&amp;$R30&amp;$S30&amp;$T30&amp;$U30&amp;$V30&amp;$W30&amp;$X30&amp;$Y30&amp;$Z30&amp;$AA30&amp;$AB30&amp;$AC30&amp;$AD30&amp;$AE30&amp;$AF30&amp;$AG30&amp;$AH30&amp;$AI30&amp;$AJ30&amp;$AK30))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M30"/>
+      </x:c>
+      <x:c r="M30" s="67"/>
       <x:c r="N30"/>
       <x:c r="O30"/>
       <x:c r="P30"/>
@@ -5051,12 +4876,8 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B31" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A31" s="8"/>
+      <x:c r="B31" s="8"/>
       <x:c r="C31" s="9" t="str">
         <x:f>IF($A31="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A31="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5072,9 +4893,7 @@
       <x:c r="G31" s="8" t="str">
         <x:f>IF($A31="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H31" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H31" s="8"/>
       <x:c r="I31" s="8" t="str">
         <x:f>IF($A31="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5086,9 +4905,8 @@
       </x:c>
       <x:c r="L31" s="10" t="str">
         <x:f>IF(TRIM($A31)="","",IF(COUNTIF($Q31:$AK31,"?*")=0,"OK","Falta revisar: "&amp;$Q31&amp;$R31&amp;$S31&amp;$T31&amp;$U31&amp;$V31&amp;$W31&amp;$X31&amp;$Y31&amp;$Z31&amp;$AA31&amp;$AB31&amp;$AC31&amp;$AD31&amp;$AE31&amp;$AF31&amp;$AG31&amp;$AH31&amp;$AI31&amp;$AJ31&amp;$AK31))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M31"/>
+      </x:c>
+      <x:c r="M31" s="67"/>
       <x:c r="N31"/>
       <x:c r="O31"/>
       <x:c r="P31"/>
@@ -5169,12 +4987,8 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A32" s="11"/>
+      <x:c r="B32" s="11"/>
       <x:c r="C32" s="12" t="str">
         <x:f>IF($A32="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A32="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5190,9 +5004,7 @@
       <x:c r="G32" s="11" t="str">
         <x:f>IF($A32="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H32" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H32" s="11"/>
       <x:c r="I32" s="11" t="str">
         <x:f>IF($A32="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5204,9 +5016,8 @@
       </x:c>
       <x:c r="L32" s="13" t="str">
         <x:f>IF(TRIM($A32)="","",IF(COUNTIF($Q32:$AK32,"?*")=0,"OK","Falta revisar: "&amp;$Q32&amp;$R32&amp;$S32&amp;$T32&amp;$U32&amp;$V32&amp;$W32&amp;$X32&amp;$Y32&amp;$Z32&amp;$AA32&amp;$AB32&amp;$AC32&amp;$AD32&amp;$AE32&amp;$AF32&amp;$AG32&amp;$AH32&amp;$AI32&amp;$AJ32&amp;$AK32))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M32"/>
+      </x:c>
+      <x:c r="M32" s="67"/>
       <x:c r="N32"/>
       <x:c r="O32"/>
       <x:c r="P32"/>
@@ -5287,12 +5098,8 @@
       </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
-      <x:c r="A33" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B33" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A33" s="11"/>
+      <x:c r="B33" s="11"/>
       <x:c r="C33" s="12" t="str">
         <x:f>IF($A33="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A33="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5308,9 +5115,7 @@
       <x:c r="G33" s="11" t="str">
         <x:f>IF($A33="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H33" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H33" s="11"/>
       <x:c r="I33" s="11" t="str">
         <x:f>IF($A33="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5322,9 +5127,8 @@
       </x:c>
       <x:c r="L33" s="13" t="str">
         <x:f>IF(TRIM($A33)="","",IF(COUNTIF($Q33:$AK33,"?*")=0,"OK","Falta revisar: "&amp;$Q33&amp;$R33&amp;$S33&amp;$T33&amp;$U33&amp;$V33&amp;$W33&amp;$X33&amp;$Y33&amp;$Z33&amp;$AA33&amp;$AB33&amp;$AC33&amp;$AD33&amp;$AE33&amp;$AF33&amp;$AG33&amp;$AH33&amp;$AI33&amp;$AJ33&amp;$AK33))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M33"/>
+      </x:c>
+      <x:c r="M33" s="67"/>
       <x:c r="N33"/>
       <x:c r="O33"/>
       <x:c r="P33"/>
@@ -5405,12 +5209,8 @@
       </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A34" s="11"/>
+      <x:c r="B34" s="11"/>
       <x:c r="C34" s="12" t="str">
         <x:f>IF($A34="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A34="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5426,9 +5226,7 @@
       <x:c r="G34" s="11" t="str">
         <x:f>IF($A34="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H34" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H34" s="11"/>
       <x:c r="I34" s="11" t="str">
         <x:f>IF($A34="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5440,9 +5238,8 @@
       </x:c>
       <x:c r="L34" s="13" t="str">
         <x:f>IF(TRIM($A34)="","",IF(COUNTIF($Q34:$AK34,"?*")=0,"OK","Falta revisar: "&amp;$Q34&amp;$R34&amp;$S34&amp;$T34&amp;$U34&amp;$V34&amp;$W34&amp;$X34&amp;$Y34&amp;$Z34&amp;$AA34&amp;$AB34&amp;$AC34&amp;$AD34&amp;$AE34&amp;$AF34&amp;$AG34&amp;$AH34&amp;$AI34&amp;$AJ34&amp;$AK34))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M34"/>
+      </x:c>
+      <x:c r="M34" s="67"/>
       <x:c r="N34"/>
       <x:c r="O34"/>
       <x:c r="P34"/>
@@ -5523,12 +5320,8 @@
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
-      <x:c r="A35" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A35" s="11"/>
+      <x:c r="B35" s="11"/>
       <x:c r="C35" s="12" t="str">
         <x:f>IF($A35="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A35="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5544,9 +5337,7 @@
       <x:c r="G35" s="11" t="str">
         <x:f>IF($A35="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H35" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H35" s="11"/>
       <x:c r="I35" s="11" t="str">
         <x:f>IF($A35="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5558,9 +5349,8 @@
       </x:c>
       <x:c r="L35" s="13" t="str">
         <x:f>IF(TRIM($A35)="","",IF(COUNTIF($Q35:$AK35,"?*")=0,"OK","Falta revisar: "&amp;$Q35&amp;$R35&amp;$S35&amp;$T35&amp;$U35&amp;$V35&amp;$W35&amp;$X35&amp;$Y35&amp;$Z35&amp;$AA35&amp;$AB35&amp;$AC35&amp;$AD35&amp;$AE35&amp;$AF35&amp;$AG35&amp;$AH35&amp;$AI35&amp;$AJ35&amp;$AK35))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M35"/>
+      </x:c>
+      <x:c r="M35" s="67"/>
       <x:c r="N35"/>
       <x:c r="O35"/>
       <x:c r="P35"/>
@@ -5641,12 +5431,8 @@
       </x:c>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
-      <x:c r="A36" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B36" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A36" s="11"/>
+      <x:c r="B36" s="11"/>
       <x:c r="C36" s="12" t="str">
         <x:f>IF($A36="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A36="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5662,9 +5448,7 @@
       <x:c r="G36" s="11" t="str">
         <x:f>IF($A36="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H36" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H36" s="11"/>
       <x:c r="I36" s="11" t="str">
         <x:f>IF($A36="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5676,9 +5460,8 @@
       </x:c>
       <x:c r="L36" s="13" t="str">
         <x:f>IF(TRIM($A36)="","",IF(COUNTIF($Q36:$AK36,"?*")=0,"OK","Falta revisar: "&amp;$Q36&amp;$R36&amp;$S36&amp;$T36&amp;$U36&amp;$V36&amp;$W36&amp;$X36&amp;$Y36&amp;$Z36&amp;$AA36&amp;$AB36&amp;$AC36&amp;$AD36&amp;$AE36&amp;$AF36&amp;$AG36&amp;$AH36&amp;$AI36&amp;$AJ36&amp;$AK36))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M36"/>
+      </x:c>
+      <x:c r="M36" s="67"/>
       <x:c r="N36"/>
       <x:c r="O36"/>
       <x:c r="P36"/>
@@ -5759,12 +5542,8 @@
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
-      <x:c r="A37" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B37" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A37" s="11"/>
+      <x:c r="B37" s="11"/>
       <x:c r="C37" s="12" t="str">
         <x:f>IF($A37="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A37="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5780,9 +5559,7 @@
       <x:c r="G37" s="11" t="str">
         <x:f>IF($A37="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H37" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H37" s="11"/>
       <x:c r="I37" s="11" t="str">
         <x:f>IF($A37="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5794,9 +5571,8 @@
       </x:c>
       <x:c r="L37" s="13" t="str">
         <x:f>IF(TRIM($A37)="","",IF(COUNTIF($Q37:$AK37,"?*")=0,"OK","Falta revisar: "&amp;$Q37&amp;$R37&amp;$S37&amp;$T37&amp;$U37&amp;$V37&amp;$W37&amp;$X37&amp;$Y37&amp;$Z37&amp;$AA37&amp;$AB37&amp;$AC37&amp;$AD37&amp;$AE37&amp;$AF37&amp;$AG37&amp;$AH37&amp;$AI37&amp;$AJ37&amp;$AK37))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M37"/>
+      </x:c>
+      <x:c r="M37" s="67"/>
       <x:c r="N37"/>
       <x:c r="O37"/>
       <x:c r="P37"/>
@@ -5877,12 +5653,8 @@
       </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
-      <x:c r="A38" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B38" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A38" s="11"/>
+      <x:c r="B38" s="11"/>
       <x:c r="C38" s="12" t="str">
         <x:f>IF($A38="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A38="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -5898,9 +5670,7 @@
       <x:c r="G38" s="11" t="str">
         <x:f>IF($A38="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H38" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H38" s="11"/>
       <x:c r="I38" s="11" t="str">
         <x:f>IF($A38="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -5912,9 +5682,8 @@
       </x:c>
       <x:c r="L38" s="13" t="str">
         <x:f>IF(TRIM($A38)="","",IF(COUNTIF($Q38:$AK38,"?*")=0,"OK","Falta revisar: "&amp;$Q38&amp;$R38&amp;$S38&amp;$T38&amp;$U38&amp;$V38&amp;$W38&amp;$X38&amp;$Y38&amp;$Z38&amp;$AA38&amp;$AB38&amp;$AC38&amp;$AD38&amp;$AE38&amp;$AF38&amp;$AG38&amp;$AH38&amp;$AI38&amp;$AJ38&amp;$AK38))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M38"/>
+      </x:c>
+      <x:c r="M38" s="67"/>
       <x:c r="N38"/>
       <x:c r="O38"/>
       <x:c r="P38"/>
@@ -5995,12 +5764,8 @@
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
-      <x:c r="A39" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B39" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A39" s="11"/>
+      <x:c r="B39" s="11"/>
       <x:c r="C39" s="12" t="str">
         <x:f>IF($A39="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A39="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6016,9 +5781,7 @@
       <x:c r="G39" s="11" t="str">
         <x:f>IF($A39="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H39" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H39" s="11"/>
       <x:c r="I39" s="11" t="str">
         <x:f>IF($A39="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6030,9 +5793,8 @@
       </x:c>
       <x:c r="L39" s="13" t="str">
         <x:f>IF(TRIM($A39)="","",IF(COUNTIF($Q39:$AK39,"?*")=0,"OK","Falta revisar: "&amp;$Q39&amp;$R39&amp;$S39&amp;$T39&amp;$U39&amp;$V39&amp;$W39&amp;$X39&amp;$Y39&amp;$Z39&amp;$AA39&amp;$AB39&amp;$AC39&amp;$AD39&amp;$AE39&amp;$AF39&amp;$AG39&amp;$AH39&amp;$AI39&amp;$AJ39&amp;$AK39))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M39"/>
+      </x:c>
+      <x:c r="M39" s="67"/>
       <x:c r="N39"/>
       <x:c r="O39"/>
       <x:c r="P39"/>
@@ -6113,12 +5875,8 @@
       </x:c>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
-      <x:c r="A40" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B40" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A40" s="11"/>
+      <x:c r="B40" s="11"/>
       <x:c r="C40" s="12" t="str">
         <x:f>IF($A40="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A40="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6134,9 +5892,7 @@
       <x:c r="G40" s="11" t="str">
         <x:f>IF($A40="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H40" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H40" s="11"/>
       <x:c r="I40" s="11" t="str">
         <x:f>IF($A40="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6148,9 +5904,8 @@
       </x:c>
       <x:c r="L40" s="13" t="str">
         <x:f>IF(TRIM($A40)="","",IF(COUNTIF($Q40:$AK40,"?*")=0,"OK","Falta revisar: "&amp;$Q40&amp;$R40&amp;$S40&amp;$T40&amp;$U40&amp;$V40&amp;$W40&amp;$X40&amp;$Y40&amp;$Z40&amp;$AA40&amp;$AB40&amp;$AC40&amp;$AD40&amp;$AE40&amp;$AF40&amp;$AG40&amp;$AH40&amp;$AI40&amp;$AJ40&amp;$AK40))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M40"/>
+      </x:c>
+      <x:c r="M40" s="67"/>
       <x:c r="N40"/>
       <x:c r="O40"/>
       <x:c r="P40"/>
@@ -6231,12 +5986,8 @@
       </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
-      <x:c r="A41" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B41" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A41" s="11"/>
+      <x:c r="B41" s="11"/>
       <x:c r="C41" s="12" t="str">
         <x:f>IF($A41="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A41="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6252,9 +6003,7 @@
       <x:c r="G41" s="11" t="str">
         <x:f>IF($A41="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H41" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H41" s="11"/>
       <x:c r="I41" s="11" t="str">
         <x:f>IF($A41="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6266,9 +6015,8 @@
       </x:c>
       <x:c r="L41" s="13" t="str">
         <x:f>IF(TRIM($A41)="","",IF(COUNTIF($Q41:$AK41,"?*")=0,"OK","Falta revisar: "&amp;$Q41&amp;$R41&amp;$S41&amp;$T41&amp;$U41&amp;$V41&amp;$W41&amp;$X41&amp;$Y41&amp;$Z41&amp;$AA41&amp;$AB41&amp;$AC41&amp;$AD41&amp;$AE41&amp;$AF41&amp;$AG41&amp;$AH41&amp;$AI41&amp;$AJ41&amp;$AK41))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M41"/>
+      </x:c>
+      <x:c r="M41" s="67"/>
       <x:c r="N41"/>
       <x:c r="O41"/>
       <x:c r="P41"/>
@@ -6349,12 +6097,8 @@
       </x:c>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
-      <x:c r="A42" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B42" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A42" s="11"/>
+      <x:c r="B42" s="11"/>
       <x:c r="C42" s="12" t="str">
         <x:f>IF($A42="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A42="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6370,9 +6114,7 @@
       <x:c r="G42" s="11" t="str">
         <x:f>IF($A42="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H42" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H42" s="11"/>
       <x:c r="I42" s="11" t="str">
         <x:f>IF($A42="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6384,9 +6126,8 @@
       </x:c>
       <x:c r="L42" s="13" t="str">
         <x:f>IF(TRIM($A42)="","",IF(COUNTIF($Q42:$AK42,"?*")=0,"OK","Falta revisar: "&amp;$Q42&amp;$R42&amp;$S42&amp;$T42&amp;$U42&amp;$V42&amp;$W42&amp;$X42&amp;$Y42&amp;$Z42&amp;$AA42&amp;$AB42&amp;$AC42&amp;$AD42&amp;$AE42&amp;$AF42&amp;$AG42&amp;$AH42&amp;$AI42&amp;$AJ42&amp;$AK42))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M42"/>
+      </x:c>
+      <x:c r="M42" s="67"/>
       <x:c r="N42"/>
       <x:c r="O42"/>
       <x:c r="P42"/>
@@ -6467,12 +6208,8 @@
       </x:c>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
-      <x:c r="A43" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B43" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A43" s="11"/>
+      <x:c r="B43" s="11"/>
       <x:c r="C43" s="12" t="str">
         <x:f>IF($A43="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A43="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6488,9 +6225,7 @@
       <x:c r="G43" s="11" t="str">
         <x:f>IF($A43="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H43" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H43" s="11"/>
       <x:c r="I43" s="11" t="str">
         <x:f>IF($A43="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6502,9 +6237,8 @@
       </x:c>
       <x:c r="L43" s="13" t="str">
         <x:f>IF(TRIM($A43)="","",IF(COUNTIF($Q43:$AK43,"?*")=0,"OK","Falta revisar: "&amp;$Q43&amp;$R43&amp;$S43&amp;$T43&amp;$U43&amp;$V43&amp;$W43&amp;$X43&amp;$Y43&amp;$Z43&amp;$AA43&amp;$AB43&amp;$AC43&amp;$AD43&amp;$AE43&amp;$AF43&amp;$AG43&amp;$AH43&amp;$AI43&amp;$AJ43&amp;$AK43))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M43"/>
+      </x:c>
+      <x:c r="M43" s="67"/>
       <x:c r="N43"/>
       <x:c r="O43"/>
       <x:c r="P43"/>
@@ -6585,12 +6319,8 @@
       </x:c>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
-      <x:c r="A44" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B44" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A44" s="11"/>
+      <x:c r="B44" s="11"/>
       <x:c r="C44" s="12" t="str">
         <x:f>IF($A44="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A44="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6606,9 +6336,7 @@
       <x:c r="G44" s="11" t="str">
         <x:f>IF($A44="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H44" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H44" s="11"/>
       <x:c r="I44" s="11" t="str">
         <x:f>IF($A44="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6620,9 +6348,8 @@
       </x:c>
       <x:c r="L44" s="13" t="str">
         <x:f>IF(TRIM($A44)="","",IF(COUNTIF($Q44:$AK44,"?*")=0,"OK","Falta revisar: "&amp;$Q44&amp;$R44&amp;$S44&amp;$T44&amp;$U44&amp;$V44&amp;$W44&amp;$X44&amp;$Y44&amp;$Z44&amp;$AA44&amp;$AB44&amp;$AC44&amp;$AD44&amp;$AE44&amp;$AF44&amp;$AG44&amp;$AH44&amp;$AI44&amp;$AJ44&amp;$AK44))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M44"/>
+      </x:c>
+      <x:c r="M44" s="67"/>
       <x:c r="N44"/>
       <x:c r="O44"/>
       <x:c r="P44"/>
@@ -6703,12 +6430,8 @@
       </x:c>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
-      <x:c r="A45" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B45" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A45" s="11"/>
+      <x:c r="B45" s="11"/>
       <x:c r="C45" s="12" t="str">
         <x:f>IF($A45="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A45="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6724,9 +6447,7 @@
       <x:c r="G45" s="11" t="str">
         <x:f>IF($A45="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H45" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H45" s="11"/>
       <x:c r="I45" s="11" t="str">
         <x:f>IF($A45="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6738,9 +6459,8 @@
       </x:c>
       <x:c r="L45" s="13" t="str">
         <x:f>IF(TRIM($A45)="","",IF(COUNTIF($Q45:$AK45,"?*")=0,"OK","Falta revisar: "&amp;$Q45&amp;$R45&amp;$S45&amp;$T45&amp;$U45&amp;$V45&amp;$W45&amp;$X45&amp;$Y45&amp;$Z45&amp;$AA45&amp;$AB45&amp;$AC45&amp;$AD45&amp;$AE45&amp;$AF45&amp;$AG45&amp;$AH45&amp;$AI45&amp;$AJ45&amp;$AK45))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M45"/>
+      </x:c>
+      <x:c r="M45" s="67"/>
       <x:c r="N45"/>
       <x:c r="O45"/>
       <x:c r="P45"/>
@@ -6821,12 +6541,8 @@
       </x:c>
     </x:row>
     <x:row r="46" ht="24" customHeight="1">
-      <x:c r="A46" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B46" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A46" s="11"/>
+      <x:c r="B46" s="11"/>
       <x:c r="C46" s="12" t="str">
         <x:f>IF($A46="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A46="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6842,9 +6558,7 @@
       <x:c r="G46" s="11" t="str">
         <x:f>IF($A46="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H46" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H46" s="11"/>
       <x:c r="I46" s="11" t="str">
         <x:f>IF($A46="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6856,9 +6570,8 @@
       </x:c>
       <x:c r="L46" s="13" t="str">
         <x:f>IF(TRIM($A46)="","",IF(COUNTIF($Q46:$AK46,"?*")=0,"OK","Falta revisar: "&amp;$Q46&amp;$R46&amp;$S46&amp;$T46&amp;$U46&amp;$V46&amp;$W46&amp;$X46&amp;$Y46&amp;$Z46&amp;$AA46&amp;$AB46&amp;$AC46&amp;$AD46&amp;$AE46&amp;$AF46&amp;$AG46&amp;$AH46&amp;$AI46&amp;$AJ46&amp;$AK46))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M46"/>
+      </x:c>
+      <x:c r="M46" s="67"/>
       <x:c r="N46"/>
       <x:c r="O46"/>
       <x:c r="P46"/>
@@ -6939,12 +6652,8 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
-      <x:c r="A47" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B47" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A47" s="11"/>
+      <x:c r="B47" s="11"/>
       <x:c r="C47" s="12" t="str">
         <x:f>IF($A47="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A47="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -6960,9 +6669,7 @@
       <x:c r="G47" s="11" t="str">
         <x:f>IF($A47="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H47" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H47" s="11"/>
       <x:c r="I47" s="11" t="str">
         <x:f>IF($A47="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -6974,9 +6681,8 @@
       </x:c>
       <x:c r="L47" s="13" t="str">
         <x:f>IF(TRIM($A47)="","",IF(COUNTIF($Q47:$AK47,"?*")=0,"OK","Falta revisar: "&amp;$Q47&amp;$R47&amp;$S47&amp;$T47&amp;$U47&amp;$V47&amp;$W47&amp;$X47&amp;$Y47&amp;$Z47&amp;$AA47&amp;$AB47&amp;$AC47&amp;$AD47&amp;$AE47&amp;$AF47&amp;$AG47&amp;$AH47&amp;$AI47&amp;$AJ47&amp;$AK47))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M47"/>
+      </x:c>
+      <x:c r="M47" s="67"/>
       <x:c r="N47"/>
       <x:c r="O47"/>
       <x:c r="P47"/>
@@ -7057,12 +6763,8 @@
       </x:c>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
-      <x:c r="A48" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B48" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A48" s="11"/>
+      <x:c r="B48" s="11"/>
       <x:c r="C48" s="12" t="str">
         <x:f>IF($A48="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A48="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7078,9 +6780,7 @@
       <x:c r="G48" s="11" t="str">
         <x:f>IF($A48="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H48" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H48" s="11"/>
       <x:c r="I48" s="11" t="str">
         <x:f>IF($A48="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7092,9 +6792,8 @@
       </x:c>
       <x:c r="L48" s="13" t="str">
         <x:f>IF(TRIM($A48)="","",IF(COUNTIF($Q48:$AK48,"?*")=0,"OK","Falta revisar: "&amp;$Q48&amp;$R48&amp;$S48&amp;$T48&amp;$U48&amp;$V48&amp;$W48&amp;$X48&amp;$Y48&amp;$Z48&amp;$AA48&amp;$AB48&amp;$AC48&amp;$AD48&amp;$AE48&amp;$AF48&amp;$AG48&amp;$AH48&amp;$AI48&amp;$AJ48&amp;$AK48))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M48"/>
+      </x:c>
+      <x:c r="M48" s="67"/>
       <x:c r="N48"/>
       <x:c r="O48"/>
       <x:c r="P48"/>
@@ -7175,12 +6874,8 @@
       </x:c>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
-      <x:c r="A49" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B49" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A49" s="11"/>
+      <x:c r="B49" s="11"/>
       <x:c r="C49" s="12" t="str">
         <x:f>IF($A49="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A49="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7196,9 +6891,7 @@
       <x:c r="G49" s="11" t="str">
         <x:f>IF($A49="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H49" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H49" s="11"/>
       <x:c r="I49" s="11" t="str">
         <x:f>IF($A49="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7210,9 +6903,8 @@
       </x:c>
       <x:c r="L49" s="13" t="str">
         <x:f>IF(TRIM($A49)="","",IF(COUNTIF($Q49:$AK49,"?*")=0,"OK","Falta revisar: "&amp;$Q49&amp;$R49&amp;$S49&amp;$T49&amp;$U49&amp;$V49&amp;$W49&amp;$X49&amp;$Y49&amp;$Z49&amp;$AA49&amp;$AB49&amp;$AC49&amp;$AD49&amp;$AE49&amp;$AF49&amp;$AG49&amp;$AH49&amp;$AI49&amp;$AJ49&amp;$AK49))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M49"/>
+      </x:c>
+      <x:c r="M49" s="67"/>
       <x:c r="N49"/>
       <x:c r="O49"/>
       <x:c r="P49"/>
@@ -7293,12 +6985,8 @@
       </x:c>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
-      <x:c r="A50" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B50" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A50" s="11"/>
+      <x:c r="B50" s="11"/>
       <x:c r="C50" s="12" t="str">
         <x:f>IF($A50="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A50="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7314,9 +7002,7 @@
       <x:c r="G50" s="11" t="str">
         <x:f>IF($A50="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H50" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H50" s="11"/>
       <x:c r="I50" s="11" t="str">
         <x:f>IF($A50="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7328,9 +7014,8 @@
       </x:c>
       <x:c r="L50" s="13" t="str">
         <x:f>IF(TRIM($A50)="","",IF(COUNTIF($Q50:$AK50,"?*")=0,"OK","Falta revisar: "&amp;$Q50&amp;$R50&amp;$S50&amp;$T50&amp;$U50&amp;$V50&amp;$W50&amp;$X50&amp;$Y50&amp;$Z50&amp;$AA50&amp;$AB50&amp;$AC50&amp;$AD50&amp;$AE50&amp;$AF50&amp;$AG50&amp;$AH50&amp;$AI50&amp;$AJ50&amp;$AK50))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M50"/>
+      </x:c>
+      <x:c r="M50" s="67"/>
       <x:c r="N50"/>
       <x:c r="O50"/>
       <x:c r="P50"/>
@@ -7411,12 +7096,8 @@
       </x:c>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
-      <x:c r="A51" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B51" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A51" s="11"/>
+      <x:c r="B51" s="11"/>
       <x:c r="C51" s="12" t="str">
         <x:f>IF($A51="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A51="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7432,9 +7113,7 @@
       <x:c r="G51" s="11" t="str">
         <x:f>IF($A51="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H51" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H51" s="11"/>
       <x:c r="I51" s="11" t="str">
         <x:f>IF($A51="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7446,9 +7125,8 @@
       </x:c>
       <x:c r="L51" s="13" t="str">
         <x:f>IF(TRIM($A51)="","",IF(COUNTIF($Q51:$AK51,"?*")=0,"OK","Falta revisar: "&amp;$Q51&amp;$R51&amp;$S51&amp;$T51&amp;$U51&amp;$V51&amp;$W51&amp;$X51&amp;$Y51&amp;$Z51&amp;$AA51&amp;$AB51&amp;$AC51&amp;$AD51&amp;$AE51&amp;$AF51&amp;$AG51&amp;$AH51&amp;$AI51&amp;$AJ51&amp;$AK51))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M51"/>
+      </x:c>
+      <x:c r="M51" s="67"/>
       <x:c r="N51"/>
       <x:c r="O51"/>
       <x:c r="P51"/>
@@ -7529,12 +7207,8 @@
       </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
-      <x:c r="A52" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B52" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A52" s="11"/>
+      <x:c r="B52" s="11"/>
       <x:c r="C52" s="12" t="str">
         <x:f>IF($A52="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A52="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7550,9 +7224,7 @@
       <x:c r="G52" s="11" t="str">
         <x:f>IF($A52="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H52" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H52" s="11"/>
       <x:c r="I52" s="11" t="str">
         <x:f>IF($A52="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7564,9 +7236,8 @@
       </x:c>
       <x:c r="L52" s="13" t="str">
         <x:f>IF(TRIM($A52)="","",IF(COUNTIF($Q52:$AK52,"?*")=0,"OK","Falta revisar: "&amp;$Q52&amp;$R52&amp;$S52&amp;$T52&amp;$U52&amp;$V52&amp;$W52&amp;$X52&amp;$Y52&amp;$Z52&amp;$AA52&amp;$AB52&amp;$AC52&amp;$AD52&amp;$AE52&amp;$AF52&amp;$AG52&amp;$AH52&amp;$AI52&amp;$AJ52&amp;$AK52))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M52"/>
+      </x:c>
+      <x:c r="M52" s="67"/>
       <x:c r="N52"/>
       <x:c r="O52"/>
       <x:c r="P52"/>
@@ -7647,12 +7318,8 @@
       </x:c>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
-      <x:c r="A53" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B53" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A53" s="11"/>
+      <x:c r="B53" s="11"/>
       <x:c r="C53" s="12" t="str">
         <x:f>IF($A53="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A53="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7668,9 +7335,7 @@
       <x:c r="G53" s="11" t="str">
         <x:f>IF($A53="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H53" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H53" s="11"/>
       <x:c r="I53" s="11" t="str">
         <x:f>IF($A53="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7682,9 +7347,8 @@
       </x:c>
       <x:c r="L53" s="13" t="str">
         <x:f>IF(TRIM($A53)="","",IF(COUNTIF($Q53:$AK53,"?*")=0,"OK","Falta revisar: "&amp;$Q53&amp;$R53&amp;$S53&amp;$T53&amp;$U53&amp;$V53&amp;$W53&amp;$X53&amp;$Y53&amp;$Z53&amp;$AA53&amp;$AB53&amp;$AC53&amp;$AD53&amp;$AE53&amp;$AF53&amp;$AG53&amp;$AH53&amp;$AI53&amp;$AJ53&amp;$AK53))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M53"/>
+      </x:c>
+      <x:c r="M53" s="67"/>
       <x:c r="N53"/>
       <x:c r="O53"/>
       <x:c r="P53"/>
@@ -7765,12 +7429,8 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
-      <x:c r="A54" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B54" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A54" s="11"/>
+      <x:c r="B54" s="11"/>
       <x:c r="C54" s="12" t="str">
         <x:f>IF($A54="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A54="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7786,9 +7446,7 @@
       <x:c r="G54" s="11" t="str">
         <x:f>IF($A54="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H54" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H54" s="11"/>
       <x:c r="I54" s="11" t="str">
         <x:f>IF($A54="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7800,9 +7458,8 @@
       </x:c>
       <x:c r="L54" s="13" t="str">
         <x:f>IF(TRIM($A54)="","",IF(COUNTIF($Q54:$AK54,"?*")=0,"OK","Falta revisar: "&amp;$Q54&amp;$R54&amp;$S54&amp;$T54&amp;$U54&amp;$V54&amp;$W54&amp;$X54&amp;$Y54&amp;$Z54&amp;$AA54&amp;$AB54&amp;$AC54&amp;$AD54&amp;$AE54&amp;$AF54&amp;$AG54&amp;$AH54&amp;$AI54&amp;$AJ54&amp;$AK54))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M54"/>
+      </x:c>
+      <x:c r="M54" s="67"/>
       <x:c r="N54"/>
       <x:c r="O54"/>
       <x:c r="P54"/>
@@ -7883,12 +7540,8 @@
       </x:c>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
-      <x:c r="A55" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B55" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A55" s="11"/>
+      <x:c r="B55" s="11"/>
       <x:c r="C55" s="12" t="str">
         <x:f>IF($A55="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A55="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -7904,9 +7557,7 @@
       <x:c r="G55" s="11" t="str">
         <x:f>IF($A55="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H55" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H55" s="11"/>
       <x:c r="I55" s="11" t="str">
         <x:f>IF($A55="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -7918,9 +7569,8 @@
       </x:c>
       <x:c r="L55" s="13" t="str">
         <x:f>IF(TRIM($A55)="","",IF(COUNTIF($Q55:$AK55,"?*")=0,"OK","Falta revisar: "&amp;$Q55&amp;$R55&amp;$S55&amp;$T55&amp;$U55&amp;$V55&amp;$W55&amp;$X55&amp;$Y55&amp;$Z55&amp;$AA55&amp;$AB55&amp;$AC55&amp;$AD55&amp;$AE55&amp;$AF55&amp;$AG55&amp;$AH55&amp;$AI55&amp;$AJ55&amp;$AK55))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M55"/>
+      </x:c>
+      <x:c r="M55" s="67"/>
       <x:c r="N55"/>
       <x:c r="O55"/>
       <x:c r="P55"/>
@@ -8001,12 +7651,8 @@
       </x:c>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
-      <x:c r="A56" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B56" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A56" s="11"/>
+      <x:c r="B56" s="11"/>
       <x:c r="C56" s="12" t="str">
         <x:f>IF($A56="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A56="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8022,9 +7668,7 @@
       <x:c r="G56" s="11" t="str">
         <x:f>IF($A56="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H56" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H56" s="11"/>
       <x:c r="I56" s="11" t="str">
         <x:f>IF($A56="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8036,9 +7680,8 @@
       </x:c>
       <x:c r="L56" s="13" t="str">
         <x:f>IF(TRIM($A56)="","",IF(COUNTIF($Q56:$AK56,"?*")=0,"OK","Falta revisar: "&amp;$Q56&amp;$R56&amp;$S56&amp;$T56&amp;$U56&amp;$V56&amp;$W56&amp;$X56&amp;$Y56&amp;$Z56&amp;$AA56&amp;$AB56&amp;$AC56&amp;$AD56&amp;$AE56&amp;$AF56&amp;$AG56&amp;$AH56&amp;$AI56&amp;$AJ56&amp;$AK56))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M56"/>
+      </x:c>
+      <x:c r="M56" s="67"/>
       <x:c r="N56"/>
       <x:c r="O56"/>
       <x:c r="P56"/>
@@ -8119,12 +7762,8 @@
       </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
-      <x:c r="A57" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B57" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A57" s="11"/>
+      <x:c r="B57" s="11"/>
       <x:c r="C57" s="12" t="str">
         <x:f>IF($A57="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A57="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8140,9 +7779,7 @@
       <x:c r="G57" s="11" t="str">
         <x:f>IF($A57="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H57" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H57" s="11"/>
       <x:c r="I57" s="11" t="str">
         <x:f>IF($A57="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8154,9 +7791,8 @@
       </x:c>
       <x:c r="L57" s="13" t="str">
         <x:f>IF(TRIM($A57)="","",IF(COUNTIF($Q57:$AK57,"?*")=0,"OK","Falta revisar: "&amp;$Q57&amp;$R57&amp;$S57&amp;$T57&amp;$U57&amp;$V57&amp;$W57&amp;$X57&amp;$Y57&amp;$Z57&amp;$AA57&amp;$AB57&amp;$AC57&amp;$AD57&amp;$AE57&amp;$AF57&amp;$AG57&amp;$AH57&amp;$AI57&amp;$AJ57&amp;$AK57))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M57"/>
+      </x:c>
+      <x:c r="M57" s="67"/>
       <x:c r="N57"/>
       <x:c r="O57"/>
       <x:c r="P57"/>
@@ -8237,12 +7873,8 @@
       </x:c>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B58" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A58" s="11"/>
+      <x:c r="B58" s="11"/>
       <x:c r="C58" s="12" t="str">
         <x:f>IF($A58="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A58="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8258,9 +7890,7 @@
       <x:c r="G58" s="11" t="str">
         <x:f>IF($A58="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H58" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H58" s="11"/>
       <x:c r="I58" s="11" t="str">
         <x:f>IF($A58="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8272,9 +7902,8 @@
       </x:c>
       <x:c r="L58" s="13" t="str">
         <x:f>IF(TRIM($A58)="","",IF(COUNTIF($Q58:$AK58,"?*")=0,"OK","Falta revisar: "&amp;$Q58&amp;$R58&amp;$S58&amp;$T58&amp;$U58&amp;$V58&amp;$W58&amp;$X58&amp;$Y58&amp;$Z58&amp;$AA58&amp;$AB58&amp;$AC58&amp;$AD58&amp;$AE58&amp;$AF58&amp;$AG58&amp;$AH58&amp;$AI58&amp;$AJ58&amp;$AK58))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M58"/>
+      </x:c>
+      <x:c r="M58" s="67"/>
       <x:c r="N58"/>
       <x:c r="O58"/>
       <x:c r="P58"/>
@@ -8355,12 +7984,8 @@
       </x:c>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
-      <x:c r="A59" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B59" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A59" s="11"/>
+      <x:c r="B59" s="11"/>
       <x:c r="C59" s="12" t="str">
         <x:f>IF($A59="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A59="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8376,9 +8001,7 @@
       <x:c r="G59" s="11" t="str">
         <x:f>IF($A59="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H59" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H59" s="11"/>
       <x:c r="I59" s="11" t="str">
         <x:f>IF($A59="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8390,9 +8013,8 @@
       </x:c>
       <x:c r="L59" s="13" t="str">
         <x:f>IF(TRIM($A59)="","",IF(COUNTIF($Q59:$AK59,"?*")=0,"OK","Falta revisar: "&amp;$Q59&amp;$R59&amp;$S59&amp;$T59&amp;$U59&amp;$V59&amp;$W59&amp;$X59&amp;$Y59&amp;$Z59&amp;$AA59&amp;$AB59&amp;$AC59&amp;$AD59&amp;$AE59&amp;$AF59&amp;$AG59&amp;$AH59&amp;$AI59&amp;$AJ59&amp;$AK59))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M59"/>
+      </x:c>
+      <x:c r="M59" s="67"/>
       <x:c r="N59"/>
       <x:c r="O59"/>
       <x:c r="P59"/>
@@ -8473,12 +8095,8 @@
       </x:c>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B60" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A60" s="11"/>
+      <x:c r="B60" s="11"/>
       <x:c r="C60" s="12" t="str">
         <x:f>IF($A60="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A60="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8494,9 +8112,7 @@
       <x:c r="G60" s="11" t="str">
         <x:f>IF($A60="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H60" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H60" s="11"/>
       <x:c r="I60" s="11" t="str">
         <x:f>IF($A60="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8508,9 +8124,8 @@
       </x:c>
       <x:c r="L60" s="13" t="str">
         <x:f>IF(TRIM($A60)="","",IF(COUNTIF($Q60:$AK60,"?*")=0,"OK","Falta revisar: "&amp;$Q60&amp;$R60&amp;$S60&amp;$T60&amp;$U60&amp;$V60&amp;$W60&amp;$X60&amp;$Y60&amp;$Z60&amp;$AA60&amp;$AB60&amp;$AC60&amp;$AD60&amp;$AE60&amp;$AF60&amp;$AG60&amp;$AH60&amp;$AI60&amp;$AJ60&amp;$AK60))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M60"/>
+      </x:c>
+      <x:c r="M60" s="67"/>
       <x:c r="N60"/>
       <x:c r="O60"/>
       <x:c r="P60"/>
@@ -8591,12 +8206,8 @@
       </x:c>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
-      <x:c r="A61" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B61" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A61" s="11"/>
+      <x:c r="B61" s="11"/>
       <x:c r="C61" s="12" t="str">
         <x:f>IF($A61="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A61="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8612,9 +8223,7 @@
       <x:c r="G61" s="11" t="str">
         <x:f>IF($A61="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H61" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H61" s="11"/>
       <x:c r="I61" s="11" t="str">
         <x:f>IF($A61="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8626,9 +8235,8 @@
       </x:c>
       <x:c r="L61" s="13" t="str">
         <x:f>IF(TRIM($A61)="","",IF(COUNTIF($Q61:$AK61,"?*")=0,"OK","Falta revisar: "&amp;$Q61&amp;$R61&amp;$S61&amp;$T61&amp;$U61&amp;$V61&amp;$W61&amp;$X61&amp;$Y61&amp;$Z61&amp;$AA61&amp;$AB61&amp;$AC61&amp;$AD61&amp;$AE61&amp;$AF61&amp;$AG61&amp;$AH61&amp;$AI61&amp;$AJ61&amp;$AK61))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M61"/>
+      </x:c>
+      <x:c r="M61" s="67"/>
       <x:c r="N61"/>
       <x:c r="O61"/>
       <x:c r="P61"/>
@@ -8709,12 +8317,8 @@
       </x:c>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
-      <x:c r="A62" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B62" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A62" s="11"/>
+      <x:c r="B62" s="11"/>
       <x:c r="C62" s="12" t="str">
         <x:f>IF($A62="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A62="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8730,9 +8334,7 @@
       <x:c r="G62" s="11" t="str">
         <x:f>IF($A62="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H62" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H62" s="11"/>
       <x:c r="I62" s="11" t="str">
         <x:f>IF($A62="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8744,9 +8346,8 @@
       </x:c>
       <x:c r="L62" s="13" t="str">
         <x:f>IF(TRIM($A62)="","",IF(COUNTIF($Q62:$AK62,"?*")=0,"OK","Falta revisar: "&amp;$Q62&amp;$R62&amp;$S62&amp;$T62&amp;$U62&amp;$V62&amp;$W62&amp;$X62&amp;$Y62&amp;$Z62&amp;$AA62&amp;$AB62&amp;$AC62&amp;$AD62&amp;$AE62&amp;$AF62&amp;$AG62&amp;$AH62&amp;$AI62&amp;$AJ62&amp;$AK62))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M62"/>
+      </x:c>
+      <x:c r="M62" s="67"/>
       <x:c r="N62"/>
       <x:c r="O62"/>
       <x:c r="P62"/>
@@ -8827,12 +8428,8 @@
       </x:c>
     </x:row>
     <x:row r="63" ht="24" customHeight="1">
-      <x:c r="A63" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B63" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A63" s="11"/>
+      <x:c r="B63" s="11"/>
       <x:c r="C63" s="12" t="str">
         <x:f>IF($A63="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A63="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8848,9 +8445,7 @@
       <x:c r="G63" s="11" t="str">
         <x:f>IF($A63="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H63" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H63" s="11"/>
       <x:c r="I63" s="11" t="str">
         <x:f>IF($A63="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8862,9 +8457,8 @@
       </x:c>
       <x:c r="L63" s="13" t="str">
         <x:f>IF(TRIM($A63)="","",IF(COUNTIF($Q63:$AK63,"?*")=0,"OK","Falta revisar: "&amp;$Q63&amp;$R63&amp;$S63&amp;$T63&amp;$U63&amp;$V63&amp;$W63&amp;$X63&amp;$Y63&amp;$Z63&amp;$AA63&amp;$AB63&amp;$AC63&amp;$AD63&amp;$AE63&amp;$AF63&amp;$AG63&amp;$AH63&amp;$AI63&amp;$AJ63&amp;$AK63))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M63"/>
+      </x:c>
+      <x:c r="M63" s="67"/>
       <x:c r="N63"/>
       <x:c r="O63"/>
       <x:c r="P63"/>
@@ -8945,12 +8539,8 @@
       </x:c>
     </x:row>
     <x:row r="64" ht="24" customHeight="1">
-      <x:c r="A64" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B64" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A64" s="11"/>
+      <x:c r="B64" s="11"/>
       <x:c r="C64" s="12" t="str">
         <x:f>IF($A64="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A64="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -8966,9 +8556,7 @@
       <x:c r="G64" s="11" t="str">
         <x:f>IF($A64="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H64" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H64" s="11"/>
       <x:c r="I64" s="11" t="str">
         <x:f>IF($A64="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -8980,9 +8568,8 @@
       </x:c>
       <x:c r="L64" s="13" t="str">
         <x:f>IF(TRIM($A64)="","",IF(COUNTIF($Q64:$AK64,"?*")=0,"OK","Falta revisar: "&amp;$Q64&amp;$R64&amp;$S64&amp;$T64&amp;$U64&amp;$V64&amp;$W64&amp;$X64&amp;$Y64&amp;$Z64&amp;$AA64&amp;$AB64&amp;$AC64&amp;$AD64&amp;$AE64&amp;$AF64&amp;$AG64&amp;$AH64&amp;$AI64&amp;$AJ64&amp;$AK64))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M64"/>
+      </x:c>
+      <x:c r="M64" s="67"/>
       <x:c r="N64"/>
       <x:c r="O64"/>
       <x:c r="P64"/>
@@ -9063,12 +8650,8 @@
       </x:c>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
-      <x:c r="A65" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B65" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A65" s="11"/>
+      <x:c r="B65" s="11"/>
       <x:c r="C65" s="12" t="str">
         <x:f>IF($A65="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A65="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9084,9 +8667,7 @@
       <x:c r="G65" s="11" t="str">
         <x:f>IF($A65="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H65" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H65" s="11"/>
       <x:c r="I65" s="11" t="str">
         <x:f>IF($A65="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9098,9 +8679,8 @@
       </x:c>
       <x:c r="L65" s="13" t="str">
         <x:f>IF(TRIM($A65)="","",IF(COUNTIF($Q65:$AK65,"?*")=0,"OK","Falta revisar: "&amp;$Q65&amp;$R65&amp;$S65&amp;$T65&amp;$U65&amp;$V65&amp;$W65&amp;$X65&amp;$Y65&amp;$Z65&amp;$AA65&amp;$AB65&amp;$AC65&amp;$AD65&amp;$AE65&amp;$AF65&amp;$AG65&amp;$AH65&amp;$AI65&amp;$AJ65&amp;$AK65))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M65"/>
+      </x:c>
+      <x:c r="M65" s="67"/>
       <x:c r="N65"/>
       <x:c r="O65"/>
       <x:c r="P65"/>
@@ -9181,12 +8761,8 @@
       </x:c>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
-      <x:c r="A66" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B66" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A66" s="11"/>
+      <x:c r="B66" s="11"/>
       <x:c r="C66" s="12" t="str">
         <x:f>IF($A66="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A66="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9202,9 +8778,7 @@
       <x:c r="G66" s="11" t="str">
         <x:f>IF($A66="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H66" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H66" s="11"/>
       <x:c r="I66" s="11" t="str">
         <x:f>IF($A66="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9216,9 +8790,8 @@
       </x:c>
       <x:c r="L66" s="13" t="str">
         <x:f>IF(TRIM($A66)="","",IF(COUNTIF($Q66:$AK66,"?*")=0,"OK","Falta revisar: "&amp;$Q66&amp;$R66&amp;$S66&amp;$T66&amp;$U66&amp;$V66&amp;$W66&amp;$X66&amp;$Y66&amp;$Z66&amp;$AA66&amp;$AB66&amp;$AC66&amp;$AD66&amp;$AE66&amp;$AF66&amp;$AG66&amp;$AH66&amp;$AI66&amp;$AJ66&amp;$AK66))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M66"/>
+      </x:c>
+      <x:c r="M66" s="67"/>
       <x:c r="N66"/>
       <x:c r="O66"/>
       <x:c r="P66"/>
@@ -9299,12 +8872,8 @@
       </x:c>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
-      <x:c r="A67" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B67" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A67" s="11"/>
+      <x:c r="B67" s="11"/>
       <x:c r="C67" s="12" t="str">
         <x:f>IF($A67="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A67="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9320,9 +8889,7 @@
       <x:c r="G67" s="11" t="str">
         <x:f>IF($A67="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H67" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H67" s="11"/>
       <x:c r="I67" s="11" t="str">
         <x:f>IF($A67="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9334,9 +8901,8 @@
       </x:c>
       <x:c r="L67" s="13" t="str">
         <x:f>IF(TRIM($A67)="","",IF(COUNTIF($Q67:$AK67,"?*")=0,"OK","Falta revisar: "&amp;$Q67&amp;$R67&amp;$S67&amp;$T67&amp;$U67&amp;$V67&amp;$W67&amp;$X67&amp;$Y67&amp;$Z67&amp;$AA67&amp;$AB67&amp;$AC67&amp;$AD67&amp;$AE67&amp;$AF67&amp;$AG67&amp;$AH67&amp;$AI67&amp;$AJ67&amp;$AK67))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M67"/>
+      </x:c>
+      <x:c r="M67" s="67"/>
       <x:c r="N67"/>
       <x:c r="O67"/>
       <x:c r="P67"/>
@@ -9417,12 +8983,8 @@
       </x:c>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
-      <x:c r="A68" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B68" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A68" s="11"/>
+      <x:c r="B68" s="11"/>
       <x:c r="C68" s="12" t="str">
         <x:f>IF($A68="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A68="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9438,9 +9000,7 @@
       <x:c r="G68" s="11" t="str">
         <x:f>IF($A68="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H68" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H68" s="11"/>
       <x:c r="I68" s="11" t="str">
         <x:f>IF($A68="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9452,9 +9012,8 @@
       </x:c>
       <x:c r="L68" s="13" t="str">
         <x:f>IF(TRIM($A68)="","",IF(COUNTIF($Q68:$AK68,"?*")=0,"OK","Falta revisar: "&amp;$Q68&amp;$R68&amp;$S68&amp;$T68&amp;$U68&amp;$V68&amp;$W68&amp;$X68&amp;$Y68&amp;$Z68&amp;$AA68&amp;$AB68&amp;$AC68&amp;$AD68&amp;$AE68&amp;$AF68&amp;$AG68&amp;$AH68&amp;$AI68&amp;$AJ68&amp;$AK68))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M68"/>
+      </x:c>
+      <x:c r="M68" s="67"/>
       <x:c r="N68"/>
       <x:c r="O68"/>
       <x:c r="P68"/>
@@ -9535,12 +9094,8 @@
       </x:c>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
-      <x:c r="A69" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B69" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A69" s="11"/>
+      <x:c r="B69" s="11"/>
       <x:c r="C69" s="12" t="str">
         <x:f>IF($A69="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A69="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9556,9 +9111,7 @@
       <x:c r="G69" s="11" t="str">
         <x:f>IF($A69="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H69" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H69" s="11"/>
       <x:c r="I69" s="11" t="str">
         <x:f>IF($A69="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9570,9 +9123,8 @@
       </x:c>
       <x:c r="L69" s="13" t="str">
         <x:f>IF(TRIM($A69)="","",IF(COUNTIF($Q69:$AK69,"?*")=0,"OK","Falta revisar: "&amp;$Q69&amp;$R69&amp;$S69&amp;$T69&amp;$U69&amp;$V69&amp;$W69&amp;$X69&amp;$Y69&amp;$Z69&amp;$AA69&amp;$AB69&amp;$AC69&amp;$AD69&amp;$AE69&amp;$AF69&amp;$AG69&amp;$AH69&amp;$AI69&amp;$AJ69&amp;$AK69))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M69"/>
+      </x:c>
+      <x:c r="M69" s="67"/>
       <x:c r="N69"/>
       <x:c r="O69"/>
       <x:c r="P69"/>
@@ -9653,12 +9205,8 @@
       </x:c>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
-      <x:c r="A70" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B70" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A70" s="11"/>
+      <x:c r="B70" s="11"/>
       <x:c r="C70" s="12" t="str">
         <x:f>IF($A70="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A70="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9674,9 +9222,7 @@
       <x:c r="G70" s="11" t="str">
         <x:f>IF($A70="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H70" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H70" s="11"/>
       <x:c r="I70" s="11" t="str">
         <x:f>IF($A70="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9688,9 +9234,8 @@
       </x:c>
       <x:c r="L70" s="13" t="str">
         <x:f>IF(TRIM($A70)="","",IF(COUNTIF($Q70:$AK70,"?*")=0,"OK","Falta revisar: "&amp;$Q70&amp;$R70&amp;$S70&amp;$T70&amp;$U70&amp;$V70&amp;$W70&amp;$X70&amp;$Y70&amp;$Z70&amp;$AA70&amp;$AB70&amp;$AC70&amp;$AD70&amp;$AE70&amp;$AF70&amp;$AG70&amp;$AH70&amp;$AI70&amp;$AJ70&amp;$AK70))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M70"/>
+      </x:c>
+      <x:c r="M70" s="67"/>
       <x:c r="N70"/>
       <x:c r="O70"/>
       <x:c r="P70"/>
@@ -9771,12 +9316,8 @@
       </x:c>
     </x:row>
     <x:row r="71" ht="24" customHeight="1">
-      <x:c r="A71" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B71" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A71" s="11"/>
+      <x:c r="B71" s="11"/>
       <x:c r="C71" s="12" t="str">
         <x:f>IF($A71="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A71="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9792,9 +9333,7 @@
       <x:c r="G71" s="11" t="str">
         <x:f>IF($A71="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H71" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H71" s="11"/>
       <x:c r="I71" s="11" t="str">
         <x:f>IF($A71="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9806,9 +9345,8 @@
       </x:c>
       <x:c r="L71" s="13" t="str">
         <x:f>IF(TRIM($A71)="","",IF(COUNTIF($Q71:$AK71,"?*")=0,"OK","Falta revisar: "&amp;$Q71&amp;$R71&amp;$S71&amp;$T71&amp;$U71&amp;$V71&amp;$W71&amp;$X71&amp;$Y71&amp;$Z71&amp;$AA71&amp;$AB71&amp;$AC71&amp;$AD71&amp;$AE71&amp;$AF71&amp;$AG71&amp;$AH71&amp;$AI71&amp;$AJ71&amp;$AK71))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M71"/>
+      </x:c>
+      <x:c r="M71" s="67"/>
       <x:c r="N71"/>
       <x:c r="O71"/>
       <x:c r="P71"/>
@@ -9889,12 +9427,8 @@
       </x:c>
     </x:row>
     <x:row r="72" ht="24" customHeight="1">
-      <x:c r="A72" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B72" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A72" s="11"/>
+      <x:c r="B72" s="11"/>
       <x:c r="C72" s="12" t="str">
         <x:f>IF($A72="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A72="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -9910,9 +9444,7 @@
       <x:c r="G72" s="11" t="str">
         <x:f>IF($A72="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H72" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H72" s="11"/>
       <x:c r="I72" s="11" t="str">
         <x:f>IF($A72="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -9924,9 +9456,8 @@
       </x:c>
       <x:c r="L72" s="13" t="str">
         <x:f>IF(TRIM($A72)="","",IF(COUNTIF($Q72:$AK72,"?*")=0,"OK","Falta revisar: "&amp;$Q72&amp;$R72&amp;$S72&amp;$T72&amp;$U72&amp;$V72&amp;$W72&amp;$X72&amp;$Y72&amp;$Z72&amp;$AA72&amp;$AB72&amp;$AC72&amp;$AD72&amp;$AE72&amp;$AF72&amp;$AG72&amp;$AH72&amp;$AI72&amp;$AJ72&amp;$AK72))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M72"/>
+      </x:c>
+      <x:c r="M72" s="67"/>
       <x:c r="N72"/>
       <x:c r="O72"/>
       <x:c r="P72"/>
@@ -10007,12 +9538,8 @@
       </x:c>
     </x:row>
     <x:row r="73" ht="24" customHeight="1">
-      <x:c r="A73" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B73" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A73" s="11"/>
+      <x:c r="B73" s="11"/>
       <x:c r="C73" s="12" t="str">
         <x:f>IF($A73="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A73="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10028,9 +9555,7 @@
       <x:c r="G73" s="11" t="str">
         <x:f>IF($A73="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H73" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H73" s="11"/>
       <x:c r="I73" s="11" t="str">
         <x:f>IF($A73="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10042,9 +9567,8 @@
       </x:c>
       <x:c r="L73" s="13" t="str">
         <x:f>IF(TRIM($A73)="","",IF(COUNTIF($Q73:$AK73,"?*")=0,"OK","Falta revisar: "&amp;$Q73&amp;$R73&amp;$S73&amp;$T73&amp;$U73&amp;$V73&amp;$W73&amp;$X73&amp;$Y73&amp;$Z73&amp;$AA73&amp;$AB73&amp;$AC73&amp;$AD73&amp;$AE73&amp;$AF73&amp;$AG73&amp;$AH73&amp;$AI73&amp;$AJ73&amp;$AK73))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M73"/>
+      </x:c>
+      <x:c r="M73" s="67"/>
       <x:c r="N73"/>
       <x:c r="O73"/>
       <x:c r="P73"/>
@@ -10125,12 +9649,8 @@
       </x:c>
     </x:row>
     <x:row r="74" ht="24" customHeight="1">
-      <x:c r="A74" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B74" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A74" s="11"/>
+      <x:c r="B74" s="11"/>
       <x:c r="C74" s="12" t="str">
         <x:f>IF($A74="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A74="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10146,9 +9666,7 @@
       <x:c r="G74" s="11" t="str">
         <x:f>IF($A74="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H74" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H74" s="11"/>
       <x:c r="I74" s="11" t="str">
         <x:f>IF($A74="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10160,9 +9678,8 @@
       </x:c>
       <x:c r="L74" s="13" t="str">
         <x:f>IF(TRIM($A74)="","",IF(COUNTIF($Q74:$AK74,"?*")=0,"OK","Falta revisar: "&amp;$Q74&amp;$R74&amp;$S74&amp;$T74&amp;$U74&amp;$V74&amp;$W74&amp;$X74&amp;$Y74&amp;$Z74&amp;$AA74&amp;$AB74&amp;$AC74&amp;$AD74&amp;$AE74&amp;$AF74&amp;$AG74&amp;$AH74&amp;$AI74&amp;$AJ74&amp;$AK74))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M74"/>
+      </x:c>
+      <x:c r="M74" s="67"/>
       <x:c r="N74"/>
       <x:c r="O74"/>
       <x:c r="P74"/>
@@ -10243,12 +9760,8 @@
       </x:c>
     </x:row>
     <x:row r="75" ht="24" customHeight="1">
-      <x:c r="A75" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B75" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A75" s="11"/>
+      <x:c r="B75" s="11"/>
       <x:c r="C75" s="12" t="str">
         <x:f>IF($A75="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A75="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10264,9 +9777,7 @@
       <x:c r="G75" s="11" t="str">
         <x:f>IF($A75="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H75" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H75" s="11"/>
       <x:c r="I75" s="11" t="str">
         <x:f>IF($A75="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10278,9 +9789,8 @@
       </x:c>
       <x:c r="L75" s="13" t="str">
         <x:f>IF(TRIM($A75)="","",IF(COUNTIF($Q75:$AK75,"?*")=0,"OK","Falta revisar: "&amp;$Q75&amp;$R75&amp;$S75&amp;$T75&amp;$U75&amp;$V75&amp;$W75&amp;$X75&amp;$Y75&amp;$Z75&amp;$AA75&amp;$AB75&amp;$AC75&amp;$AD75&amp;$AE75&amp;$AF75&amp;$AG75&amp;$AH75&amp;$AI75&amp;$AJ75&amp;$AK75))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M75"/>
+      </x:c>
+      <x:c r="M75" s="67"/>
       <x:c r="N75"/>
       <x:c r="O75"/>
       <x:c r="P75"/>
@@ -10361,12 +9871,8 @@
       </x:c>
     </x:row>
     <x:row r="76" ht="24" customHeight="1">
-      <x:c r="A76" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B76" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A76" s="11"/>
+      <x:c r="B76" s="11"/>
       <x:c r="C76" s="12" t="str">
         <x:f>IF($A76="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A76="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10382,9 +9888,7 @@
       <x:c r="G76" s="11" t="str">
         <x:f>IF($A76="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H76" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H76" s="11"/>
       <x:c r="I76" s="11" t="str">
         <x:f>IF($A76="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10396,9 +9900,8 @@
       </x:c>
       <x:c r="L76" s="13" t="str">
         <x:f>IF(TRIM($A76)="","",IF(COUNTIF($Q76:$AK76,"?*")=0,"OK","Falta revisar: "&amp;$Q76&amp;$R76&amp;$S76&amp;$T76&amp;$U76&amp;$V76&amp;$W76&amp;$X76&amp;$Y76&amp;$Z76&amp;$AA76&amp;$AB76&amp;$AC76&amp;$AD76&amp;$AE76&amp;$AF76&amp;$AG76&amp;$AH76&amp;$AI76&amp;$AJ76&amp;$AK76))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M76"/>
+      </x:c>
+      <x:c r="M76" s="67"/>
       <x:c r="N76"/>
       <x:c r="O76"/>
       <x:c r="P76"/>
@@ -10479,12 +9982,8 @@
       </x:c>
     </x:row>
     <x:row r="77" ht="24" customHeight="1">
-      <x:c r="A77" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B77" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A77" s="11"/>
+      <x:c r="B77" s="11"/>
       <x:c r="C77" s="12" t="str">
         <x:f>IF($A77="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A77="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10500,9 +9999,7 @@
       <x:c r="G77" s="11" t="str">
         <x:f>IF($A77="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H77" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H77" s="11"/>
       <x:c r="I77" s="11" t="str">
         <x:f>IF($A77="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10514,9 +10011,8 @@
       </x:c>
       <x:c r="L77" s="13" t="str">
         <x:f>IF(TRIM($A77)="","",IF(COUNTIF($Q77:$AK77,"?*")=0,"OK","Falta revisar: "&amp;$Q77&amp;$R77&amp;$S77&amp;$T77&amp;$U77&amp;$V77&amp;$W77&amp;$X77&amp;$Y77&amp;$Z77&amp;$AA77&amp;$AB77&amp;$AC77&amp;$AD77&amp;$AE77&amp;$AF77&amp;$AG77&amp;$AH77&amp;$AI77&amp;$AJ77&amp;$AK77))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M77"/>
+      </x:c>
+      <x:c r="M77" s="67"/>
       <x:c r="N77"/>
       <x:c r="O77"/>
       <x:c r="P77"/>
@@ -10597,12 +10093,8 @@
       </x:c>
     </x:row>
     <x:row r="78" ht="24" customHeight="1">
-      <x:c r="A78" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B78" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A78" s="11"/>
+      <x:c r="B78" s="11"/>
       <x:c r="C78" s="12" t="str">
         <x:f>IF($A78="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A78="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10618,9 +10110,7 @@
       <x:c r="G78" s="11" t="str">
         <x:f>IF($A78="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H78" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H78" s="11"/>
       <x:c r="I78" s="11" t="str">
         <x:f>IF($A78="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10632,9 +10122,8 @@
       </x:c>
       <x:c r="L78" s="13" t="str">
         <x:f>IF(TRIM($A78)="","",IF(COUNTIF($Q78:$AK78,"?*")=0,"OK","Falta revisar: "&amp;$Q78&amp;$R78&amp;$S78&amp;$T78&amp;$U78&amp;$V78&amp;$W78&amp;$X78&amp;$Y78&amp;$Z78&amp;$AA78&amp;$AB78&amp;$AC78&amp;$AD78&amp;$AE78&amp;$AF78&amp;$AG78&amp;$AH78&amp;$AI78&amp;$AJ78&amp;$AK78))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M78"/>
+      </x:c>
+      <x:c r="M78" s="67"/>
       <x:c r="N78"/>
       <x:c r="O78"/>
       <x:c r="P78"/>
@@ -10715,12 +10204,8 @@
       </x:c>
     </x:row>
     <x:row r="79" ht="24" customHeight="1">
-      <x:c r="A79" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B79" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A79" s="11"/>
+      <x:c r="B79" s="11"/>
       <x:c r="C79" s="12" t="str">
         <x:f>IF($A79="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A79="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10736,9 +10221,7 @@
       <x:c r="G79" s="11" t="str">
         <x:f>IF($A79="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H79" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H79" s="11"/>
       <x:c r="I79" s="11" t="str">
         <x:f>IF($A79="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10750,9 +10233,8 @@
       </x:c>
       <x:c r="L79" s="13" t="str">
         <x:f>IF(TRIM($A79)="","",IF(COUNTIF($Q79:$AK79,"?*")=0,"OK","Falta revisar: "&amp;$Q79&amp;$R79&amp;$S79&amp;$T79&amp;$U79&amp;$V79&amp;$W79&amp;$X79&amp;$Y79&amp;$Z79&amp;$AA79&amp;$AB79&amp;$AC79&amp;$AD79&amp;$AE79&amp;$AF79&amp;$AG79&amp;$AH79&amp;$AI79&amp;$AJ79&amp;$AK79))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M79"/>
+      </x:c>
+      <x:c r="M79" s="67"/>
       <x:c r="N79"/>
       <x:c r="O79"/>
       <x:c r="P79"/>
@@ -10833,12 +10315,8 @@
       </x:c>
     </x:row>
     <x:row r="80" ht="24" customHeight="1">
-      <x:c r="A80" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B80" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A80" s="11"/>
+      <x:c r="B80" s="11"/>
       <x:c r="C80" s="12" t="str">
         <x:f>IF($A80="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A80="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10854,9 +10332,7 @@
       <x:c r="G80" s="11" t="str">
         <x:f>IF($A80="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H80" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H80" s="11"/>
       <x:c r="I80" s="11" t="str">
         <x:f>IF($A80="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10868,9 +10344,8 @@
       </x:c>
       <x:c r="L80" s="13" t="str">
         <x:f>IF(TRIM($A80)="","",IF(COUNTIF($Q80:$AK80,"?*")=0,"OK","Falta revisar: "&amp;$Q80&amp;$R80&amp;$S80&amp;$T80&amp;$U80&amp;$V80&amp;$W80&amp;$X80&amp;$Y80&amp;$Z80&amp;$AA80&amp;$AB80&amp;$AC80&amp;$AD80&amp;$AE80&amp;$AF80&amp;$AG80&amp;$AH80&amp;$AI80&amp;$AJ80&amp;$AK80))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M80"/>
+      </x:c>
+      <x:c r="M80" s="67"/>
       <x:c r="N80"/>
       <x:c r="O80"/>
       <x:c r="P80"/>
@@ -10951,12 +10426,8 @@
       </x:c>
     </x:row>
     <x:row r="81" ht="24" customHeight="1">
-      <x:c r="A81" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B81" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A81" s="11"/>
+      <x:c r="B81" s="11"/>
       <x:c r="C81" s="12" t="str">
         <x:f>IF($A81="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A81="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -10972,9 +10443,7 @@
       <x:c r="G81" s="11" t="str">
         <x:f>IF($A81="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H81" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H81" s="11"/>
       <x:c r="I81" s="11" t="str">
         <x:f>IF($A81="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -10986,9 +10455,8 @@
       </x:c>
       <x:c r="L81" s="13" t="str">
         <x:f>IF(TRIM($A81)="","",IF(COUNTIF($Q81:$AK81,"?*")=0,"OK","Falta revisar: "&amp;$Q81&amp;$R81&amp;$S81&amp;$T81&amp;$U81&amp;$V81&amp;$W81&amp;$X81&amp;$Y81&amp;$Z81&amp;$AA81&amp;$AB81&amp;$AC81&amp;$AD81&amp;$AE81&amp;$AF81&amp;$AG81&amp;$AH81&amp;$AI81&amp;$AJ81&amp;$AK81))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M81"/>
+      </x:c>
+      <x:c r="M81" s="67"/>
       <x:c r="N81"/>
       <x:c r="O81"/>
       <x:c r="P81"/>
@@ -11069,12 +10537,8 @@
       </x:c>
     </x:row>
     <x:row r="82" ht="24" customHeight="1">
-      <x:c r="A82" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B82" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A82" s="11"/>
+      <x:c r="B82" s="11"/>
       <x:c r="C82" s="12" t="str">
         <x:f>IF($A82="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A82="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11090,9 +10554,7 @@
       <x:c r="G82" s="11" t="str">
         <x:f>IF($A82="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H82" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H82" s="11"/>
       <x:c r="I82" s="11" t="str">
         <x:f>IF($A82="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11104,9 +10566,8 @@
       </x:c>
       <x:c r="L82" s="13" t="str">
         <x:f>IF(TRIM($A82)="","",IF(COUNTIF($Q82:$AK82,"?*")=0,"OK","Falta revisar: "&amp;$Q82&amp;$R82&amp;$S82&amp;$T82&amp;$U82&amp;$V82&amp;$W82&amp;$X82&amp;$Y82&amp;$Z82&amp;$AA82&amp;$AB82&amp;$AC82&amp;$AD82&amp;$AE82&amp;$AF82&amp;$AG82&amp;$AH82&amp;$AI82&amp;$AJ82&amp;$AK82))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M82"/>
+      </x:c>
+      <x:c r="M82" s="67"/>
       <x:c r="N82"/>
       <x:c r="O82"/>
       <x:c r="P82"/>
@@ -11187,12 +10648,8 @@
       </x:c>
     </x:row>
     <x:row r="83" ht="24" customHeight="1">
-      <x:c r="A83" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B83" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A83" s="11"/>
+      <x:c r="B83" s="11"/>
       <x:c r="C83" s="12" t="str">
         <x:f>IF($A83="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A83="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11208,9 +10665,7 @@
       <x:c r="G83" s="11" t="str">
         <x:f>IF($A83="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H83" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H83" s="11"/>
       <x:c r="I83" s="11" t="str">
         <x:f>IF($A83="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11222,9 +10677,8 @@
       </x:c>
       <x:c r="L83" s="13" t="str">
         <x:f>IF(TRIM($A83)="","",IF(COUNTIF($Q83:$AK83,"?*")=0,"OK","Falta revisar: "&amp;$Q83&amp;$R83&amp;$S83&amp;$T83&amp;$U83&amp;$V83&amp;$W83&amp;$X83&amp;$Y83&amp;$Z83&amp;$AA83&amp;$AB83&amp;$AC83&amp;$AD83&amp;$AE83&amp;$AF83&amp;$AG83&amp;$AH83&amp;$AI83&amp;$AJ83&amp;$AK83))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M83"/>
+      </x:c>
+      <x:c r="M83" s="67"/>
       <x:c r="N83"/>
       <x:c r="O83"/>
       <x:c r="P83"/>
@@ -11305,12 +10759,8 @@
       </x:c>
     </x:row>
     <x:row r="84" ht="24" customHeight="1">
-      <x:c r="A84" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B84" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A84" s="11"/>
+      <x:c r="B84" s="11"/>
       <x:c r="C84" s="12" t="str">
         <x:f>IF($A84="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A84="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11326,9 +10776,7 @@
       <x:c r="G84" s="11" t="str">
         <x:f>IF($A84="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H84" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H84" s="11"/>
       <x:c r="I84" s="11" t="str">
         <x:f>IF($A84="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11340,9 +10788,8 @@
       </x:c>
       <x:c r="L84" s="13" t="str">
         <x:f>IF(TRIM($A84)="","",IF(COUNTIF($Q84:$AK84,"?*")=0,"OK","Falta revisar: "&amp;$Q84&amp;$R84&amp;$S84&amp;$T84&amp;$U84&amp;$V84&amp;$W84&amp;$X84&amp;$Y84&amp;$Z84&amp;$AA84&amp;$AB84&amp;$AC84&amp;$AD84&amp;$AE84&amp;$AF84&amp;$AG84&amp;$AH84&amp;$AI84&amp;$AJ84&amp;$AK84))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M84"/>
+      </x:c>
+      <x:c r="M84" s="67"/>
       <x:c r="N84"/>
       <x:c r="O84"/>
       <x:c r="P84"/>
@@ -11423,12 +10870,8 @@
       </x:c>
     </x:row>
     <x:row r="85" ht="24" customHeight="1">
-      <x:c r="A85" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B85" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A85" s="11"/>
+      <x:c r="B85" s="11"/>
       <x:c r="C85" s="12" t="str">
         <x:f>IF($A85="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A85="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11444,9 +10887,7 @@
       <x:c r="G85" s="11" t="str">
         <x:f>IF($A85="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H85" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H85" s="11"/>
       <x:c r="I85" s="11" t="str">
         <x:f>IF($A85="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11458,9 +10899,8 @@
       </x:c>
       <x:c r="L85" s="13" t="str">
         <x:f>IF(TRIM($A85)="","",IF(COUNTIF($Q85:$AK85,"?*")=0,"OK","Falta revisar: "&amp;$Q85&amp;$R85&amp;$S85&amp;$T85&amp;$U85&amp;$V85&amp;$W85&amp;$X85&amp;$Y85&amp;$Z85&amp;$AA85&amp;$AB85&amp;$AC85&amp;$AD85&amp;$AE85&amp;$AF85&amp;$AG85&amp;$AH85&amp;$AI85&amp;$AJ85&amp;$AK85))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M85"/>
+      </x:c>
+      <x:c r="M85" s="67"/>
       <x:c r="N85"/>
       <x:c r="O85"/>
       <x:c r="P85"/>
@@ -11541,12 +10981,8 @@
       </x:c>
     </x:row>
     <x:row r="86" ht="24" customHeight="1">
-      <x:c r="A86" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B86" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A86" s="11"/>
+      <x:c r="B86" s="11"/>
       <x:c r="C86" s="12" t="str">
         <x:f>IF($A86="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A86="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11562,9 +10998,7 @@
       <x:c r="G86" s="11" t="str">
         <x:f>IF($A86="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H86" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H86" s="11"/>
       <x:c r="I86" s="11" t="str">
         <x:f>IF($A86="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11576,9 +11010,8 @@
       </x:c>
       <x:c r="L86" s="13" t="str">
         <x:f>IF(TRIM($A86)="","",IF(COUNTIF($Q86:$AK86,"?*")=0,"OK","Falta revisar: "&amp;$Q86&amp;$R86&amp;$S86&amp;$T86&amp;$U86&amp;$V86&amp;$W86&amp;$X86&amp;$Y86&amp;$Z86&amp;$AA86&amp;$AB86&amp;$AC86&amp;$AD86&amp;$AE86&amp;$AF86&amp;$AG86&amp;$AH86&amp;$AI86&amp;$AJ86&amp;$AK86))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M86"/>
+      </x:c>
+      <x:c r="M86" s="67"/>
       <x:c r="N86"/>
       <x:c r="O86"/>
       <x:c r="P86"/>
@@ -11659,12 +11092,8 @@
       </x:c>
     </x:row>
     <x:row r="87" ht="24" customHeight="1">
-      <x:c r="A87" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B87" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A87" s="11"/>
+      <x:c r="B87" s="11"/>
       <x:c r="C87" s="12" t="str">
         <x:f>IF($A87="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A87="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11680,9 +11109,7 @@
       <x:c r="G87" s="11" t="str">
         <x:f>IF($A87="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H87" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H87" s="11"/>
       <x:c r="I87" s="11" t="str">
         <x:f>IF($A87="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11694,9 +11121,8 @@
       </x:c>
       <x:c r="L87" s="13" t="str">
         <x:f>IF(TRIM($A87)="","",IF(COUNTIF($Q87:$AK87,"?*")=0,"OK","Falta revisar: "&amp;$Q87&amp;$R87&amp;$S87&amp;$T87&amp;$U87&amp;$V87&amp;$W87&amp;$X87&amp;$Y87&amp;$Z87&amp;$AA87&amp;$AB87&amp;$AC87&amp;$AD87&amp;$AE87&amp;$AF87&amp;$AG87&amp;$AH87&amp;$AI87&amp;$AJ87&amp;$AK87))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M87"/>
+      </x:c>
+      <x:c r="M87" s="67"/>
       <x:c r="N87"/>
       <x:c r="O87"/>
       <x:c r="P87"/>
@@ -11777,12 +11203,8 @@
       </x:c>
     </x:row>
     <x:row r="88" ht="24" customHeight="1">
-      <x:c r="A88" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B88" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A88" s="11"/>
+      <x:c r="B88" s="11"/>
       <x:c r="C88" s="12" t="str">
         <x:f>IF($A88="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A88="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11798,9 +11220,7 @@
       <x:c r="G88" s="11" t="str">
         <x:f>IF($A88="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H88" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H88" s="11"/>
       <x:c r="I88" s="11" t="str">
         <x:f>IF($A88="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11812,9 +11232,8 @@
       </x:c>
       <x:c r="L88" s="13" t="str">
         <x:f>IF(TRIM($A88)="","",IF(COUNTIF($Q88:$AK88,"?*")=0,"OK","Falta revisar: "&amp;$Q88&amp;$R88&amp;$S88&amp;$T88&amp;$U88&amp;$V88&amp;$W88&amp;$X88&amp;$Y88&amp;$Z88&amp;$AA88&amp;$AB88&amp;$AC88&amp;$AD88&amp;$AE88&amp;$AF88&amp;$AG88&amp;$AH88&amp;$AI88&amp;$AJ88&amp;$AK88))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M88"/>
+      </x:c>
+      <x:c r="M88" s="67"/>
       <x:c r="N88"/>
       <x:c r="O88"/>
       <x:c r="P88"/>
@@ -11895,12 +11314,8 @@
       </x:c>
     </x:row>
     <x:row r="89" ht="24" customHeight="1">
-      <x:c r="A89" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B89" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A89" s="11"/>
+      <x:c r="B89" s="11"/>
       <x:c r="C89" s="12" t="str">
         <x:f>IF($A89="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A89="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -11916,9 +11331,7 @@
       <x:c r="G89" s="11" t="str">
         <x:f>IF($A89="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H89" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H89" s="11"/>
       <x:c r="I89" s="11" t="str">
         <x:f>IF($A89="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -11930,9 +11343,8 @@
       </x:c>
       <x:c r="L89" s="13" t="str">
         <x:f>IF(TRIM($A89)="","",IF(COUNTIF($Q89:$AK89,"?*")=0,"OK","Falta revisar: "&amp;$Q89&amp;$R89&amp;$S89&amp;$T89&amp;$U89&amp;$V89&amp;$W89&amp;$X89&amp;$Y89&amp;$Z89&amp;$AA89&amp;$AB89&amp;$AC89&amp;$AD89&amp;$AE89&amp;$AF89&amp;$AG89&amp;$AH89&amp;$AI89&amp;$AJ89&amp;$AK89))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M89"/>
+      </x:c>
+      <x:c r="M89" s="67"/>
       <x:c r="N89"/>
       <x:c r="O89"/>
       <x:c r="P89"/>
@@ -12013,12 +11425,8 @@
       </x:c>
     </x:row>
     <x:row r="90" ht="24" customHeight="1">
-      <x:c r="A90" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B90" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A90" s="11"/>
+      <x:c r="B90" s="11"/>
       <x:c r="C90" s="12" t="str">
         <x:f>IF($A90="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A90="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12034,9 +11442,7 @@
       <x:c r="G90" s="11" t="str">
         <x:f>IF($A90="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H90" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H90" s="11"/>
       <x:c r="I90" s="11" t="str">
         <x:f>IF($A90="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -12048,9 +11454,8 @@
       </x:c>
       <x:c r="L90" s="13" t="str">
         <x:f>IF(TRIM($A90)="","",IF(COUNTIF($Q90:$AK90,"?*")=0,"OK","Falta revisar: "&amp;$Q90&amp;$R90&amp;$S90&amp;$T90&amp;$U90&amp;$V90&amp;$W90&amp;$X90&amp;$Y90&amp;$Z90&amp;$AA90&amp;$AB90&amp;$AC90&amp;$AD90&amp;$AE90&amp;$AF90&amp;$AG90&amp;$AH90&amp;$AI90&amp;$AJ90&amp;$AK90))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M90"/>
+      </x:c>
+      <x:c r="M90" s="67"/>
       <x:c r="N90"/>
       <x:c r="O90"/>
       <x:c r="P90"/>
@@ -12131,12 +11536,8 @@
       </x:c>
     </x:row>
     <x:row r="91" ht="24" customHeight="1">
-      <x:c r="A91" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B91" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A91" s="11"/>
+      <x:c r="B91" s="11"/>
       <x:c r="C91" s="12" t="str">
         <x:f>IF($A91="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A91="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12152,9 +11553,7 @@
       <x:c r="G91" s="11" t="str">
         <x:f>IF($A91="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H91" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H91" s="11"/>
       <x:c r="I91" s="11" t="str">
         <x:f>IF($A91="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
@@ -12166,9 +11565,8 @@
       </x:c>
       <x:c r="L91" s="13" t="str">
         <x:f>IF(TRIM($A91)="","",IF(COUNTIF($Q91:$AK91,"?*")=0,"OK","Falta revisar: "&amp;$Q91&amp;$R91&amp;$S91&amp;$T91&amp;$U91&amp;$V91&amp;$W91&amp;$X91&amp;$Y91&amp;$Z91&amp;$AA91&amp;$AB91&amp;$AC91&amp;$AD91&amp;$AE91&amp;$AF91&amp;$AG91&amp;$AH91&amp;$AI91&amp;$AJ91&amp;$AK91))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M91"/>
+      </x:c>
+      <x:c r="M91" s="67"/>
       <x:c r="N91"/>
       <x:c r="O91"/>
       <x:c r="P91"/>
@@ -12249,12 +11647,8 @@
       </x:c>
     </x:row>
     <x:row r="92" ht="24" customHeight="1">
-      <x:c r="A92" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B92" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A92" s="14"/>
+      <x:c r="B92" s="14"/>
       <x:c r="C92" s="15" t="str">
         <x:f>IF($A92="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A92="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12270,23 +11664,20 @@
       <x:c r="G92" s="14" t="str">
         <x:f>IF($A92="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H92" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H92" s="14"/>
       <x:c r="I92" s="14" t="str">
         <x:f>IF($A92="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J92" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K92" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L92" s="16" t="str">
         <x:f>IF(TRIM($A92)="","",IF(COUNTIF($Q92:$AK92,"?*")=0,"OK","Falta revisar: "&amp;$Q92&amp;$R92&amp;$S92&amp;$T92&amp;$U92&amp;$V92&amp;$W92&amp;$X92&amp;$Y92&amp;$Z92&amp;$AA92&amp;$AB92&amp;$AC92&amp;$AD92&amp;$AE92&amp;$AF92&amp;$AG92&amp;$AH92&amp;$AI92&amp;$AJ92&amp;$AK92))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M92"/>
+      </x:c>
+      <x:c r="M92" s="67"/>
       <x:c r="N92"/>
       <x:c r="O92"/>
       <x:c r="P92"/>
@@ -12367,12 +11758,8 @@
       </x:c>
     </x:row>
     <x:row r="93" ht="24" customHeight="1">
-      <x:c r="A93" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B93" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A93" s="14"/>
+      <x:c r="B93" s="14"/>
       <x:c r="C93" s="15" t="str">
         <x:f>IF($A93="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A93="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12388,23 +11775,20 @@
       <x:c r="G93" s="14" t="str">
         <x:f>IF($A93="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H93" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H93" s="14"/>
       <x:c r="I93" s="14" t="str">
         <x:f>IF($A93="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J93" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K93" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L93" s="16" t="str">
         <x:f>IF(TRIM($A93)="","",IF(COUNTIF($Q93:$AK93,"?*")=0,"OK","Falta revisar: "&amp;$Q93&amp;$R93&amp;$S93&amp;$T93&amp;$U93&amp;$V93&amp;$W93&amp;$X93&amp;$Y93&amp;$Z93&amp;$AA93&amp;$AB93&amp;$AC93&amp;$AD93&amp;$AE93&amp;$AF93&amp;$AG93&amp;$AH93&amp;$AI93&amp;$AJ93&amp;$AK93))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M93"/>
+      </x:c>
+      <x:c r="M93" s="67"/>
       <x:c r="N93"/>
       <x:c r="O93"/>
       <x:c r="P93"/>
@@ -12485,12 +11869,8 @@
       </x:c>
     </x:row>
     <x:row r="94" ht="24" customHeight="1">
-      <x:c r="A94" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B94" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A94" s="14"/>
+      <x:c r="B94" s="14"/>
       <x:c r="C94" s="15" t="str">
         <x:f>IF($A94="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A94="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12506,23 +11886,20 @@
       <x:c r="G94" s="14" t="str">
         <x:f>IF($A94="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H94" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H94" s="14"/>
       <x:c r="I94" s="14" t="str">
         <x:f>IF($A94="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J94" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K94" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L94" s="16" t="str">
         <x:f>IF(TRIM($A94)="","",IF(COUNTIF($Q94:$AK94,"?*")=0,"OK","Falta revisar: "&amp;$Q94&amp;$R94&amp;$S94&amp;$T94&amp;$U94&amp;$V94&amp;$W94&amp;$X94&amp;$Y94&amp;$Z94&amp;$AA94&amp;$AB94&amp;$AC94&amp;$AD94&amp;$AE94&amp;$AF94&amp;$AG94&amp;$AH94&amp;$AI94&amp;$AJ94&amp;$AK94))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M94"/>
+      </x:c>
+      <x:c r="M94" s="67"/>
       <x:c r="N94"/>
       <x:c r="O94"/>
       <x:c r="P94"/>
@@ -12603,12 +11980,8 @@
       </x:c>
     </x:row>
     <x:row r="95" ht="24" customHeight="1">
-      <x:c r="A95" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B95" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A95" s="14"/>
+      <x:c r="B95" s="14"/>
       <x:c r="C95" s="15" t="str">
         <x:f>IF($A95="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A95="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12624,23 +11997,20 @@
       <x:c r="G95" s="14" t="str">
         <x:f>IF($A95="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H95" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H95" s="14"/>
       <x:c r="I95" s="14" t="str">
         <x:f>IF($A95="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J95" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K95" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L95" s="16" t="str">
         <x:f>IF(TRIM($A95)="","",IF(COUNTIF($Q95:$AK95,"?*")=0,"OK","Falta revisar: "&amp;$Q95&amp;$R95&amp;$S95&amp;$T95&amp;$U95&amp;$V95&amp;$W95&amp;$X95&amp;$Y95&amp;$Z95&amp;$AA95&amp;$AB95&amp;$AC95&amp;$AD95&amp;$AE95&amp;$AF95&amp;$AG95&amp;$AH95&amp;$AI95&amp;$AJ95&amp;$AK95))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M95"/>
+      </x:c>
+      <x:c r="M95" s="67"/>
       <x:c r="N95"/>
       <x:c r="O95"/>
       <x:c r="P95"/>
@@ -12721,12 +12091,8 @@
       </x:c>
     </x:row>
     <x:row r="96" ht="24" customHeight="1">
-      <x:c r="A96" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B96" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A96" s="14"/>
+      <x:c r="B96" s="14"/>
       <x:c r="C96" s="15" t="str">
         <x:f>IF($A96="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A96="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12742,23 +12108,20 @@
       <x:c r="G96" s="14" t="str">
         <x:f>IF($A96="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H96" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H96" s="14"/>
       <x:c r="I96" s="14" t="str">
         <x:f>IF($A96="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J96" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K96" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L96" s="16" t="str">
         <x:f>IF(TRIM($A96)="","",IF(COUNTIF($Q96:$AK96,"?*")=0,"OK","Falta revisar: "&amp;$Q96&amp;$R96&amp;$S96&amp;$T96&amp;$U96&amp;$V96&amp;$W96&amp;$X96&amp;$Y96&amp;$Z96&amp;$AA96&amp;$AB96&amp;$AC96&amp;$AD96&amp;$AE96&amp;$AF96&amp;$AG96&amp;$AH96&amp;$AI96&amp;$AJ96&amp;$AK96))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M96"/>
+      </x:c>
+      <x:c r="M96" s="67"/>
       <x:c r="N96"/>
       <x:c r="O96"/>
       <x:c r="P96"/>
@@ -12839,12 +12202,8 @@
       </x:c>
     </x:row>
     <x:row r="97" ht="24" customHeight="1">
-      <x:c r="A97" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B97" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A97" s="14"/>
+      <x:c r="B97" s="14"/>
       <x:c r="C97" s="15" t="str">
         <x:f>IF($A97="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A97="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12860,23 +12219,20 @@
       <x:c r="G97" s="14" t="str">
         <x:f>IF($A97="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H97" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H97" s="14"/>
       <x:c r="I97" s="14" t="str">
         <x:f>IF($A97="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J97" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K97" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L97" s="16" t="str">
         <x:f>IF(TRIM($A97)="","",IF(COUNTIF($Q97:$AK97,"?*")=0,"OK","Falta revisar: "&amp;$Q97&amp;$R97&amp;$S97&amp;$T97&amp;$U97&amp;$V97&amp;$W97&amp;$X97&amp;$Y97&amp;$Z97&amp;$AA97&amp;$AB97&amp;$AC97&amp;$AD97&amp;$AE97&amp;$AF97&amp;$AG97&amp;$AH97&amp;$AI97&amp;$AJ97&amp;$AK97))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M97"/>
+      </x:c>
+      <x:c r="M97" s="67"/>
       <x:c r="N97"/>
       <x:c r="O97"/>
       <x:c r="P97"/>
@@ -12957,12 +12313,8 @@
       </x:c>
     </x:row>
     <x:row r="98" ht="24" customHeight="1">
-      <x:c r="A98" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B98" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A98" s="14"/>
+      <x:c r="B98" s="14"/>
       <x:c r="C98" s="15" t="str">
         <x:f>IF($A98="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A98="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -12978,23 +12330,20 @@
       <x:c r="G98" s="14" t="str">
         <x:f>IF($A98="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H98" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H98" s="14"/>
       <x:c r="I98" s="14" t="str">
         <x:f>IF($A98="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J98" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K98" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L98" s="16" t="str">
         <x:f>IF(TRIM($A98)="","",IF(COUNTIF($Q98:$AK98,"?*")=0,"OK","Falta revisar: "&amp;$Q98&amp;$R98&amp;$S98&amp;$T98&amp;$U98&amp;$V98&amp;$W98&amp;$X98&amp;$Y98&amp;$Z98&amp;$AA98&amp;$AB98&amp;$AC98&amp;$AD98&amp;$AE98&amp;$AF98&amp;$AG98&amp;$AH98&amp;$AI98&amp;$AJ98&amp;$AK98))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M98"/>
+      </x:c>
+      <x:c r="M98" s="67"/>
       <x:c r="N98"/>
       <x:c r="O98"/>
       <x:c r="P98"/>
@@ -13075,12 +12424,8 @@
       </x:c>
     </x:row>
     <x:row r="99" ht="24" customHeight="1">
-      <x:c r="A99" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B99" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A99" s="14"/>
+      <x:c r="B99" s="14"/>
       <x:c r="C99" s="15" t="str">
         <x:f>IF($A99="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A99="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13096,23 +12441,20 @@
       <x:c r="G99" s="14" t="str">
         <x:f>IF($A99="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H99" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H99" s="14"/>
       <x:c r="I99" s="14" t="str">
         <x:f>IF($A99="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J99" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K99" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L99" s="16" t="str">
         <x:f>IF(TRIM($A99)="","",IF(COUNTIF($Q99:$AK99,"?*")=0,"OK","Falta revisar: "&amp;$Q99&amp;$R99&amp;$S99&amp;$T99&amp;$U99&amp;$V99&amp;$W99&amp;$X99&amp;$Y99&amp;$Z99&amp;$AA99&amp;$AB99&amp;$AC99&amp;$AD99&amp;$AE99&amp;$AF99&amp;$AG99&amp;$AH99&amp;$AI99&amp;$AJ99&amp;$AK99))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M99"/>
+      </x:c>
+      <x:c r="M99" s="67"/>
       <x:c r="N99"/>
       <x:c r="O99"/>
       <x:c r="P99"/>
@@ -13193,12 +12535,8 @@
       </x:c>
     </x:row>
     <x:row r="100" ht="24" customHeight="1">
-      <x:c r="A100" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B100" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A100" s="14"/>
+      <x:c r="B100" s="14"/>
       <x:c r="C100" s="15" t="str">
         <x:f>IF($A100="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A100="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13214,23 +12552,20 @@
       <x:c r="G100" s="14" t="str">
         <x:f>IF($A100="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H100" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H100" s="14"/>
       <x:c r="I100" s="14" t="str">
         <x:f>IF($A100="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J100" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K100" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L100" s="16" t="str">
         <x:f>IF(TRIM($A100)="","",IF(COUNTIF($Q100:$AK100,"?*")=0,"OK","Falta revisar: "&amp;$Q100&amp;$R100&amp;$S100&amp;$T100&amp;$U100&amp;$V100&amp;$W100&amp;$X100&amp;$Y100&amp;$Z100&amp;$AA100&amp;$AB100&amp;$AC100&amp;$AD100&amp;$AE100&amp;$AF100&amp;$AG100&amp;$AH100&amp;$AI100&amp;$AJ100&amp;$AK100))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M100"/>
+      </x:c>
+      <x:c r="M100" s="67"/>
       <x:c r="N100"/>
       <x:c r="O100"/>
       <x:c r="P100"/>
@@ -13311,12 +12646,8 @@
       </x:c>
     </x:row>
     <x:row r="101" ht="24" customHeight="1">
-      <x:c r="A101" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B101" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A101" s="14"/>
+      <x:c r="B101" s="14"/>
       <x:c r="C101" s="15" t="str">
         <x:f>IF($A101="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A101="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13332,23 +12663,20 @@
       <x:c r="G101" s="14" t="str">
         <x:f>IF($A101="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H101" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H101" s="14"/>
       <x:c r="I101" s="14" t="str">
         <x:f>IF($A101="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J101" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K101" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L101" s="16" t="str">
         <x:f>IF(TRIM($A101)="","",IF(COUNTIF($Q101:$AK101,"?*")=0,"OK","Falta revisar: "&amp;$Q101&amp;$R101&amp;$S101&amp;$T101&amp;$U101&amp;$V101&amp;$W101&amp;$X101&amp;$Y101&amp;$Z101&amp;$AA101&amp;$AB101&amp;$AC101&amp;$AD101&amp;$AE101&amp;$AF101&amp;$AG101&amp;$AH101&amp;$AI101&amp;$AJ101&amp;$AK101))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M101"/>
+      </x:c>
+      <x:c r="M101" s="67"/>
       <x:c r="N101"/>
       <x:c r="O101"/>
       <x:c r="P101"/>
@@ -13429,12 +12757,8 @@
       </x:c>
     </x:row>
     <x:row r="102" ht="24" customHeight="1">
-      <x:c r="A102" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B102" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A102" s="14"/>
+      <x:c r="B102" s="14"/>
       <x:c r="C102" s="15" t="str">
         <x:f>IF($A102="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A102="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13450,23 +12774,20 @@
       <x:c r="G102" s="14" t="str">
         <x:f>IF($A102="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H102" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H102" s="14"/>
       <x:c r="I102" s="14" t="str">
         <x:f>IF($A102="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J102" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K102" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L102" s="16" t="str">
         <x:f>IF(TRIM($A102)="","",IF(COUNTIF($Q102:$AK102,"?*")=0,"OK","Falta revisar: "&amp;$Q102&amp;$R102&amp;$S102&amp;$T102&amp;$U102&amp;$V102&amp;$W102&amp;$X102&amp;$Y102&amp;$Z102&amp;$AA102&amp;$AB102&amp;$AC102&amp;$AD102&amp;$AE102&amp;$AF102&amp;$AG102&amp;$AH102&amp;$AI102&amp;$AJ102&amp;$AK102))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M102"/>
+      </x:c>
+      <x:c r="M102" s="67"/>
       <x:c r="N102"/>
       <x:c r="O102"/>
       <x:c r="P102"/>
@@ -13547,12 +12868,8 @@
       </x:c>
     </x:row>
     <x:row r="103" ht="24" customHeight="1">
-      <x:c r="A103" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B103" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A103" s="14"/>
+      <x:c r="B103" s="14"/>
       <x:c r="C103" s="15" t="str">
         <x:f>IF($A103="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A103="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13568,23 +12885,20 @@
       <x:c r="G103" s="14" t="str">
         <x:f>IF($A103="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H103" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H103" s="14"/>
       <x:c r="I103" s="14" t="str">
         <x:f>IF($A103="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J103" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K103" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L103" s="16" t="str">
         <x:f>IF(TRIM($A103)="","",IF(COUNTIF($Q103:$AK103,"?*")=0,"OK","Falta revisar: "&amp;$Q103&amp;$R103&amp;$S103&amp;$T103&amp;$U103&amp;$V103&amp;$W103&amp;$X103&amp;$Y103&amp;$Z103&amp;$AA103&amp;$AB103&amp;$AC103&amp;$AD103&amp;$AE103&amp;$AF103&amp;$AG103&amp;$AH103&amp;$AI103&amp;$AJ103&amp;$AK103))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M103"/>
+      </x:c>
+      <x:c r="M103" s="67"/>
       <x:c r="N103"/>
       <x:c r="O103"/>
       <x:c r="P103"/>
@@ -13665,12 +12979,8 @@
       </x:c>
     </x:row>
     <x:row r="104" ht="24" customHeight="1">
-      <x:c r="A104" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B104" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A104" s="14"/>
+      <x:c r="B104" s="14"/>
       <x:c r="C104" s="15" t="str">
         <x:f>IF($A104="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A104="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13686,23 +12996,20 @@
       <x:c r="G104" s="14" t="str">
         <x:f>IF($A104="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H104" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H104" s="14"/>
       <x:c r="I104" s="14" t="str">
         <x:f>IF($A104="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J104" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K104" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L104" s="16" t="str">
         <x:f>IF(TRIM($A104)="","",IF(COUNTIF($Q104:$AK104,"?*")=0,"OK","Falta revisar: "&amp;$Q104&amp;$R104&amp;$S104&amp;$T104&amp;$U104&amp;$V104&amp;$W104&amp;$X104&amp;$Y104&amp;$Z104&amp;$AA104&amp;$AB104&amp;$AC104&amp;$AD104&amp;$AE104&amp;$AF104&amp;$AG104&amp;$AH104&amp;$AI104&amp;$AJ104&amp;$AK104))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M104"/>
+      </x:c>
+      <x:c r="M104" s="67"/>
       <x:c r="N104"/>
       <x:c r="O104"/>
       <x:c r="P104"/>
@@ -13783,12 +13090,8 @@
       </x:c>
     </x:row>
     <x:row r="105" ht="24" customHeight="1">
-      <x:c r="A105" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B105" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A105" s="14"/>
+      <x:c r="B105" s="14"/>
       <x:c r="C105" s="15" t="str">
         <x:f>IF($A105="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A105="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13804,23 +13107,20 @@
       <x:c r="G105" s="14" t="str">
         <x:f>IF($A105="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H105" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H105" s="14"/>
       <x:c r="I105" s="14" t="str">
         <x:f>IF($A105="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J105" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K105" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L105" s="16" t="str">
         <x:f>IF(TRIM($A105)="","",IF(COUNTIF($Q105:$AK105,"?*")=0,"OK","Falta revisar: "&amp;$Q105&amp;$R105&amp;$S105&amp;$T105&amp;$U105&amp;$V105&amp;$W105&amp;$X105&amp;$Y105&amp;$Z105&amp;$AA105&amp;$AB105&amp;$AC105&amp;$AD105&amp;$AE105&amp;$AF105&amp;$AG105&amp;$AH105&amp;$AI105&amp;$AJ105&amp;$AK105))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M105"/>
+      </x:c>
+      <x:c r="M105" s="67"/>
       <x:c r="N105"/>
       <x:c r="O105"/>
       <x:c r="P105"/>
@@ -13901,12 +13201,8 @@
       </x:c>
     </x:row>
     <x:row r="106" ht="24" customHeight="1">
-      <x:c r="A106" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B106" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A106" s="14"/>
+      <x:c r="B106" s="14"/>
       <x:c r="C106" s="15" t="str">
         <x:f>IF($A106="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A106="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -13922,23 +13218,20 @@
       <x:c r="G106" s="14" t="str">
         <x:f>IF($A106="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H106" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H106" s="14"/>
       <x:c r="I106" s="14" t="str">
         <x:f>IF($A106="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J106" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K106" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L106" s="16" t="str">
         <x:f>IF(TRIM($A106)="","",IF(COUNTIF($Q106:$AK106,"?*")=0,"OK","Falta revisar: "&amp;$Q106&amp;$R106&amp;$S106&amp;$T106&amp;$U106&amp;$V106&amp;$W106&amp;$X106&amp;$Y106&amp;$Z106&amp;$AA106&amp;$AB106&amp;$AC106&amp;$AD106&amp;$AE106&amp;$AF106&amp;$AG106&amp;$AH106&amp;$AI106&amp;$AJ106&amp;$AK106))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M106"/>
+      </x:c>
+      <x:c r="M106" s="67"/>
       <x:c r="N106"/>
       <x:c r="O106"/>
       <x:c r="P106"/>
@@ -14019,12 +13312,8 @@
       </x:c>
     </x:row>
     <x:row r="107" ht="24" customHeight="1">
-      <x:c r="A107" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B107" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A107" s="14"/>
+      <x:c r="B107" s="14"/>
       <x:c r="C107" s="15" t="str">
         <x:f>IF($A107="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A107="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14040,23 +13329,20 @@
       <x:c r="G107" s="14" t="str">
         <x:f>IF($A107="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H107" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H107" s="14"/>
       <x:c r="I107" s="14" t="str">
         <x:f>IF($A107="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J107" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K107" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L107" s="16" t="str">
         <x:f>IF(TRIM($A107)="","",IF(COUNTIF($Q107:$AK107,"?*")=0,"OK","Falta revisar: "&amp;$Q107&amp;$R107&amp;$S107&amp;$T107&amp;$U107&amp;$V107&amp;$W107&amp;$X107&amp;$Y107&amp;$Z107&amp;$AA107&amp;$AB107&amp;$AC107&amp;$AD107&amp;$AE107&amp;$AF107&amp;$AG107&amp;$AH107&amp;$AI107&amp;$AJ107&amp;$AK107))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M107"/>
+      </x:c>
+      <x:c r="M107" s="67"/>
       <x:c r="N107"/>
       <x:c r="O107"/>
       <x:c r="P107"/>
@@ -14137,12 +13423,8 @@
       </x:c>
     </x:row>
     <x:row r="108" ht="24" customHeight="1">
-      <x:c r="A108" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B108" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A108" s="14"/>
+      <x:c r="B108" s="14"/>
       <x:c r="C108" s="15" t="str">
         <x:f>IF($A108="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A108="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14158,23 +13440,20 @@
       <x:c r="G108" s="14" t="str">
         <x:f>IF($A108="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H108" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H108" s="14"/>
       <x:c r="I108" s="14" t="str">
         <x:f>IF($A108="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J108" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K108" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L108" s="16" t="str">
         <x:f>IF(TRIM($A108)="","",IF(COUNTIF($Q108:$AK108,"?*")=0,"OK","Falta revisar: "&amp;$Q108&amp;$R108&amp;$S108&amp;$T108&amp;$U108&amp;$V108&amp;$W108&amp;$X108&amp;$Y108&amp;$Z108&amp;$AA108&amp;$AB108&amp;$AC108&amp;$AD108&amp;$AE108&amp;$AF108&amp;$AG108&amp;$AH108&amp;$AI108&amp;$AJ108&amp;$AK108))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M108"/>
+      </x:c>
+      <x:c r="M108" s="67"/>
       <x:c r="N108"/>
       <x:c r="O108"/>
       <x:c r="P108"/>
@@ -14255,12 +13534,8 @@
       </x:c>
     </x:row>
     <x:row r="109" ht="24" customHeight="1">
-      <x:c r="A109" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B109" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A109" s="14"/>
+      <x:c r="B109" s="14"/>
       <x:c r="C109" s="15" t="str">
         <x:f>IF($A109="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A109="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14276,23 +13551,20 @@
       <x:c r="G109" s="14" t="str">
         <x:f>IF($A109="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H109" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H109" s="14"/>
       <x:c r="I109" s="14" t="str">
         <x:f>IF($A109="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J109" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K109" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L109" s="16" t="str">
         <x:f>IF(TRIM($A109)="","",IF(COUNTIF($Q109:$AK109,"?*")=0,"OK","Falta revisar: "&amp;$Q109&amp;$R109&amp;$S109&amp;$T109&amp;$U109&amp;$V109&amp;$W109&amp;$X109&amp;$Y109&amp;$Z109&amp;$AA109&amp;$AB109&amp;$AC109&amp;$AD109&amp;$AE109&amp;$AF109&amp;$AG109&amp;$AH109&amp;$AI109&amp;$AJ109&amp;$AK109))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M109"/>
+      </x:c>
+      <x:c r="M109" s="67"/>
       <x:c r="N109"/>
       <x:c r="O109"/>
       <x:c r="P109"/>
@@ -14373,12 +13645,8 @@
       </x:c>
     </x:row>
     <x:row r="110" ht="24" customHeight="1">
-      <x:c r="A110" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B110" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A110" s="14"/>
+      <x:c r="B110" s="14"/>
       <x:c r="C110" s="15" t="str">
         <x:f>IF($A110="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A110="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14394,23 +13662,20 @@
       <x:c r="G110" s="14" t="str">
         <x:f>IF($A110="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H110" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H110" s="14"/>
       <x:c r="I110" s="14" t="str">
         <x:f>IF($A110="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J110" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K110" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L110" s="16" t="str">
         <x:f>IF(TRIM($A110)="","",IF(COUNTIF($Q110:$AK110,"?*")=0,"OK","Falta revisar: "&amp;$Q110&amp;$R110&amp;$S110&amp;$T110&amp;$U110&amp;$V110&amp;$W110&amp;$X110&amp;$Y110&amp;$Z110&amp;$AA110&amp;$AB110&amp;$AC110&amp;$AD110&amp;$AE110&amp;$AF110&amp;$AG110&amp;$AH110&amp;$AI110&amp;$AJ110&amp;$AK110))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M110"/>
+      </x:c>
+      <x:c r="M110" s="67"/>
       <x:c r="N110"/>
       <x:c r="O110"/>
       <x:c r="P110"/>
@@ -14491,12 +13756,8 @@
       </x:c>
     </x:row>
     <x:row r="111" ht="24" customHeight="1">
-      <x:c r="A111" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B111" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A111" s="14"/>
+      <x:c r="B111" s="14"/>
       <x:c r="C111" s="15" t="str">
         <x:f>IF($A111="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A111="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14512,23 +13773,20 @@
       <x:c r="G111" s="14" t="str">
         <x:f>IF($A111="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H111" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H111" s="14"/>
       <x:c r="I111" s="14" t="str">
         <x:f>IF($A111="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J111" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K111" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L111" s="16" t="str">
         <x:f>IF(TRIM($A111)="","",IF(COUNTIF($Q111:$AK111,"?*")=0,"OK","Falta revisar: "&amp;$Q111&amp;$R111&amp;$S111&amp;$T111&amp;$U111&amp;$V111&amp;$W111&amp;$X111&amp;$Y111&amp;$Z111&amp;$AA111&amp;$AB111&amp;$AC111&amp;$AD111&amp;$AE111&amp;$AF111&amp;$AG111&amp;$AH111&amp;$AI111&amp;$AJ111&amp;$AK111))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M111"/>
+      </x:c>
+      <x:c r="M111" s="67"/>
       <x:c r="N111"/>
       <x:c r="O111"/>
       <x:c r="P111"/>
@@ -14609,12 +13867,8 @@
       </x:c>
     </x:row>
     <x:row r="112" ht="24" customHeight="1">
-      <x:c r="A112" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B112" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A112" s="14"/>
+      <x:c r="B112" s="14"/>
       <x:c r="C112" s="15" t="str">
         <x:f>IF($A112="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A112="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14630,23 +13884,20 @@
       <x:c r="G112" s="14" t="str">
         <x:f>IF($A112="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H112" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H112" s="14"/>
       <x:c r="I112" s="14" t="str">
         <x:f>IF($A112="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J112" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K112" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L112" s="16" t="str">
         <x:f>IF(TRIM($A112)="","",IF(COUNTIF($Q112:$AK112,"?*")=0,"OK","Falta revisar: "&amp;$Q112&amp;$R112&amp;$S112&amp;$T112&amp;$U112&amp;$V112&amp;$W112&amp;$X112&amp;$Y112&amp;$Z112&amp;$AA112&amp;$AB112&amp;$AC112&amp;$AD112&amp;$AE112&amp;$AF112&amp;$AG112&amp;$AH112&amp;$AI112&amp;$AJ112&amp;$AK112))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M112"/>
+      </x:c>
+      <x:c r="M112" s="67"/>
       <x:c r="N112"/>
       <x:c r="O112"/>
       <x:c r="P112"/>
@@ -14727,12 +13978,8 @@
       </x:c>
     </x:row>
     <x:row r="113" ht="24" customHeight="1">
-      <x:c r="A113" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B113" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A113" s="14"/>
+      <x:c r="B113" s="14"/>
       <x:c r="C113" s="15" t="str">
         <x:f>IF($A113="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A113="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14748,23 +13995,20 @@
       <x:c r="G113" s="14" t="str">
         <x:f>IF($A113="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H113" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H113" s="14"/>
       <x:c r="I113" s="14" t="str">
         <x:f>IF($A113="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J113" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K113" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L113" s="16" t="str">
         <x:f>IF(TRIM($A113)="","",IF(COUNTIF($Q113:$AK113,"?*")=0,"OK","Falta revisar: "&amp;$Q113&amp;$R113&amp;$S113&amp;$T113&amp;$U113&amp;$V113&amp;$W113&amp;$X113&amp;$Y113&amp;$Z113&amp;$AA113&amp;$AB113&amp;$AC113&amp;$AD113&amp;$AE113&amp;$AF113&amp;$AG113&amp;$AH113&amp;$AI113&amp;$AJ113&amp;$AK113))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M113"/>
+      </x:c>
+      <x:c r="M113" s="67"/>
       <x:c r="N113"/>
       <x:c r="O113"/>
       <x:c r="P113"/>
@@ -14845,12 +14089,8 @@
       </x:c>
     </x:row>
     <x:row r="114" ht="24" customHeight="1">
-      <x:c r="A114" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B114" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A114" s="14"/>
+      <x:c r="B114" s="14"/>
       <x:c r="C114" s="15" t="str">
         <x:f>IF($A114="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A114="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14866,23 +14106,20 @@
       <x:c r="G114" s="14" t="str">
         <x:f>IF($A114="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H114" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H114" s="14"/>
       <x:c r="I114" s="14" t="str">
         <x:f>IF($A114="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J114" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K114" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L114" s="16" t="str">
         <x:f>IF(TRIM($A114)="","",IF(COUNTIF($Q114:$AK114,"?*")=0,"OK","Falta revisar: "&amp;$Q114&amp;$R114&amp;$S114&amp;$T114&amp;$U114&amp;$V114&amp;$W114&amp;$X114&amp;$Y114&amp;$Z114&amp;$AA114&amp;$AB114&amp;$AC114&amp;$AD114&amp;$AE114&amp;$AF114&amp;$AG114&amp;$AH114&amp;$AI114&amp;$AJ114&amp;$AK114))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M114"/>
+      </x:c>
+      <x:c r="M114" s="67"/>
       <x:c r="N114"/>
       <x:c r="O114"/>
       <x:c r="P114"/>
@@ -14963,12 +14200,8 @@
       </x:c>
     </x:row>
     <x:row r="115" ht="24" customHeight="1">
-      <x:c r="A115" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B115" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A115" s="14"/>
+      <x:c r="B115" s="14"/>
       <x:c r="C115" s="15" t="str">
         <x:f>IF($A115="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A115="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -14984,23 +14217,20 @@
       <x:c r="G115" s="14" t="str">
         <x:f>IF($A115="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H115" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H115" s="14"/>
       <x:c r="I115" s="14" t="str">
         <x:f>IF($A115="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J115" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K115" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L115" s="16" t="str">
         <x:f>IF(TRIM($A115)="","",IF(COUNTIF($Q115:$AK115,"?*")=0,"OK","Falta revisar: "&amp;$Q115&amp;$R115&amp;$S115&amp;$T115&amp;$U115&amp;$V115&amp;$W115&amp;$X115&amp;$Y115&amp;$Z115&amp;$AA115&amp;$AB115&amp;$AC115&amp;$AD115&amp;$AE115&amp;$AF115&amp;$AG115&amp;$AH115&amp;$AI115&amp;$AJ115&amp;$AK115))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M115"/>
+      </x:c>
+      <x:c r="M115" s="67"/>
       <x:c r="N115"/>
       <x:c r="O115"/>
       <x:c r="P115"/>
@@ -15081,12 +14311,8 @@
       </x:c>
     </x:row>
     <x:row r="116" ht="24" customHeight="1">
-      <x:c r="A116" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B116" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A116" s="14"/>
+      <x:c r="B116" s="14"/>
       <x:c r="C116" s="15" t="str">
         <x:f>IF($A116="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A116="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15102,23 +14328,20 @@
       <x:c r="G116" s="14" t="str">
         <x:f>IF($A116="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H116" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H116" s="14"/>
       <x:c r="I116" s="14" t="str">
         <x:f>IF($A116="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J116" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K116" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L116" s="16" t="str">
         <x:f>IF(TRIM($A116)="","",IF(COUNTIF($Q116:$AK116,"?*")=0,"OK","Falta revisar: "&amp;$Q116&amp;$R116&amp;$S116&amp;$T116&amp;$U116&amp;$V116&amp;$W116&amp;$X116&amp;$Y116&amp;$Z116&amp;$AA116&amp;$AB116&amp;$AC116&amp;$AD116&amp;$AE116&amp;$AF116&amp;$AG116&amp;$AH116&amp;$AI116&amp;$AJ116&amp;$AK116))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M116"/>
+      </x:c>
+      <x:c r="M116" s="67"/>
       <x:c r="N116"/>
       <x:c r="O116"/>
       <x:c r="P116"/>
@@ -15199,12 +14422,8 @@
       </x:c>
     </x:row>
     <x:row r="117" ht="24" customHeight="1">
-      <x:c r="A117" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B117" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A117" s="14"/>
+      <x:c r="B117" s="14"/>
       <x:c r="C117" s="15" t="str">
         <x:f>IF($A117="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A117="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15220,23 +14439,20 @@
       <x:c r="G117" s="14" t="str">
         <x:f>IF($A117="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H117" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H117" s="14"/>
       <x:c r="I117" s="14" t="str">
         <x:f>IF($A117="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J117" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K117" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L117" s="16" t="str">
         <x:f>IF(TRIM($A117)="","",IF(COUNTIF($Q117:$AK117,"?*")=0,"OK","Falta revisar: "&amp;$Q117&amp;$R117&amp;$S117&amp;$T117&amp;$U117&amp;$V117&amp;$W117&amp;$X117&amp;$Y117&amp;$Z117&amp;$AA117&amp;$AB117&amp;$AC117&amp;$AD117&amp;$AE117&amp;$AF117&amp;$AG117&amp;$AH117&amp;$AI117&amp;$AJ117&amp;$AK117))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M117"/>
+      </x:c>
+      <x:c r="M117" s="67"/>
       <x:c r="N117"/>
       <x:c r="O117"/>
       <x:c r="P117"/>
@@ -15317,12 +14533,8 @@
       </x:c>
     </x:row>
     <x:row r="118" ht="24" customHeight="1">
-      <x:c r="A118" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B118" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A118" s="14"/>
+      <x:c r="B118" s="14"/>
       <x:c r="C118" s="15" t="str">
         <x:f>IF($A118="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A118="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15338,23 +14550,20 @@
       <x:c r="G118" s="14" t="str">
         <x:f>IF($A118="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H118" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H118" s="14"/>
       <x:c r="I118" s="14" t="str">
         <x:f>IF($A118="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J118" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K118" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L118" s="16" t="str">
         <x:f>IF(TRIM($A118)="","",IF(COUNTIF($Q118:$AK118,"?*")=0,"OK","Falta revisar: "&amp;$Q118&amp;$R118&amp;$S118&amp;$T118&amp;$U118&amp;$V118&amp;$W118&amp;$X118&amp;$Y118&amp;$Z118&amp;$AA118&amp;$AB118&amp;$AC118&amp;$AD118&amp;$AE118&amp;$AF118&amp;$AG118&amp;$AH118&amp;$AI118&amp;$AJ118&amp;$AK118))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M118"/>
+      </x:c>
+      <x:c r="M118" s="67"/>
       <x:c r="N118"/>
       <x:c r="O118"/>
       <x:c r="P118"/>
@@ -15435,12 +14644,8 @@
       </x:c>
     </x:row>
     <x:row r="119" ht="24" customHeight="1">
-      <x:c r="A119" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B119" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A119" s="14"/>
+      <x:c r="B119" s="14"/>
       <x:c r="C119" s="15" t="str">
         <x:f>IF($A119="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A119="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15456,23 +14661,20 @@
       <x:c r="G119" s="14" t="str">
         <x:f>IF($A119="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H119" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H119" s="14"/>
       <x:c r="I119" s="14" t="str">
         <x:f>IF($A119="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J119" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K119" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L119" s="16" t="str">
         <x:f>IF(TRIM($A119)="","",IF(COUNTIF($Q119:$AK119,"?*")=0,"OK","Falta revisar: "&amp;$Q119&amp;$R119&amp;$S119&amp;$T119&amp;$U119&amp;$V119&amp;$W119&amp;$X119&amp;$Y119&amp;$Z119&amp;$AA119&amp;$AB119&amp;$AC119&amp;$AD119&amp;$AE119&amp;$AF119&amp;$AG119&amp;$AH119&amp;$AI119&amp;$AJ119&amp;$AK119))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M119"/>
+      </x:c>
+      <x:c r="M119" s="67"/>
       <x:c r="N119"/>
       <x:c r="O119"/>
       <x:c r="P119"/>
@@ -15553,12 +14755,8 @@
       </x:c>
     </x:row>
     <x:row r="120" ht="24" customHeight="1">
-      <x:c r="A120" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B120" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A120" s="14"/>
+      <x:c r="B120" s="14"/>
       <x:c r="C120" s="15" t="str">
         <x:f>IF($A120="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A120="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15574,23 +14772,20 @@
       <x:c r="G120" s="14" t="str">
         <x:f>IF($A120="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H120" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H120" s="14"/>
       <x:c r="I120" s="14" t="str">
         <x:f>IF($A120="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J120" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K120" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L120" s="16" t="str">
         <x:f>IF(TRIM($A120)="","",IF(COUNTIF($Q120:$AK120,"?*")=0,"OK","Falta revisar: "&amp;$Q120&amp;$R120&amp;$S120&amp;$T120&amp;$U120&amp;$V120&amp;$W120&amp;$X120&amp;$Y120&amp;$Z120&amp;$AA120&amp;$AB120&amp;$AC120&amp;$AD120&amp;$AE120&amp;$AF120&amp;$AG120&amp;$AH120&amp;$AI120&amp;$AJ120&amp;$AK120))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M120"/>
+      </x:c>
+      <x:c r="M120" s="67"/>
       <x:c r="N120"/>
       <x:c r="O120"/>
       <x:c r="P120"/>
@@ -15671,12 +14866,8 @@
       </x:c>
     </x:row>
     <x:row r="121" ht="24" customHeight="1">
-      <x:c r="A121" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B121" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A121" s="14"/>
+      <x:c r="B121" s="14"/>
       <x:c r="C121" s="15" t="str">
         <x:f>IF($A121="Emparejamiento Ampliado",VALIDACIONES!$I$1,IF($A121="Respuesta A/B/Ambas/Ninguna","I. "&amp;CHAR(10)&amp;"II. ",""))</x:f>
       </x:c>
@@ -15692,23 +14883,20 @@
       <x:c r="G121" s="14" t="str">
         <x:f>IF($A121="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera","")</x:f>
       </x:c>
-      <x:c r="H121" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="H121" s="14"/>
       <x:c r="I121" s="14" t="str">
         <x:f>IF($A121="Verdadero o Falso Simple","A","")</x:f>
       </x:c>
       <x:c r="J121" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K121" s="14" t="str">
         <x:v>1P</x:v>
       </x:c>
       <x:c r="L121" s="16" t="str">
         <x:f>IF(TRIM($A121)="","",IF(COUNTIF($Q121:$AK121,"?*")=0,"OK","Falta revisar: "&amp;$Q121&amp;$R121&amp;$S121&amp;$T121&amp;$U121&amp;$V121&amp;$W121&amp;$X121&amp;$Y121&amp;$Z121&amp;$AA121&amp;$AB121&amp;$AC121&amp;$AD121&amp;$AE121&amp;$AF121&amp;$AG121&amp;$AH121&amp;$AI121&amp;$AJ121&amp;$AK121))</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="M121"/>
+      </x:c>
+      <x:c r="M121" s="67"/>
       <x:c r="N121"/>
       <x:c r="O121"/>
       <x:c r="P121"/>
@@ -19316,408 +18504,360 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B1" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C1" s="18" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D1" s="18" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E1" s="18" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F1" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G1" s="18" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B1" s="18" t="s">
+      <x:c r="H1" s="18" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C1" s="18" t="s">
+      <x:c r="I1" s="18" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D1" s="18" t="s">
+      <x:c r="J1" s="18" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E1" s="18" t="s">
+      <x:c r="K1" s="18" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F1" s="18" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G1" s="18" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H1" s="18" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I1" s="18" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J1" s="18" t="s">
+      <x:c r="L1" s="18" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="K1" s="18" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="L1" s="18" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="17" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="B2"/>
       <x:c r="C2" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H2" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
       <x:c r="I2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K2" t="s">
-        <x:v>4</x:v>
+      <x:c r="K2" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" t="s">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="B3"/>
       <x:c r="C3" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H3" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
       <x:c r="I3" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K3" t="s">
-        <x:v>4</x:v>
+      <x:c r="K3" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B4"/>
       <x:c r="C4" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H4" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H4"/>
       <x:c r="I4" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K4" t="s">
-        <x:v>4</x:v>
+      <x:c r="K4" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5"/>
       <x:c r="C5" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G5" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H5" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H5"/>
       <x:c r="I5" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J5" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K5" t="s">
-        <x:v>4</x:v>
+      <x:c r="K5" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L5" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6"/>
+      <x:c r="C6" s="6" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D6" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F6" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H6" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I6" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D6" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H6" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="I6" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="J6" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6" t="s">
-        <x:v>4</x:v>
+      <x:c r="K6" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L6" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7"/>
       <x:c r="C7" s="6" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F7" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G7" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H7" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I7" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J7" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K7" t="s">
-        <x:v>4</x:v>
+      <x:c r="K7" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L7" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8"/>
       <x:c r="C8" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F8" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G8" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H8" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H8"/>
       <x:c r="I8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J8" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="J8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K8" t="s">
-        <x:v>4</x:v>
+      <x:c r="K8" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L8" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9"/>
       <x:c r="C9" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G9" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H9" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H9"/>
       <x:c r="I9" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K9" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L9" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I10" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
       <x:c r="J10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K10" t="s">
-        <x:v>4</x:v>
+      <x:c r="K10" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L10" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G11" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D11" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G11" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="H11" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I11" t="s">
         <x:v>1</x:v>
@@ -19725,277 +18865,219 @@
       <x:c r="J11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K11" t="s">
-        <x:v>4</x:v>
+      <x:c r="K11" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L11" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F12" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G12" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H12" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I12" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" t="s">
-        <x:v>4</x:v>
+      <x:c r="K12" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L12" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K13" t="s">
-        <x:v>4</x:v>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L13" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
       <x:c r="I14" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K14" t="s">
-        <x:v>4</x:v>
+      <x:c r="K14" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L14" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D15" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E15" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F15" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G15" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H15" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
       <x:c r="I15" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J15" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K15" t="s">
-        <x:v>4</x:v>
+      <x:c r="K15" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L15" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E16" t="s">
-        <x:v>133</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F16" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G16" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H16" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I16" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J16" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K16" t="s">
-        <x:v>4</x:v>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L16" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H17" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
       <x:c r="I17" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J17" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K17" t="s">
-        <x:v>4</x:v>
+      <x:c r="K17" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L17" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C18" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D18" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E18" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F18" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G18" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H18" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
       <x:c r="I18" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J18" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K18" t="s">
-        <x:v>4</x:v>
+      <x:c r="K18" t="str">
+        <x:v>1P</x:v>
       </x:c>
       <x:c r="L18" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/evaluaciones-frontend/src/assets/formato_banco_preguntas_asig_EF_1P.xlsx
+++ b/evaluaciones-frontend/src/assets/formato_banco_preguntas_asig_EF_1P.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R65e99fdbbbd447ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banco" sheetId="3" r:id="R9465090ac55c42f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplo" sheetId="4" r:id="Ree1b56f1657e4909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACIONES" state="veryHidden" sheetId="1" r:id="R0e1518ce15dd493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Re7d0b35c229c4d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banco" sheetId="3" r:id="Ree777055b0b24760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplo" sheetId="4" r:id="R7788594530cf472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACIONES" state="veryHidden" sheetId="1" r:id="R09ff04e01f484e99"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="LISTA_TIPOS_2P">VALIDACIONES!$A$1:$A$8</x:definedName>
@@ -468,7 +468,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="66">
+  <x:fills count="76">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -568,6 +568,56 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF7D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4527A0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F0FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4527A0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F0FF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -902,7 +952,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="315">
+  <x:cellXfs count="367">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1716,6 +1766,146 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="67" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="66" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="68" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="70" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="70" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="69" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="71" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="72" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="71" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="73" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="75" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="75" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="75" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="75" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="74" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2221,10 +2411,10 @@
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="314" t="str">
+      <x:c r="A35" s="366" t="str">
         <x:v>AYUDA RÁPIDA PARA INCISOS</x:v>
       </x:c>
-      <x:c r="B35" s="314" t="str"/>
+      <x:c r="B35" s="366" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="106" t="str">
@@ -2409,40 +2599,42 @@
       <x:c r="AN1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AO1" s="299" t="str">
+      <x:c r="AO1" s="351" t="str">
         <x:v>CONTROL DE DISTRIBUCIÓN · 1P</x:v>
       </x:c>
-      <x:c r="AP1" s="299"/>
-      <x:c r="AQ1" s="299"/>
+      <x:c r="AP1" s="351"/>
+      <x:c r="AQ1" s="351"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="290"/>
-      <x:c r="B2" s="290"/>
-      <x:c r="C2" s="290"/>
-      <x:c r="D2" s="290" t="str">
+      <x:c r="A2" s="342"/>
+      <x:c r="B2" s="342"/>
+      <x:c r="C2" s="342"/>
+      <x:c r="D2" s="342" t="str">
         <x:f>IF($A2="Verdadero o Falso Simple","Verdadero",IF($A2="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A2="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E2" s="290" t="str">
+      <x:c r="E2" s="342" t="str">
         <x:f>IF($A2="Verdadero o Falso Simple","Falso",IF($A2="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A2="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F2" s="290" t="str">
+      <x:c r="F2" s="342" t="str">
         <x:f>IF($A2="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A2="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G2" s="290" t="str">
+      <x:c r="G2" s="342" t="str">
         <x:f>IF($A2="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A2="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H2" s="290" t="str">
+      <x:c r="H2" s="342" t="str">
         <x:f>IF($A2="Verdadero o Falso Simple","",IF($A2="Respuesta A/B/Ambas/Ninguna","",IF($A2="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I2" s="290"/>
-      <x:c r="J2" s="290" t="n">
+      <x:c r="I2" s="342"/>
+      <x:c r="J2" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K2" s="290" t="str">
+      <x:c r="K2" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L2" s="291"/>
-      <x:c r="M2" s="289"/>
+      <x:c r="L2" s="343" t="str">
+        <x:f>IF(TRIM($A2)="","",IF(COUNTIF($Q2:$AJ2,"?*")=0,"OK","Falta revisar: "&amp;$Q2&amp;$R2&amp;$S2&amp;$T2&amp;$U2&amp;$V2&amp;$W2&amp;$X2&amp;$Y2&amp;$Z2&amp;$AA2&amp;$AB2&amp;$AC2&amp;$AD2&amp;$AE2&amp;$AF2&amp;$AG2&amp;$AH2&amp;$AI2&amp;$AJ2))</x:f>
+      </x:c>
+      <x:c r="M2" s="341"/>
       <x:c r="N2"/>
       <x:c r="O2"/>
       <x:c r="P2"/>
@@ -2519,45 +2711,47 @@
       <x:c r="AN2" t="str">
         <x:f>IF(AND(OR($A2="Ítems agrupados por caso clínico o problema",$A2="Subítem de caso o problema",$A2="Emparejamiento Ampliado",$A2="Opción de Emparejamiento Ampliado"),TRIM($B2)=""),IF(COUNTIF($M2:$O2,"?*")&gt;0,", ","")&amp;"grupo","")</x:f>
       </x:c>
-      <x:c r="AO2" s="305" t="str">
+      <x:c r="AO2" s="357" t="str">
         <x:v>Fáciles (1)</x:v>
       </x:c>
-      <x:c r="AP2" s="306" t="n">
-        <x:f>COUNTIF($J$2:$J$61,1)</x:f>
+      <x:c r="AP2" s="358" t="n">
+        <x:f>COUNTIF($J$2:$J$1001,1)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AQ2" s="307" t="str">
+      <x:c r="AQ2" s="359" t="str">
         <x:v>Meta: 15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="290"/>
-      <x:c r="B3" s="290"/>
-      <x:c r="C3" s="290"/>
-      <x:c r="D3" s="290" t="str">
+      <x:c r="A3" s="342"/>
+      <x:c r="B3" s="342"/>
+      <x:c r="C3" s="342"/>
+      <x:c r="D3" s="342" t="str">
         <x:f>IF($A3="Verdadero o Falso Simple","Verdadero",IF($A3="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A3="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E3" s="290" t="str">
+      <x:c r="E3" s="342" t="str">
         <x:f>IF($A3="Verdadero o Falso Simple","Falso",IF($A3="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A3="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F3" s="290" t="str">
+      <x:c r="F3" s="342" t="str">
         <x:f>IF($A3="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A3="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G3" s="290" t="str">
+      <x:c r="G3" s="342" t="str">
         <x:f>IF($A3="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A3="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H3" s="290" t="str">
+      <x:c r="H3" s="342" t="str">
         <x:f>IF($A3="Verdadero o Falso Simple","",IF($A3="Respuesta A/B/Ambas/Ninguna","",IF($A3="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I3" s="290"/>
-      <x:c r="J3" s="290" t="n">
+      <x:c r="I3" s="342"/>
+      <x:c r="J3" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K3" s="290" t="str">
+      <x:c r="K3" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L3" s="291"/>
-      <x:c r="M3" s="289"/>
+      <x:c r="L3" s="343" t="str">
+        <x:f>IF(TRIM($A3)="","",IF(COUNTIF($Q3:$AJ3,"?*")=0,"OK","Falta revisar: "&amp;$Q3&amp;$R3&amp;$S3&amp;$T3&amp;$U3&amp;$V3&amp;$W3&amp;$X3&amp;$Y3&amp;$Z3&amp;$AA3&amp;$AB3&amp;$AC3&amp;$AD3&amp;$AE3&amp;$AF3&amp;$AG3&amp;$AH3&amp;$AI3&amp;$AJ3))</x:f>
+      </x:c>
+      <x:c r="M3" s="341"/>
       <x:c r="N3"/>
       <x:c r="O3"/>
       <x:c r="P3"/>
@@ -2634,45 +2828,47 @@
       <x:c r="AN3" t="str">
         <x:f>IF(AND(OR($A3="Ítems agrupados por caso clínico o problema",$A3="Subítem de caso o problema",$A3="Emparejamiento Ampliado",$A3="Opción de Emparejamiento Ampliado"),TRIM($B3)=""),IF(COUNTIF($M3:$O3,"?*")&gt;0,", ","")&amp;"grupo","")</x:f>
       </x:c>
-      <x:c r="AO3" s="308" t="str">
+      <x:c r="AO3" s="360" t="str">
         <x:v>Medias (2)</x:v>
       </x:c>
-      <x:c r="AP3" s="309" t="n">
-        <x:f>COUNTIF($J$2:$J$61,2)</x:f>
+      <x:c r="AP3" s="361" t="n">
+        <x:f>COUNTIF($J$2:$J$1001,2)</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AQ3" s="310" t="str">
+      <x:c r="AQ3" s="362" t="str">
         <x:v>Meta: 30</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="290"/>
-      <x:c r="B4" s="290"/>
-      <x:c r="C4" s="290"/>
-      <x:c r="D4" s="290" t="str">
+      <x:c r="A4" s="342"/>
+      <x:c r="B4" s="342"/>
+      <x:c r="C4" s="342"/>
+      <x:c r="D4" s="342" t="str">
         <x:f>IF($A4="Verdadero o Falso Simple","Verdadero",IF($A4="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A4="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E4" s="290" t="str">
+      <x:c r="E4" s="342" t="str">
         <x:f>IF($A4="Verdadero o Falso Simple","Falso",IF($A4="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A4="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F4" s="290" t="str">
+      <x:c r="F4" s="342" t="str">
         <x:f>IF($A4="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A4="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G4" s="290" t="str">
+      <x:c r="G4" s="342" t="str">
         <x:f>IF($A4="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A4="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H4" s="290" t="str">
+      <x:c r="H4" s="342" t="str">
         <x:f>IF($A4="Verdadero o Falso Simple","",IF($A4="Respuesta A/B/Ambas/Ninguna","",IF($A4="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I4" s="290"/>
-      <x:c r="J4" s="290" t="n">
+      <x:c r="I4" s="342"/>
+      <x:c r="J4" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K4" s="290" t="str">
+      <x:c r="K4" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L4" s="291"/>
-      <x:c r="M4" s="289"/>
+      <x:c r="L4" s="343" t="str">
+        <x:f>IF(TRIM($A4)="","",IF(COUNTIF($Q4:$AJ4,"?*")=0,"OK","Falta revisar: "&amp;$Q4&amp;$R4&amp;$S4&amp;$T4&amp;$U4&amp;$V4&amp;$W4&amp;$X4&amp;$Y4&amp;$Z4&amp;$AA4&amp;$AB4&amp;$AC4&amp;$AD4&amp;$AE4&amp;$AF4&amp;$AG4&amp;$AH4&amp;$AI4&amp;$AJ4))</x:f>
+      </x:c>
+      <x:c r="M4" s="341"/>
       <x:c r="N4"/>
       <x:c r="O4"/>
       <x:c r="P4"/>
@@ -2749,45 +2945,47 @@
       <x:c r="AN4" t="str">
         <x:f>IF(AND(OR($A4="Ítems agrupados por caso clínico o problema",$A4="Subítem de caso o problema",$A4="Emparejamiento Ampliado",$A4="Opción de Emparejamiento Ampliado"),TRIM($B4)=""),IF(COUNTIF($M4:$O4,"?*")&gt;0,", ","")&amp;"grupo","")</x:f>
       </x:c>
-      <x:c r="AO4" s="308" t="str">
+      <x:c r="AO4" s="360" t="str">
         <x:v>Difíciles (3)</x:v>
       </x:c>
-      <x:c r="AP4" s="309" t="n">
-        <x:f>COUNTIF($J$2:$J$61,3)</x:f>
+      <x:c r="AP4" s="361" t="n">
+        <x:f>COUNTIF($J$2:$J$1001,3)</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AQ4" s="310" t="str">
+      <x:c r="AQ4" s="362" t="str">
         <x:v>Meta: 15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="290"/>
-      <x:c r="B5" s="290"/>
-      <x:c r="C5" s="290"/>
-      <x:c r="D5" s="290" t="str">
+      <x:c r="A5" s="342"/>
+      <x:c r="B5" s="342"/>
+      <x:c r="C5" s="342"/>
+      <x:c r="D5" s="342" t="str">
         <x:f>IF($A5="Verdadero o Falso Simple","Verdadero",IF($A5="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A5="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E5" s="290" t="str">
+      <x:c r="E5" s="342" t="str">
         <x:f>IF($A5="Verdadero o Falso Simple","Falso",IF($A5="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A5="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F5" s="290" t="str">
+      <x:c r="F5" s="342" t="str">
         <x:f>IF($A5="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A5="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G5" s="290" t="str">
+      <x:c r="G5" s="342" t="str">
         <x:f>IF($A5="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A5="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H5" s="290" t="str">
+      <x:c r="H5" s="342" t="str">
         <x:f>IF($A5="Verdadero o Falso Simple","",IF($A5="Respuesta A/B/Ambas/Ninguna","",IF($A5="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I5" s="290"/>
-      <x:c r="J5" s="290" t="n">
+      <x:c r="I5" s="342"/>
+      <x:c r="J5" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5" s="290" t="str">
+      <x:c r="K5" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L5" s="291"/>
-      <x:c r="M5" s="289"/>
+      <x:c r="L5" s="343" t="str">
+        <x:f>IF(TRIM($A5)="","",IF(COUNTIF($Q5:$AJ5,"?*")=0,"OK","Falta revisar: "&amp;$Q5&amp;$R5&amp;$S5&amp;$T5&amp;$U5&amp;$V5&amp;$W5&amp;$X5&amp;$Y5&amp;$Z5&amp;$AA5&amp;$AB5&amp;$AC5&amp;$AD5&amp;$AE5&amp;$AF5&amp;$AG5&amp;$AH5&amp;$AI5&amp;$AJ5))</x:f>
+      </x:c>
+      <x:c r="M5" s="341"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
       <x:c r="P5"/>
@@ -2864,45 +3062,47 @@
       <x:c r="AN5" t="str">
         <x:f>IF(AND(OR($A5="Ítems agrupados por caso clínico o problema",$A5="Subítem de caso o problema",$A5="Emparejamiento Ampliado",$A5="Opción de Emparejamiento Ampliado"),TRIM($B5)=""),IF(COUNTIF($M5:$O5,"?*")&gt;0,", ","")&amp;"grupo","")</x:f>
       </x:c>
-      <x:c r="AO5" s="308" t="str">
+      <x:c r="AO5" s="360" t="str">
         <x:v>Total de ítems</x:v>
       </x:c>
-      <x:c r="AP5" s="309" t="n">
+      <x:c r="AP5" s="361" t="n">
         <x:f>SUM(AP2:AP4)</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="AQ5" s="310" t="str">
+      <x:c r="AQ5" s="362" t="str">
         <x:v>Meta: 60</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="290"/>
-      <x:c r="B6" s="290"/>
-      <x:c r="C6" s="290"/>
-      <x:c r="D6" s="290" t="str">
+      <x:c r="A6" s="342"/>
+      <x:c r="B6" s="342"/>
+      <x:c r="C6" s="342"/>
+      <x:c r="D6" s="342" t="str">
         <x:f>IF($A6="Verdadero o Falso Simple","Verdadero",IF($A6="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A6="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E6" s="290" t="str">
+      <x:c r="E6" s="342" t="str">
         <x:f>IF($A6="Verdadero o Falso Simple","Falso",IF($A6="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A6="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F6" s="290" t="str">
+      <x:c r="F6" s="342" t="str">
         <x:f>IF($A6="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A6="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G6" s="290" t="str">
+      <x:c r="G6" s="342" t="str">
         <x:f>IF($A6="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A6="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H6" s="290" t="str">
+      <x:c r="H6" s="342" t="str">
         <x:f>IF($A6="Verdadero o Falso Simple","",IF($A6="Respuesta A/B/Ambas/Ninguna","",IF($A6="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I6" s="290"/>
-      <x:c r="J6" s="290" t="n">
+      <x:c r="I6" s="342"/>
+      <x:c r="J6" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K6" s="290" t="str">
+      <x:c r="K6" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L6" s="291"/>
-      <x:c r="M6" s="289"/>
+      <x:c r="L6" s="343" t="str">
+        <x:f>IF(TRIM($A6)="","",IF(COUNTIF($Q6:$AJ6,"?*")=0,"OK","Falta revisar: "&amp;$Q6&amp;$R6&amp;$S6&amp;$T6&amp;$U6&amp;$V6&amp;$W6&amp;$X6&amp;$Y6&amp;$Z6&amp;$AA6&amp;$AB6&amp;$AC6&amp;$AD6&amp;$AE6&amp;$AF6&amp;$AG6&amp;$AH6&amp;$AI6&amp;$AJ6))</x:f>
+      </x:c>
+      <x:c r="M6" s="341"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
       <x:c r="P6"/>
@@ -2979,43 +3179,45 @@
       <x:c r="AN6" t="str">
         <x:f>IF(AND(OR($A6="Ítems agrupados por caso clínico o problema",$A6="Subítem de caso o problema",$A6="Emparejamiento Ampliado",$A6="Opción de Emparejamiento Ampliado"),TRIM($B6)=""),IF(COUNTIF($M6:$O6,"?*")&gt;0,", ","")&amp;"grupo","")</x:f>
       </x:c>
-      <x:c r="AO6" s="311" t="str">
+      <x:c r="AO6" s="363" t="str">
         <x:v>Estado</x:v>
       </x:c>
-      <x:c r="AP6" s="312" t="str">
+      <x:c r="AP6" s="364" t="str">
         <x:f>IF(AND(AP2=15,AP3=30,AP4=15,AP5=60),"COMPLETA","REVISAR")</x:f>
         <x:v>COMPLETA</x:v>
       </x:c>
-      <x:c r="AQ6" s="313" t="str"/>
+      <x:c r="AQ6" s="365" t="str"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="290"/>
-      <x:c r="B7" s="290"/>
-      <x:c r="C7" s="290"/>
-      <x:c r="D7" s="290" t="str">
+      <x:c r="A7" s="342"/>
+      <x:c r="B7" s="342"/>
+      <x:c r="C7" s="342"/>
+      <x:c r="D7" s="342" t="str">
         <x:f>IF($A7="Verdadero o Falso Simple","Verdadero",IF($A7="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A7="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E7" s="290" t="str">
+      <x:c r="E7" s="342" t="str">
         <x:f>IF($A7="Verdadero o Falso Simple","Falso",IF($A7="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A7="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F7" s="290" t="str">
+      <x:c r="F7" s="342" t="str">
         <x:f>IF($A7="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A7="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G7" s="290" t="str">
+      <x:c r="G7" s="342" t="str">
         <x:f>IF($A7="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A7="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H7" s="290" t="str">
+      <x:c r="H7" s="342" t="str">
         <x:f>IF($A7="Verdadero o Falso Simple","",IF($A7="Respuesta A/B/Ambas/Ninguna","",IF($A7="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I7" s="290"/>
-      <x:c r="J7" s="290" t="n">
+      <x:c r="I7" s="342"/>
+      <x:c r="J7" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K7" s="290" t="str">
+      <x:c r="K7" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L7" s="291"/>
-      <x:c r="M7" s="289"/>
+      <x:c r="L7" s="343" t="str">
+        <x:f>IF(TRIM($A7)="","",IF(COUNTIF($Q7:$AJ7,"?*")=0,"OK","Falta revisar: "&amp;$Q7&amp;$R7&amp;$S7&amp;$T7&amp;$U7&amp;$V7&amp;$W7&amp;$X7&amp;$Y7&amp;$Z7&amp;$AA7&amp;$AB7&amp;$AC7&amp;$AD7&amp;$AE7&amp;$AF7&amp;$AG7&amp;$AH7&amp;$AI7&amp;$AJ7))</x:f>
+      </x:c>
+      <x:c r="M7" s="341"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
       <x:c r="P7"/>
@@ -3094,33 +3296,35 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="290"/>
-      <x:c r="B8" s="290"/>
-      <x:c r="C8" s="290"/>
-      <x:c r="D8" s="290" t="str">
+      <x:c r="A8" s="342"/>
+      <x:c r="B8" s="342"/>
+      <x:c r="C8" s="342"/>
+      <x:c r="D8" s="342" t="str">
         <x:f>IF($A8="Verdadero o Falso Simple","Verdadero",IF($A8="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A8="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E8" s="290" t="str">
+      <x:c r="E8" s="342" t="str">
         <x:f>IF($A8="Verdadero o Falso Simple","Falso",IF($A8="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A8="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F8" s="290" t="str">
+      <x:c r="F8" s="342" t="str">
         <x:f>IF($A8="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A8="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G8" s="290" t="str">
+      <x:c r="G8" s="342" t="str">
         <x:f>IF($A8="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A8="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H8" s="290" t="str">
+      <x:c r="H8" s="342" t="str">
         <x:f>IF($A8="Verdadero o Falso Simple","",IF($A8="Respuesta A/B/Ambas/Ninguna","",IF($A8="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I8" s="290"/>
-      <x:c r="J8" s="290" t="n">
+      <x:c r="I8" s="342"/>
+      <x:c r="J8" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="290" t="str">
+      <x:c r="K8" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L8" s="291"/>
-      <x:c r="M8" s="289"/>
+      <x:c r="L8" s="343" t="str">
+        <x:f>IF(TRIM($A8)="","",IF(COUNTIF($Q8:$AJ8,"?*")=0,"OK","Falta revisar: "&amp;$Q8&amp;$R8&amp;$S8&amp;$T8&amp;$U8&amp;$V8&amp;$W8&amp;$X8&amp;$Y8&amp;$Z8&amp;$AA8&amp;$AB8&amp;$AC8&amp;$AD8&amp;$AE8&amp;$AF8&amp;$AG8&amp;$AH8&amp;$AI8&amp;$AJ8))</x:f>
+      </x:c>
+      <x:c r="M8" s="341"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
       <x:c r="P8"/>
@@ -3199,33 +3403,35 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="290"/>
-      <x:c r="B9" s="290"/>
-      <x:c r="C9" s="290"/>
-      <x:c r="D9" s="290" t="str">
+      <x:c r="A9" s="342"/>
+      <x:c r="B9" s="342"/>
+      <x:c r="C9" s="342"/>
+      <x:c r="D9" s="342" t="str">
         <x:f>IF($A9="Verdadero o Falso Simple","Verdadero",IF($A9="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A9="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E9" s="290" t="str">
+      <x:c r="E9" s="342" t="str">
         <x:f>IF($A9="Verdadero o Falso Simple","Falso",IF($A9="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A9="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F9" s="290" t="str">
+      <x:c r="F9" s="342" t="str">
         <x:f>IF($A9="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A9="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G9" s="290" t="str">
+      <x:c r="G9" s="342" t="str">
         <x:f>IF($A9="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A9="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H9" s="290" t="str">
+      <x:c r="H9" s="342" t="str">
         <x:f>IF($A9="Verdadero o Falso Simple","",IF($A9="Respuesta A/B/Ambas/Ninguna","",IF($A9="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I9" s="290"/>
-      <x:c r="J9" s="290" t="n">
+      <x:c r="I9" s="342"/>
+      <x:c r="J9" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K9" s="290" t="str">
+      <x:c r="K9" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L9" s="291"/>
-      <x:c r="M9" s="289"/>
+      <x:c r="L9" s="343" t="str">
+        <x:f>IF(TRIM($A9)="","",IF(COUNTIF($Q9:$AJ9,"?*")=0,"OK","Falta revisar: "&amp;$Q9&amp;$R9&amp;$S9&amp;$T9&amp;$U9&amp;$V9&amp;$W9&amp;$X9&amp;$Y9&amp;$Z9&amp;$AA9&amp;$AB9&amp;$AC9&amp;$AD9&amp;$AE9&amp;$AF9&amp;$AG9&amp;$AH9&amp;$AI9&amp;$AJ9))</x:f>
+      </x:c>
+      <x:c r="M9" s="341"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
@@ -3304,33 +3510,35 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="290"/>
-      <x:c r="B10" s="290"/>
-      <x:c r="C10" s="290"/>
-      <x:c r="D10" s="290" t="str">
+      <x:c r="A10" s="342"/>
+      <x:c r="B10" s="342"/>
+      <x:c r="C10" s="342"/>
+      <x:c r="D10" s="342" t="str">
         <x:f>IF($A10="Verdadero o Falso Simple","Verdadero",IF($A10="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A10="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E10" s="290" t="str">
+      <x:c r="E10" s="342" t="str">
         <x:f>IF($A10="Verdadero o Falso Simple","Falso",IF($A10="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A10="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F10" s="290" t="str">
+      <x:c r="F10" s="342" t="str">
         <x:f>IF($A10="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A10="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G10" s="290" t="str">
+      <x:c r="G10" s="342" t="str">
         <x:f>IF($A10="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A10="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H10" s="290" t="str">
+      <x:c r="H10" s="342" t="str">
         <x:f>IF($A10="Verdadero o Falso Simple","",IF($A10="Respuesta A/B/Ambas/Ninguna","",IF($A10="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I10" s="290"/>
-      <x:c r="J10" s="290" t="n">
+      <x:c r="I10" s="342"/>
+      <x:c r="J10" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="290" t="str">
+      <x:c r="K10" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L10" s="291"/>
-      <x:c r="M10" s="289"/>
+      <x:c r="L10" s="343" t="str">
+        <x:f>IF(TRIM($A10)="","",IF(COUNTIF($Q10:$AJ10,"?*")=0,"OK","Falta revisar: "&amp;$Q10&amp;$R10&amp;$S10&amp;$T10&amp;$U10&amp;$V10&amp;$W10&amp;$X10&amp;$Y10&amp;$Z10&amp;$AA10&amp;$AB10&amp;$AC10&amp;$AD10&amp;$AE10&amp;$AF10&amp;$AG10&amp;$AH10&amp;$AI10&amp;$AJ10))</x:f>
+      </x:c>
+      <x:c r="M10" s="341"/>
       <x:c r="N10"/>
       <x:c r="O10"/>
       <x:c r="P10"/>
@@ -3409,33 +3617,35 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="290"/>
-      <x:c r="B11" s="290"/>
-      <x:c r="C11" s="290"/>
-      <x:c r="D11" s="290" t="str">
+      <x:c r="A11" s="342"/>
+      <x:c r="B11" s="342"/>
+      <x:c r="C11" s="342"/>
+      <x:c r="D11" s="342" t="str">
         <x:f>IF($A11="Verdadero o Falso Simple","Verdadero",IF($A11="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A11="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E11" s="290" t="str">
+      <x:c r="E11" s="342" t="str">
         <x:f>IF($A11="Verdadero o Falso Simple","Falso",IF($A11="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A11="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F11" s="290" t="str">
+      <x:c r="F11" s="342" t="str">
         <x:f>IF($A11="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A11="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G11" s="290" t="str">
+      <x:c r="G11" s="342" t="str">
         <x:f>IF($A11="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A11="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H11" s="290" t="str">
+      <x:c r="H11" s="342" t="str">
         <x:f>IF($A11="Verdadero o Falso Simple","",IF($A11="Respuesta A/B/Ambas/Ninguna","",IF($A11="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I11" s="290"/>
-      <x:c r="J11" s="290" t="n">
+      <x:c r="I11" s="342"/>
+      <x:c r="J11" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="290" t="str">
+      <x:c r="K11" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L11" s="291"/>
-      <x:c r="M11" s="289"/>
+      <x:c r="L11" s="343" t="str">
+        <x:f>IF(TRIM($A11)="","",IF(COUNTIF($Q11:$AJ11,"?*")=0,"OK","Falta revisar: "&amp;$Q11&amp;$R11&amp;$S11&amp;$T11&amp;$U11&amp;$V11&amp;$W11&amp;$X11&amp;$Y11&amp;$Z11&amp;$AA11&amp;$AB11&amp;$AC11&amp;$AD11&amp;$AE11&amp;$AF11&amp;$AG11&amp;$AH11&amp;$AI11&amp;$AJ11))</x:f>
+      </x:c>
+      <x:c r="M11" s="341"/>
       <x:c r="N11"/>
       <x:c r="O11"/>
       <x:c r="P11"/>
@@ -3514,33 +3724,35 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="290"/>
-      <x:c r="B12" s="290"/>
-      <x:c r="C12" s="290"/>
-      <x:c r="D12" s="290" t="str">
+      <x:c r="A12" s="342"/>
+      <x:c r="B12" s="342"/>
+      <x:c r="C12" s="342"/>
+      <x:c r="D12" s="342" t="str">
         <x:f>IF($A12="Verdadero o Falso Simple","Verdadero",IF($A12="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A12="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E12" s="290" t="str">
+      <x:c r="E12" s="342" t="str">
         <x:f>IF($A12="Verdadero o Falso Simple","Falso",IF($A12="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A12="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F12" s="290" t="str">
+      <x:c r="F12" s="342" t="str">
         <x:f>IF($A12="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A12="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G12" s="290" t="str">
+      <x:c r="G12" s="342" t="str">
         <x:f>IF($A12="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A12="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H12" s="290" t="str">
+      <x:c r="H12" s="342" t="str">
         <x:f>IF($A12="Verdadero o Falso Simple","",IF($A12="Respuesta A/B/Ambas/Ninguna","",IF($A12="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I12" s="290"/>
-      <x:c r="J12" s="290" t="n">
+      <x:c r="I12" s="342"/>
+      <x:c r="J12" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="290" t="str">
+      <x:c r="K12" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L12" s="291"/>
-      <x:c r="M12" s="289"/>
+      <x:c r="L12" s="343" t="str">
+        <x:f>IF(TRIM($A12)="","",IF(COUNTIF($Q12:$AJ12,"?*")=0,"OK","Falta revisar: "&amp;$Q12&amp;$R12&amp;$S12&amp;$T12&amp;$U12&amp;$V12&amp;$W12&amp;$X12&amp;$Y12&amp;$Z12&amp;$AA12&amp;$AB12&amp;$AC12&amp;$AD12&amp;$AE12&amp;$AF12&amp;$AG12&amp;$AH12&amp;$AI12&amp;$AJ12))</x:f>
+      </x:c>
+      <x:c r="M12" s="341"/>
       <x:c r="N12"/>
       <x:c r="O12"/>
       <x:c r="P12"/>
@@ -3619,33 +3831,35 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="290"/>
-      <x:c r="B13" s="290"/>
-      <x:c r="C13" s="290"/>
-      <x:c r="D13" s="290" t="str">
+      <x:c r="A13" s="342"/>
+      <x:c r="B13" s="342"/>
+      <x:c r="C13" s="342"/>
+      <x:c r="D13" s="342" t="str">
         <x:f>IF($A13="Verdadero o Falso Simple","Verdadero",IF($A13="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A13="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E13" s="290" t="str">
+      <x:c r="E13" s="342" t="str">
         <x:f>IF($A13="Verdadero o Falso Simple","Falso",IF($A13="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A13="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F13" s="290" t="str">
+      <x:c r="F13" s="342" t="str">
         <x:f>IF($A13="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A13="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G13" s="290" t="str">
+      <x:c r="G13" s="342" t="str">
         <x:f>IF($A13="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A13="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H13" s="290" t="str">
+      <x:c r="H13" s="342" t="str">
         <x:f>IF($A13="Verdadero o Falso Simple","",IF($A13="Respuesta A/B/Ambas/Ninguna","",IF($A13="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I13" s="290"/>
-      <x:c r="J13" s="290" t="n">
+      <x:c r="I13" s="342"/>
+      <x:c r="J13" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="290" t="str">
+      <x:c r="K13" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L13" s="291"/>
-      <x:c r="M13" s="289"/>
+      <x:c r="L13" s="343" t="str">
+        <x:f>IF(TRIM($A13)="","",IF(COUNTIF($Q13:$AJ13,"?*")=0,"OK","Falta revisar: "&amp;$Q13&amp;$R13&amp;$S13&amp;$T13&amp;$U13&amp;$V13&amp;$W13&amp;$X13&amp;$Y13&amp;$Z13&amp;$AA13&amp;$AB13&amp;$AC13&amp;$AD13&amp;$AE13&amp;$AF13&amp;$AG13&amp;$AH13&amp;$AI13&amp;$AJ13))</x:f>
+      </x:c>
+      <x:c r="M13" s="341"/>
       <x:c r="N13"/>
       <x:c r="O13"/>
       <x:c r="P13"/>
@@ -3724,33 +3938,35 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="290"/>
-      <x:c r="B14" s="290"/>
-      <x:c r="C14" s="290"/>
-      <x:c r="D14" s="290" t="str">
+      <x:c r="A14" s="342"/>
+      <x:c r="B14" s="342"/>
+      <x:c r="C14" s="342"/>
+      <x:c r="D14" s="342" t="str">
         <x:f>IF($A14="Verdadero o Falso Simple","Verdadero",IF($A14="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A14="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E14" s="290" t="str">
+      <x:c r="E14" s="342" t="str">
         <x:f>IF($A14="Verdadero o Falso Simple","Falso",IF($A14="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A14="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F14" s="290" t="str">
+      <x:c r="F14" s="342" t="str">
         <x:f>IF($A14="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A14="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G14" s="290" t="str">
+      <x:c r="G14" s="342" t="str">
         <x:f>IF($A14="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A14="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H14" s="290" t="str">
+      <x:c r="H14" s="342" t="str">
         <x:f>IF($A14="Verdadero o Falso Simple","",IF($A14="Respuesta A/B/Ambas/Ninguna","",IF($A14="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I14" s="290"/>
-      <x:c r="J14" s="290" t="n">
+      <x:c r="I14" s="342"/>
+      <x:c r="J14" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K14" s="290" t="str">
+      <x:c r="K14" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L14" s="291"/>
-      <x:c r="M14" s="289"/>
+      <x:c r="L14" s="343" t="str">
+        <x:f>IF(TRIM($A14)="","",IF(COUNTIF($Q14:$AJ14,"?*")=0,"OK","Falta revisar: "&amp;$Q14&amp;$R14&amp;$S14&amp;$T14&amp;$U14&amp;$V14&amp;$W14&amp;$X14&amp;$Y14&amp;$Z14&amp;$AA14&amp;$AB14&amp;$AC14&amp;$AD14&amp;$AE14&amp;$AF14&amp;$AG14&amp;$AH14&amp;$AI14&amp;$AJ14))</x:f>
+      </x:c>
+      <x:c r="M14" s="341"/>
       <x:c r="N14"/>
       <x:c r="O14"/>
       <x:c r="P14"/>
@@ -3829,33 +4045,35 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="290"/>
-      <x:c r="B15" s="290"/>
-      <x:c r="C15" s="290"/>
-      <x:c r="D15" s="290" t="str">
+      <x:c r="A15" s="342"/>
+      <x:c r="B15" s="342"/>
+      <x:c r="C15" s="342"/>
+      <x:c r="D15" s="342" t="str">
         <x:f>IF($A15="Verdadero o Falso Simple","Verdadero",IF($A15="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A15="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E15" s="290" t="str">
+      <x:c r="E15" s="342" t="str">
         <x:f>IF($A15="Verdadero o Falso Simple","Falso",IF($A15="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A15="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F15" s="290" t="str">
+      <x:c r="F15" s="342" t="str">
         <x:f>IF($A15="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A15="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G15" s="290" t="str">
+      <x:c r="G15" s="342" t="str">
         <x:f>IF($A15="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A15="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H15" s="290" t="str">
+      <x:c r="H15" s="342" t="str">
         <x:f>IF($A15="Verdadero o Falso Simple","",IF($A15="Respuesta A/B/Ambas/Ninguna","",IF($A15="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I15" s="290"/>
-      <x:c r="J15" s="290" t="n">
+      <x:c r="I15" s="342"/>
+      <x:c r="J15" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="290" t="str">
+      <x:c r="K15" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L15" s="291"/>
-      <x:c r="M15" s="289"/>
+      <x:c r="L15" s="343" t="str">
+        <x:f>IF(TRIM($A15)="","",IF(COUNTIF($Q15:$AJ15,"?*")=0,"OK","Falta revisar: "&amp;$Q15&amp;$R15&amp;$S15&amp;$T15&amp;$U15&amp;$V15&amp;$W15&amp;$X15&amp;$Y15&amp;$Z15&amp;$AA15&amp;$AB15&amp;$AC15&amp;$AD15&amp;$AE15&amp;$AF15&amp;$AG15&amp;$AH15&amp;$AI15&amp;$AJ15))</x:f>
+      </x:c>
+      <x:c r="M15" s="341"/>
       <x:c r="N15"/>
       <x:c r="O15"/>
       <x:c r="P15"/>
@@ -3934,33 +4152,35 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="290"/>
-      <x:c r="B16" s="290"/>
-      <x:c r="C16" s="290"/>
-      <x:c r="D16" s="290" t="str">
+      <x:c r="A16" s="342"/>
+      <x:c r="B16" s="342"/>
+      <x:c r="C16" s="342"/>
+      <x:c r="D16" s="342" t="str">
         <x:f>IF($A16="Verdadero o Falso Simple","Verdadero",IF($A16="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A16="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E16" s="290" t="str">
+      <x:c r="E16" s="342" t="str">
         <x:f>IF($A16="Verdadero o Falso Simple","Falso",IF($A16="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A16="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F16" s="290" t="str">
+      <x:c r="F16" s="342" t="str">
         <x:f>IF($A16="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A16="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G16" s="290" t="str">
+      <x:c r="G16" s="342" t="str">
         <x:f>IF($A16="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A16="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H16" s="290" t="str">
+      <x:c r="H16" s="342" t="str">
         <x:f>IF($A16="Verdadero o Falso Simple","",IF($A16="Respuesta A/B/Ambas/Ninguna","",IF($A16="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I16" s="290"/>
-      <x:c r="J16" s="290" t="n">
+      <x:c r="I16" s="342"/>
+      <x:c r="J16" s="342" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="290" t="str">
+      <x:c r="K16" s="342" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L16" s="291"/>
-      <x:c r="M16" s="289"/>
+      <x:c r="L16" s="343" t="str">
+        <x:f>IF(TRIM($A16)="","",IF(COUNTIF($Q16:$AJ16,"?*")=0,"OK","Falta revisar: "&amp;$Q16&amp;$R16&amp;$S16&amp;$T16&amp;$U16&amp;$V16&amp;$W16&amp;$X16&amp;$Y16&amp;$Z16&amp;$AA16&amp;$AB16&amp;$AC16&amp;$AD16&amp;$AE16&amp;$AF16&amp;$AG16&amp;$AH16&amp;$AI16&amp;$AJ16))</x:f>
+      </x:c>
+      <x:c r="M16" s="341"/>
       <x:c r="N16"/>
       <x:c r="O16"/>
       <x:c r="P16"/>
@@ -4039,33 +4259,35 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="292"/>
-      <x:c r="B17" s="292"/>
-      <x:c r="C17" s="292"/>
-      <x:c r="D17" s="292" t="str">
+      <x:c r="A17" s="344"/>
+      <x:c r="B17" s="344"/>
+      <x:c r="C17" s="344"/>
+      <x:c r="D17" s="344" t="str">
         <x:f>IF($A17="Verdadero o Falso Simple","Verdadero",IF($A17="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A17="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E17" s="292" t="str">
+      <x:c r="E17" s="344" t="str">
         <x:f>IF($A17="Verdadero o Falso Simple","Falso",IF($A17="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A17="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F17" s="292" t="str">
+      <x:c r="F17" s="344" t="str">
         <x:f>IF($A17="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A17="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G17" s="292" t="str">
+      <x:c r="G17" s="344" t="str">
         <x:f>IF($A17="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A17="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H17" s="292" t="str">
+      <x:c r="H17" s="344" t="str">
         <x:f>IF($A17="Verdadero o Falso Simple","",IF($A17="Respuesta A/B/Ambas/Ninguna","",IF($A17="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I17" s="292"/>
-      <x:c r="J17" s="292" t="n">
+      <x:c r="I17" s="344"/>
+      <x:c r="J17" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K17" s="292" t="str">
+      <x:c r="K17" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L17" s="293"/>
-      <x:c r="M17" s="289"/>
+      <x:c r="L17" s="345" t="str">
+        <x:f>IF(TRIM($A17)="","",IF(COUNTIF($Q17:$AJ17,"?*")=0,"OK","Falta revisar: "&amp;$Q17&amp;$R17&amp;$S17&amp;$T17&amp;$U17&amp;$V17&amp;$W17&amp;$X17&amp;$Y17&amp;$Z17&amp;$AA17&amp;$AB17&amp;$AC17&amp;$AD17&amp;$AE17&amp;$AF17&amp;$AG17&amp;$AH17&amp;$AI17&amp;$AJ17))</x:f>
+      </x:c>
+      <x:c r="M17" s="341"/>
       <x:c r="N17"/>
       <x:c r="O17"/>
       <x:c r="P17"/>
@@ -4144,33 +4366,35 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="292"/>
-      <x:c r="B18" s="292"/>
-      <x:c r="C18" s="292"/>
-      <x:c r="D18" s="292" t="str">
+      <x:c r="A18" s="344"/>
+      <x:c r="B18" s="344"/>
+      <x:c r="C18" s="344"/>
+      <x:c r="D18" s="344" t="str">
         <x:f>IF($A18="Verdadero o Falso Simple","Verdadero",IF($A18="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A18="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E18" s="292" t="str">
+      <x:c r="E18" s="344" t="str">
         <x:f>IF($A18="Verdadero o Falso Simple","Falso",IF($A18="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A18="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F18" s="292" t="str">
+      <x:c r="F18" s="344" t="str">
         <x:f>IF($A18="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A18="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G18" s="292" t="str">
+      <x:c r="G18" s="344" t="str">
         <x:f>IF($A18="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A18="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H18" s="292" t="str">
+      <x:c r="H18" s="344" t="str">
         <x:f>IF($A18="Verdadero o Falso Simple","",IF($A18="Respuesta A/B/Ambas/Ninguna","",IF($A18="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I18" s="292"/>
-      <x:c r="J18" s="292" t="n">
+      <x:c r="I18" s="344"/>
+      <x:c r="J18" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K18" s="292" t="str">
+      <x:c r="K18" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L18" s="293"/>
-      <x:c r="M18" s="289"/>
+      <x:c r="L18" s="345" t="str">
+        <x:f>IF(TRIM($A18)="","",IF(COUNTIF($Q18:$AJ18,"?*")=0,"OK","Falta revisar: "&amp;$Q18&amp;$R18&amp;$S18&amp;$T18&amp;$U18&amp;$V18&amp;$W18&amp;$X18&amp;$Y18&amp;$Z18&amp;$AA18&amp;$AB18&amp;$AC18&amp;$AD18&amp;$AE18&amp;$AF18&amp;$AG18&amp;$AH18&amp;$AI18&amp;$AJ18))</x:f>
+      </x:c>
+      <x:c r="M18" s="341"/>
       <x:c r="N18"/>
       <x:c r="O18"/>
       <x:c r="P18"/>
@@ -4249,33 +4473,35 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="292"/>
-      <x:c r="B19" s="292"/>
-      <x:c r="C19" s="292"/>
-      <x:c r="D19" s="292" t="str">
+      <x:c r="A19" s="344"/>
+      <x:c r="B19" s="344"/>
+      <x:c r="C19" s="344"/>
+      <x:c r="D19" s="344" t="str">
         <x:f>IF($A19="Verdadero o Falso Simple","Verdadero",IF($A19="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A19="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E19" s="292" t="str">
+      <x:c r="E19" s="344" t="str">
         <x:f>IF($A19="Verdadero o Falso Simple","Falso",IF($A19="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A19="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F19" s="292" t="str">
+      <x:c r="F19" s="344" t="str">
         <x:f>IF($A19="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A19="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G19" s="292" t="str">
+      <x:c r="G19" s="344" t="str">
         <x:f>IF($A19="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A19="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H19" s="292" t="str">
+      <x:c r="H19" s="344" t="str">
         <x:f>IF($A19="Verdadero o Falso Simple","",IF($A19="Respuesta A/B/Ambas/Ninguna","",IF($A19="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I19" s="292"/>
-      <x:c r="J19" s="292" t="n">
+      <x:c r="I19" s="344"/>
+      <x:c r="J19" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K19" s="292" t="str">
+      <x:c r="K19" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L19" s="293"/>
-      <x:c r="M19" s="289"/>
+      <x:c r="L19" s="345" t="str">
+        <x:f>IF(TRIM($A19)="","",IF(COUNTIF($Q19:$AJ19,"?*")=0,"OK","Falta revisar: "&amp;$Q19&amp;$R19&amp;$S19&amp;$T19&amp;$U19&amp;$V19&amp;$W19&amp;$X19&amp;$Y19&amp;$Z19&amp;$AA19&amp;$AB19&amp;$AC19&amp;$AD19&amp;$AE19&amp;$AF19&amp;$AG19&amp;$AH19&amp;$AI19&amp;$AJ19))</x:f>
+      </x:c>
+      <x:c r="M19" s="341"/>
       <x:c r="N19"/>
       <x:c r="O19"/>
       <x:c r="P19"/>
@@ -4354,33 +4580,35 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="292"/>
-      <x:c r="B20" s="292"/>
-      <x:c r="C20" s="292"/>
-      <x:c r="D20" s="292" t="str">
+      <x:c r="A20" s="344"/>
+      <x:c r="B20" s="344"/>
+      <x:c r="C20" s="344"/>
+      <x:c r="D20" s="344" t="str">
         <x:f>IF($A20="Verdadero o Falso Simple","Verdadero",IF($A20="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A20="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E20" s="292" t="str">
+      <x:c r="E20" s="344" t="str">
         <x:f>IF($A20="Verdadero o Falso Simple","Falso",IF($A20="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A20="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F20" s="292" t="str">
+      <x:c r="F20" s="344" t="str">
         <x:f>IF($A20="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A20="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G20" s="292" t="str">
+      <x:c r="G20" s="344" t="str">
         <x:f>IF($A20="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A20="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H20" s="292" t="str">
+      <x:c r="H20" s="344" t="str">
         <x:f>IF($A20="Verdadero o Falso Simple","",IF($A20="Respuesta A/B/Ambas/Ninguna","",IF($A20="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I20" s="292"/>
-      <x:c r="J20" s="292" t="n">
+      <x:c r="I20" s="344"/>
+      <x:c r="J20" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K20" s="292" t="str">
+      <x:c r="K20" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L20" s="293"/>
-      <x:c r="M20" s="289"/>
+      <x:c r="L20" s="345" t="str">
+        <x:f>IF(TRIM($A20)="","",IF(COUNTIF($Q20:$AJ20,"?*")=0,"OK","Falta revisar: "&amp;$Q20&amp;$R20&amp;$S20&amp;$T20&amp;$U20&amp;$V20&amp;$W20&amp;$X20&amp;$Y20&amp;$Z20&amp;$AA20&amp;$AB20&amp;$AC20&amp;$AD20&amp;$AE20&amp;$AF20&amp;$AG20&amp;$AH20&amp;$AI20&amp;$AJ20))</x:f>
+      </x:c>
+      <x:c r="M20" s="341"/>
       <x:c r="N20"/>
       <x:c r="O20"/>
       <x:c r="P20"/>
@@ -4459,33 +4687,35 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="292"/>
-      <x:c r="B21" s="292"/>
-      <x:c r="C21" s="292"/>
-      <x:c r="D21" s="292" t="str">
+      <x:c r="A21" s="344"/>
+      <x:c r="B21" s="344"/>
+      <x:c r="C21" s="344"/>
+      <x:c r="D21" s="344" t="str">
         <x:f>IF($A21="Verdadero o Falso Simple","Verdadero",IF($A21="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A21="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E21" s="292" t="str">
+      <x:c r="E21" s="344" t="str">
         <x:f>IF($A21="Verdadero o Falso Simple","Falso",IF($A21="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A21="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F21" s="292" t="str">
+      <x:c r="F21" s="344" t="str">
         <x:f>IF($A21="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A21="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G21" s="292" t="str">
+      <x:c r="G21" s="344" t="str">
         <x:f>IF($A21="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A21="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H21" s="292" t="str">
+      <x:c r="H21" s="344" t="str">
         <x:f>IF($A21="Verdadero o Falso Simple","",IF($A21="Respuesta A/B/Ambas/Ninguna","",IF($A21="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I21" s="292"/>
-      <x:c r="J21" s="292" t="n">
+      <x:c r="I21" s="344"/>
+      <x:c r="J21" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K21" s="292" t="str">
+      <x:c r="K21" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L21" s="293"/>
-      <x:c r="M21" s="289"/>
+      <x:c r="L21" s="345" t="str">
+        <x:f>IF(TRIM($A21)="","",IF(COUNTIF($Q21:$AJ21,"?*")=0,"OK","Falta revisar: "&amp;$Q21&amp;$R21&amp;$S21&amp;$T21&amp;$U21&amp;$V21&amp;$W21&amp;$X21&amp;$Y21&amp;$Z21&amp;$AA21&amp;$AB21&amp;$AC21&amp;$AD21&amp;$AE21&amp;$AF21&amp;$AG21&amp;$AH21&amp;$AI21&amp;$AJ21))</x:f>
+      </x:c>
+      <x:c r="M21" s="341"/>
       <x:c r="N21"/>
       <x:c r="O21"/>
       <x:c r="P21"/>
@@ -4564,33 +4794,35 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="292"/>
-      <x:c r="B22" s="292"/>
-      <x:c r="C22" s="292"/>
-      <x:c r="D22" s="292" t="str">
+      <x:c r="A22" s="344"/>
+      <x:c r="B22" s="344"/>
+      <x:c r="C22" s="344"/>
+      <x:c r="D22" s="344" t="str">
         <x:f>IF($A22="Verdadero o Falso Simple","Verdadero",IF($A22="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A22="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E22" s="292" t="str">
+      <x:c r="E22" s="344" t="str">
         <x:f>IF($A22="Verdadero o Falso Simple","Falso",IF($A22="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A22="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F22" s="292" t="str">
+      <x:c r="F22" s="344" t="str">
         <x:f>IF($A22="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A22="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G22" s="292" t="str">
+      <x:c r="G22" s="344" t="str">
         <x:f>IF($A22="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A22="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H22" s="292" t="str">
+      <x:c r="H22" s="344" t="str">
         <x:f>IF($A22="Verdadero o Falso Simple","",IF($A22="Respuesta A/B/Ambas/Ninguna","",IF($A22="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I22" s="292"/>
-      <x:c r="J22" s="292" t="n">
+      <x:c r="I22" s="344"/>
+      <x:c r="J22" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K22" s="292" t="str">
+      <x:c r="K22" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L22" s="293"/>
-      <x:c r="M22" s="289"/>
+      <x:c r="L22" s="345" t="str">
+        <x:f>IF(TRIM($A22)="","",IF(COUNTIF($Q22:$AJ22,"?*")=0,"OK","Falta revisar: "&amp;$Q22&amp;$R22&amp;$S22&amp;$T22&amp;$U22&amp;$V22&amp;$W22&amp;$X22&amp;$Y22&amp;$Z22&amp;$AA22&amp;$AB22&amp;$AC22&amp;$AD22&amp;$AE22&amp;$AF22&amp;$AG22&amp;$AH22&amp;$AI22&amp;$AJ22))</x:f>
+      </x:c>
+      <x:c r="M22" s="341"/>
       <x:c r="N22"/>
       <x:c r="O22"/>
       <x:c r="P22"/>
@@ -4669,33 +4901,35 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="292"/>
-      <x:c r="B23" s="292"/>
-      <x:c r="C23" s="292"/>
-      <x:c r="D23" s="292" t="str">
+      <x:c r="A23" s="344"/>
+      <x:c r="B23" s="344"/>
+      <x:c r="C23" s="344"/>
+      <x:c r="D23" s="344" t="str">
         <x:f>IF($A23="Verdadero o Falso Simple","Verdadero",IF($A23="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A23="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E23" s="292" t="str">
+      <x:c r="E23" s="344" t="str">
         <x:f>IF($A23="Verdadero o Falso Simple","Falso",IF($A23="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A23="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F23" s="292" t="str">
+      <x:c r="F23" s="344" t="str">
         <x:f>IF($A23="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A23="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G23" s="292" t="str">
+      <x:c r="G23" s="344" t="str">
         <x:f>IF($A23="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A23="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H23" s="292" t="str">
+      <x:c r="H23" s="344" t="str">
         <x:f>IF($A23="Verdadero o Falso Simple","",IF($A23="Respuesta A/B/Ambas/Ninguna","",IF($A23="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I23" s="292"/>
-      <x:c r="J23" s="292" t="n">
+      <x:c r="I23" s="344"/>
+      <x:c r="J23" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K23" s="292" t="str">
+      <x:c r="K23" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L23" s="293"/>
-      <x:c r="M23" s="289"/>
+      <x:c r="L23" s="345" t="str">
+        <x:f>IF(TRIM($A23)="","",IF(COUNTIF($Q23:$AJ23,"?*")=0,"OK","Falta revisar: "&amp;$Q23&amp;$R23&amp;$S23&amp;$T23&amp;$U23&amp;$V23&amp;$W23&amp;$X23&amp;$Y23&amp;$Z23&amp;$AA23&amp;$AB23&amp;$AC23&amp;$AD23&amp;$AE23&amp;$AF23&amp;$AG23&amp;$AH23&amp;$AI23&amp;$AJ23))</x:f>
+      </x:c>
+      <x:c r="M23" s="341"/>
       <x:c r="N23"/>
       <x:c r="O23"/>
       <x:c r="P23"/>
@@ -4774,33 +5008,35 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="292"/>
-      <x:c r="B24" s="292"/>
-      <x:c r="C24" s="292"/>
-      <x:c r="D24" s="292" t="str">
+      <x:c r="A24" s="344"/>
+      <x:c r="B24" s="344"/>
+      <x:c r="C24" s="344"/>
+      <x:c r="D24" s="344" t="str">
         <x:f>IF($A24="Verdadero o Falso Simple","Verdadero",IF($A24="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A24="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E24" s="292" t="str">
+      <x:c r="E24" s="344" t="str">
         <x:f>IF($A24="Verdadero o Falso Simple","Falso",IF($A24="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A24="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F24" s="292" t="str">
+      <x:c r="F24" s="344" t="str">
         <x:f>IF($A24="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A24="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G24" s="292" t="str">
+      <x:c r="G24" s="344" t="str">
         <x:f>IF($A24="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A24="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H24" s="292" t="str">
+      <x:c r="H24" s="344" t="str">
         <x:f>IF($A24="Verdadero o Falso Simple","",IF($A24="Respuesta A/B/Ambas/Ninguna","",IF($A24="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I24" s="292"/>
-      <x:c r="J24" s="292" t="n">
+      <x:c r="I24" s="344"/>
+      <x:c r="J24" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K24" s="292" t="str">
+      <x:c r="K24" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L24" s="293"/>
-      <x:c r="M24" s="289"/>
+      <x:c r="L24" s="345" t="str">
+        <x:f>IF(TRIM($A24)="","",IF(COUNTIF($Q24:$AJ24,"?*")=0,"OK","Falta revisar: "&amp;$Q24&amp;$R24&amp;$S24&amp;$T24&amp;$U24&amp;$V24&amp;$W24&amp;$X24&amp;$Y24&amp;$Z24&amp;$AA24&amp;$AB24&amp;$AC24&amp;$AD24&amp;$AE24&amp;$AF24&amp;$AG24&amp;$AH24&amp;$AI24&amp;$AJ24))</x:f>
+      </x:c>
+      <x:c r="M24" s="341"/>
       <x:c r="N24"/>
       <x:c r="O24"/>
       <x:c r="P24"/>
@@ -4879,33 +5115,35 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="292"/>
-      <x:c r="B25" s="292"/>
-      <x:c r="C25" s="292"/>
-      <x:c r="D25" s="292" t="str">
+      <x:c r="A25" s="344"/>
+      <x:c r="B25" s="344"/>
+      <x:c r="C25" s="344"/>
+      <x:c r="D25" s="344" t="str">
         <x:f>IF($A25="Verdadero o Falso Simple","Verdadero",IF($A25="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A25="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E25" s="292" t="str">
+      <x:c r="E25" s="344" t="str">
         <x:f>IF($A25="Verdadero o Falso Simple","Falso",IF($A25="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A25="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F25" s="292" t="str">
+      <x:c r="F25" s="344" t="str">
         <x:f>IF($A25="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A25="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G25" s="292" t="str">
+      <x:c r="G25" s="344" t="str">
         <x:f>IF($A25="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A25="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H25" s="292" t="str">
+      <x:c r="H25" s="344" t="str">
         <x:f>IF($A25="Verdadero o Falso Simple","",IF($A25="Respuesta A/B/Ambas/Ninguna","",IF($A25="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I25" s="292"/>
-      <x:c r="J25" s="292" t="n">
+      <x:c r="I25" s="344"/>
+      <x:c r="J25" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K25" s="292" t="str">
+      <x:c r="K25" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L25" s="293"/>
-      <x:c r="M25" s="289"/>
+      <x:c r="L25" s="345" t="str">
+        <x:f>IF(TRIM($A25)="","",IF(COUNTIF($Q25:$AJ25,"?*")=0,"OK","Falta revisar: "&amp;$Q25&amp;$R25&amp;$S25&amp;$T25&amp;$U25&amp;$V25&amp;$W25&amp;$X25&amp;$Y25&amp;$Z25&amp;$AA25&amp;$AB25&amp;$AC25&amp;$AD25&amp;$AE25&amp;$AF25&amp;$AG25&amp;$AH25&amp;$AI25&amp;$AJ25))</x:f>
+      </x:c>
+      <x:c r="M25" s="341"/>
       <x:c r="N25"/>
       <x:c r="O25"/>
       <x:c r="P25"/>
@@ -4984,33 +5222,35 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="292"/>
-      <x:c r="B26" s="292"/>
-      <x:c r="C26" s="292"/>
-      <x:c r="D26" s="292" t="str">
+      <x:c r="A26" s="344"/>
+      <x:c r="B26" s="344"/>
+      <x:c r="C26" s="344"/>
+      <x:c r="D26" s="344" t="str">
         <x:f>IF($A26="Verdadero o Falso Simple","Verdadero",IF($A26="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A26="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E26" s="292" t="str">
+      <x:c r="E26" s="344" t="str">
         <x:f>IF($A26="Verdadero o Falso Simple","Falso",IF($A26="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A26="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F26" s="292" t="str">
+      <x:c r="F26" s="344" t="str">
         <x:f>IF($A26="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A26="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G26" s="292" t="str">
+      <x:c r="G26" s="344" t="str">
         <x:f>IF($A26="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A26="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H26" s="292" t="str">
+      <x:c r="H26" s="344" t="str">
         <x:f>IF($A26="Verdadero o Falso Simple","",IF($A26="Respuesta A/B/Ambas/Ninguna","",IF($A26="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I26" s="292"/>
-      <x:c r="J26" s="292" t="n">
+      <x:c r="I26" s="344"/>
+      <x:c r="J26" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K26" s="292" t="str">
+      <x:c r="K26" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L26" s="293"/>
-      <x:c r="M26" s="289"/>
+      <x:c r="L26" s="345" t="str">
+        <x:f>IF(TRIM($A26)="","",IF(COUNTIF($Q26:$AJ26,"?*")=0,"OK","Falta revisar: "&amp;$Q26&amp;$R26&amp;$S26&amp;$T26&amp;$U26&amp;$V26&amp;$W26&amp;$X26&amp;$Y26&amp;$Z26&amp;$AA26&amp;$AB26&amp;$AC26&amp;$AD26&amp;$AE26&amp;$AF26&amp;$AG26&amp;$AH26&amp;$AI26&amp;$AJ26))</x:f>
+      </x:c>
+      <x:c r="M26" s="341"/>
       <x:c r="N26"/>
       <x:c r="O26"/>
       <x:c r="P26"/>
@@ -5089,33 +5329,35 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="292"/>
-      <x:c r="B27" s="292"/>
-      <x:c r="C27" s="292"/>
-      <x:c r="D27" s="292" t="str">
+      <x:c r="A27" s="344"/>
+      <x:c r="B27" s="344"/>
+      <x:c r="C27" s="344"/>
+      <x:c r="D27" s="344" t="str">
         <x:f>IF($A27="Verdadero o Falso Simple","Verdadero",IF($A27="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A27="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E27" s="292" t="str">
+      <x:c r="E27" s="344" t="str">
         <x:f>IF($A27="Verdadero o Falso Simple","Falso",IF($A27="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A27="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F27" s="292" t="str">
+      <x:c r="F27" s="344" t="str">
         <x:f>IF($A27="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A27="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G27" s="292" t="str">
+      <x:c r="G27" s="344" t="str">
         <x:f>IF($A27="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A27="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H27" s="292" t="str">
+      <x:c r="H27" s="344" t="str">
         <x:f>IF($A27="Verdadero o Falso Simple","",IF($A27="Respuesta A/B/Ambas/Ninguna","",IF($A27="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I27" s="292"/>
-      <x:c r="J27" s="292" t="n">
+      <x:c r="I27" s="344"/>
+      <x:c r="J27" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K27" s="292" t="str">
+      <x:c r="K27" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L27" s="293"/>
-      <x:c r="M27" s="289"/>
+      <x:c r="L27" s="345" t="str">
+        <x:f>IF(TRIM($A27)="","",IF(COUNTIF($Q27:$AJ27,"?*")=0,"OK","Falta revisar: "&amp;$Q27&amp;$R27&amp;$S27&amp;$T27&amp;$U27&amp;$V27&amp;$W27&amp;$X27&amp;$Y27&amp;$Z27&amp;$AA27&amp;$AB27&amp;$AC27&amp;$AD27&amp;$AE27&amp;$AF27&amp;$AG27&amp;$AH27&amp;$AI27&amp;$AJ27))</x:f>
+      </x:c>
+      <x:c r="M27" s="341"/>
       <x:c r="N27"/>
       <x:c r="O27"/>
       <x:c r="P27"/>
@@ -5194,33 +5436,35 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="292"/>
-      <x:c r="B28" s="292"/>
-      <x:c r="C28" s="292"/>
-      <x:c r="D28" s="292" t="str">
+      <x:c r="A28" s="344"/>
+      <x:c r="B28" s="344"/>
+      <x:c r="C28" s="344"/>
+      <x:c r="D28" s="344" t="str">
         <x:f>IF($A28="Verdadero o Falso Simple","Verdadero",IF($A28="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A28="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E28" s="292" t="str">
+      <x:c r="E28" s="344" t="str">
         <x:f>IF($A28="Verdadero o Falso Simple","Falso",IF($A28="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A28="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F28" s="292" t="str">
+      <x:c r="F28" s="344" t="str">
         <x:f>IF($A28="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A28="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G28" s="292" t="str">
+      <x:c r="G28" s="344" t="str">
         <x:f>IF($A28="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A28="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H28" s="292" t="str">
+      <x:c r="H28" s="344" t="str">
         <x:f>IF($A28="Verdadero o Falso Simple","",IF($A28="Respuesta A/B/Ambas/Ninguna","",IF($A28="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I28" s="292"/>
-      <x:c r="J28" s="292" t="n">
+      <x:c r="I28" s="344"/>
+      <x:c r="J28" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K28" s="292" t="str">
+      <x:c r="K28" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L28" s="293"/>
-      <x:c r="M28" s="289"/>
+      <x:c r="L28" s="345" t="str">
+        <x:f>IF(TRIM($A28)="","",IF(COUNTIF($Q28:$AJ28,"?*")=0,"OK","Falta revisar: "&amp;$Q28&amp;$R28&amp;$S28&amp;$T28&amp;$U28&amp;$V28&amp;$W28&amp;$X28&amp;$Y28&amp;$Z28&amp;$AA28&amp;$AB28&amp;$AC28&amp;$AD28&amp;$AE28&amp;$AF28&amp;$AG28&amp;$AH28&amp;$AI28&amp;$AJ28))</x:f>
+      </x:c>
+      <x:c r="M28" s="341"/>
       <x:c r="N28"/>
       <x:c r="O28"/>
       <x:c r="P28"/>
@@ -5299,33 +5543,35 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="292"/>
-      <x:c r="B29" s="292"/>
-      <x:c r="C29" s="292"/>
-      <x:c r="D29" s="292" t="str">
+      <x:c r="A29" s="344"/>
+      <x:c r="B29" s="344"/>
+      <x:c r="C29" s="344"/>
+      <x:c r="D29" s="344" t="str">
         <x:f>IF($A29="Verdadero o Falso Simple","Verdadero",IF($A29="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A29="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E29" s="292" t="str">
+      <x:c r="E29" s="344" t="str">
         <x:f>IF($A29="Verdadero o Falso Simple","Falso",IF($A29="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A29="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F29" s="292" t="str">
+      <x:c r="F29" s="344" t="str">
         <x:f>IF($A29="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A29="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G29" s="292" t="str">
+      <x:c r="G29" s="344" t="str">
         <x:f>IF($A29="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A29="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H29" s="292" t="str">
+      <x:c r="H29" s="344" t="str">
         <x:f>IF($A29="Verdadero o Falso Simple","",IF($A29="Respuesta A/B/Ambas/Ninguna","",IF($A29="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I29" s="292"/>
-      <x:c r="J29" s="292" t="n">
+      <x:c r="I29" s="344"/>
+      <x:c r="J29" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K29" s="292" t="str">
+      <x:c r="K29" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L29" s="293"/>
-      <x:c r="M29" s="289"/>
+      <x:c r="L29" s="345" t="str">
+        <x:f>IF(TRIM($A29)="","",IF(COUNTIF($Q29:$AJ29,"?*")=0,"OK","Falta revisar: "&amp;$Q29&amp;$R29&amp;$S29&amp;$T29&amp;$U29&amp;$V29&amp;$W29&amp;$X29&amp;$Y29&amp;$Z29&amp;$AA29&amp;$AB29&amp;$AC29&amp;$AD29&amp;$AE29&amp;$AF29&amp;$AG29&amp;$AH29&amp;$AI29&amp;$AJ29))</x:f>
+      </x:c>
+      <x:c r="M29" s="341"/>
       <x:c r="N29"/>
       <x:c r="O29"/>
       <x:c r="P29"/>
@@ -5404,33 +5650,35 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="292"/>
-      <x:c r="B30" s="292"/>
-      <x:c r="C30" s="292"/>
-      <x:c r="D30" s="292" t="str">
+      <x:c r="A30" s="344"/>
+      <x:c r="B30" s="344"/>
+      <x:c r="C30" s="344"/>
+      <x:c r="D30" s="344" t="str">
         <x:f>IF($A30="Verdadero o Falso Simple","Verdadero",IF($A30="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A30="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E30" s="292" t="str">
+      <x:c r="E30" s="344" t="str">
         <x:f>IF($A30="Verdadero o Falso Simple","Falso",IF($A30="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A30="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F30" s="292" t="str">
+      <x:c r="F30" s="344" t="str">
         <x:f>IF($A30="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A30="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G30" s="292" t="str">
+      <x:c r="G30" s="344" t="str">
         <x:f>IF($A30="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A30="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H30" s="292" t="str">
+      <x:c r="H30" s="344" t="str">
         <x:f>IF($A30="Verdadero o Falso Simple","",IF($A30="Respuesta A/B/Ambas/Ninguna","",IF($A30="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I30" s="292"/>
-      <x:c r="J30" s="292" t="n">
+      <x:c r="I30" s="344"/>
+      <x:c r="J30" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K30" s="292" t="str">
+      <x:c r="K30" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L30" s="293"/>
-      <x:c r="M30" s="289"/>
+      <x:c r="L30" s="345" t="str">
+        <x:f>IF(TRIM($A30)="","",IF(COUNTIF($Q30:$AJ30,"?*")=0,"OK","Falta revisar: "&amp;$Q30&amp;$R30&amp;$S30&amp;$T30&amp;$U30&amp;$V30&amp;$W30&amp;$X30&amp;$Y30&amp;$Z30&amp;$AA30&amp;$AB30&amp;$AC30&amp;$AD30&amp;$AE30&amp;$AF30&amp;$AG30&amp;$AH30&amp;$AI30&amp;$AJ30))</x:f>
+      </x:c>
+      <x:c r="M30" s="341"/>
       <x:c r="N30"/>
       <x:c r="O30"/>
       <x:c r="P30"/>
@@ -5509,33 +5757,35 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="292"/>
-      <x:c r="B31" s="292"/>
-      <x:c r="C31" s="292"/>
-      <x:c r="D31" s="292" t="str">
+      <x:c r="A31" s="344"/>
+      <x:c r="B31" s="344"/>
+      <x:c r="C31" s="344"/>
+      <x:c r="D31" s="344" t="str">
         <x:f>IF($A31="Verdadero o Falso Simple","Verdadero",IF($A31="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A31="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E31" s="292" t="str">
+      <x:c r="E31" s="344" t="str">
         <x:f>IF($A31="Verdadero o Falso Simple","Falso",IF($A31="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A31="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F31" s="292" t="str">
+      <x:c r="F31" s="344" t="str">
         <x:f>IF($A31="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A31="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G31" s="292" t="str">
+      <x:c r="G31" s="344" t="str">
         <x:f>IF($A31="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A31="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H31" s="292" t="str">
+      <x:c r="H31" s="344" t="str">
         <x:f>IF($A31="Verdadero o Falso Simple","",IF($A31="Respuesta A/B/Ambas/Ninguna","",IF($A31="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I31" s="292"/>
-      <x:c r="J31" s="292" t="n">
+      <x:c r="I31" s="344"/>
+      <x:c r="J31" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K31" s="292" t="str">
+      <x:c r="K31" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L31" s="293"/>
-      <x:c r="M31" s="289"/>
+      <x:c r="L31" s="345" t="str">
+        <x:f>IF(TRIM($A31)="","",IF(COUNTIF($Q31:$AJ31,"?*")=0,"OK","Falta revisar: "&amp;$Q31&amp;$R31&amp;$S31&amp;$T31&amp;$U31&amp;$V31&amp;$W31&amp;$X31&amp;$Y31&amp;$Z31&amp;$AA31&amp;$AB31&amp;$AC31&amp;$AD31&amp;$AE31&amp;$AF31&amp;$AG31&amp;$AH31&amp;$AI31&amp;$AJ31))</x:f>
+      </x:c>
+      <x:c r="M31" s="341"/>
       <x:c r="N31"/>
       <x:c r="O31"/>
       <x:c r="P31"/>
@@ -5614,33 +5864,35 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="292"/>
-      <x:c r="B32" s="292"/>
-      <x:c r="C32" s="292"/>
-      <x:c r="D32" s="292" t="str">
+      <x:c r="A32" s="344"/>
+      <x:c r="B32" s="344"/>
+      <x:c r="C32" s="344"/>
+      <x:c r="D32" s="344" t="str">
         <x:f>IF($A32="Verdadero o Falso Simple","Verdadero",IF($A32="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A32="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E32" s="292" t="str">
+      <x:c r="E32" s="344" t="str">
         <x:f>IF($A32="Verdadero o Falso Simple","Falso",IF($A32="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A32="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F32" s="292" t="str">
+      <x:c r="F32" s="344" t="str">
         <x:f>IF($A32="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A32="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G32" s="292" t="str">
+      <x:c r="G32" s="344" t="str">
         <x:f>IF($A32="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A32="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H32" s="292" t="str">
+      <x:c r="H32" s="344" t="str">
         <x:f>IF($A32="Verdadero o Falso Simple","",IF($A32="Respuesta A/B/Ambas/Ninguna","",IF($A32="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I32" s="292"/>
-      <x:c r="J32" s="292" t="n">
+      <x:c r="I32" s="344"/>
+      <x:c r="J32" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K32" s="292" t="str">
+      <x:c r="K32" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L32" s="293"/>
-      <x:c r="M32" s="289"/>
+      <x:c r="L32" s="345" t="str">
+        <x:f>IF(TRIM($A32)="","",IF(COUNTIF($Q32:$AJ32,"?*")=0,"OK","Falta revisar: "&amp;$Q32&amp;$R32&amp;$S32&amp;$T32&amp;$U32&amp;$V32&amp;$W32&amp;$X32&amp;$Y32&amp;$Z32&amp;$AA32&amp;$AB32&amp;$AC32&amp;$AD32&amp;$AE32&amp;$AF32&amp;$AG32&amp;$AH32&amp;$AI32&amp;$AJ32))</x:f>
+      </x:c>
+      <x:c r="M32" s="341"/>
       <x:c r="N32"/>
       <x:c r="O32"/>
       <x:c r="P32"/>
@@ -5719,33 +5971,35 @@
       </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
-      <x:c r="A33" s="292"/>
-      <x:c r="B33" s="292"/>
-      <x:c r="C33" s="292"/>
-      <x:c r="D33" s="292" t="str">
+      <x:c r="A33" s="344"/>
+      <x:c r="B33" s="344"/>
+      <x:c r="C33" s="344"/>
+      <x:c r="D33" s="344" t="str">
         <x:f>IF($A33="Verdadero o Falso Simple","Verdadero",IF($A33="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A33="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E33" s="292" t="str">
+      <x:c r="E33" s="344" t="str">
         <x:f>IF($A33="Verdadero o Falso Simple","Falso",IF($A33="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A33="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F33" s="292" t="str">
+      <x:c r="F33" s="344" t="str">
         <x:f>IF($A33="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A33="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G33" s="292" t="str">
+      <x:c r="G33" s="344" t="str">
         <x:f>IF($A33="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A33="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H33" s="292" t="str">
+      <x:c r="H33" s="344" t="str">
         <x:f>IF($A33="Verdadero o Falso Simple","",IF($A33="Respuesta A/B/Ambas/Ninguna","",IF($A33="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I33" s="292"/>
-      <x:c r="J33" s="292" t="n">
+      <x:c r="I33" s="344"/>
+      <x:c r="J33" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K33" s="292" t="str">
+      <x:c r="K33" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L33" s="293"/>
-      <x:c r="M33" s="289"/>
+      <x:c r="L33" s="345" t="str">
+        <x:f>IF(TRIM($A33)="","",IF(COUNTIF($Q33:$AJ33,"?*")=0,"OK","Falta revisar: "&amp;$Q33&amp;$R33&amp;$S33&amp;$T33&amp;$U33&amp;$V33&amp;$W33&amp;$X33&amp;$Y33&amp;$Z33&amp;$AA33&amp;$AB33&amp;$AC33&amp;$AD33&amp;$AE33&amp;$AF33&amp;$AG33&amp;$AH33&amp;$AI33&amp;$AJ33))</x:f>
+      </x:c>
+      <x:c r="M33" s="341"/>
       <x:c r="N33"/>
       <x:c r="O33"/>
       <x:c r="P33"/>
@@ -5824,33 +6078,35 @@
       </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="292"/>
-      <x:c r="B34" s="292"/>
-      <x:c r="C34" s="292"/>
-      <x:c r="D34" s="292" t="str">
+      <x:c r="A34" s="344"/>
+      <x:c r="B34" s="344"/>
+      <x:c r="C34" s="344"/>
+      <x:c r="D34" s="344" t="str">
         <x:f>IF($A34="Verdadero o Falso Simple","Verdadero",IF($A34="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A34="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E34" s="292" t="str">
+      <x:c r="E34" s="344" t="str">
         <x:f>IF($A34="Verdadero o Falso Simple","Falso",IF($A34="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A34="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F34" s="292" t="str">
+      <x:c r="F34" s="344" t="str">
         <x:f>IF($A34="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A34="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G34" s="292" t="str">
+      <x:c r="G34" s="344" t="str">
         <x:f>IF($A34="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A34="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H34" s="292" t="str">
+      <x:c r="H34" s="344" t="str">
         <x:f>IF($A34="Verdadero o Falso Simple","",IF($A34="Respuesta A/B/Ambas/Ninguna","",IF($A34="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I34" s="292"/>
-      <x:c r="J34" s="292" t="n">
+      <x:c r="I34" s="344"/>
+      <x:c r="J34" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K34" s="292" t="str">
+      <x:c r="K34" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L34" s="293"/>
-      <x:c r="M34" s="289"/>
+      <x:c r="L34" s="345" t="str">
+        <x:f>IF(TRIM($A34)="","",IF(COUNTIF($Q34:$AJ34,"?*")=0,"OK","Falta revisar: "&amp;$Q34&amp;$R34&amp;$S34&amp;$T34&amp;$U34&amp;$V34&amp;$W34&amp;$X34&amp;$Y34&amp;$Z34&amp;$AA34&amp;$AB34&amp;$AC34&amp;$AD34&amp;$AE34&amp;$AF34&amp;$AG34&amp;$AH34&amp;$AI34&amp;$AJ34))</x:f>
+      </x:c>
+      <x:c r="M34" s="341"/>
       <x:c r="N34"/>
       <x:c r="O34"/>
       <x:c r="P34"/>
@@ -5929,33 +6185,35 @@
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
-      <x:c r="A35" s="292"/>
-      <x:c r="B35" s="292"/>
-      <x:c r="C35" s="292"/>
-      <x:c r="D35" s="292" t="str">
+      <x:c r="A35" s="344"/>
+      <x:c r="B35" s="344"/>
+      <x:c r="C35" s="344"/>
+      <x:c r="D35" s="344" t="str">
         <x:f>IF($A35="Verdadero o Falso Simple","Verdadero",IF($A35="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A35="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E35" s="292" t="str">
+      <x:c r="E35" s="344" t="str">
         <x:f>IF($A35="Verdadero o Falso Simple","Falso",IF($A35="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A35="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F35" s="292" t="str">
+      <x:c r="F35" s="344" t="str">
         <x:f>IF($A35="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A35="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G35" s="292" t="str">
+      <x:c r="G35" s="344" t="str">
         <x:f>IF($A35="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A35="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H35" s="292" t="str">
+      <x:c r="H35" s="344" t="str">
         <x:f>IF($A35="Verdadero o Falso Simple","",IF($A35="Respuesta A/B/Ambas/Ninguna","",IF($A35="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I35" s="292"/>
-      <x:c r="J35" s="292" t="n">
+      <x:c r="I35" s="344"/>
+      <x:c r="J35" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K35" s="292" t="str">
+      <x:c r="K35" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L35" s="293"/>
-      <x:c r="M35" s="289"/>
+      <x:c r="L35" s="345" t="str">
+        <x:f>IF(TRIM($A35)="","",IF(COUNTIF($Q35:$AJ35,"?*")=0,"OK","Falta revisar: "&amp;$Q35&amp;$R35&amp;$S35&amp;$T35&amp;$U35&amp;$V35&amp;$W35&amp;$X35&amp;$Y35&amp;$Z35&amp;$AA35&amp;$AB35&amp;$AC35&amp;$AD35&amp;$AE35&amp;$AF35&amp;$AG35&amp;$AH35&amp;$AI35&amp;$AJ35))</x:f>
+      </x:c>
+      <x:c r="M35" s="341"/>
       <x:c r="N35"/>
       <x:c r="O35"/>
       <x:c r="P35"/>
@@ -6034,33 +6292,35 @@
       </x:c>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
-      <x:c r="A36" s="292"/>
-      <x:c r="B36" s="292"/>
-      <x:c r="C36" s="292"/>
-      <x:c r="D36" s="292" t="str">
+      <x:c r="A36" s="344"/>
+      <x:c r="B36" s="344"/>
+      <x:c r="C36" s="344"/>
+      <x:c r="D36" s="344" t="str">
         <x:f>IF($A36="Verdadero o Falso Simple","Verdadero",IF($A36="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A36="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E36" s="292" t="str">
+      <x:c r="E36" s="344" t="str">
         <x:f>IF($A36="Verdadero o Falso Simple","Falso",IF($A36="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A36="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F36" s="292" t="str">
+      <x:c r="F36" s="344" t="str">
         <x:f>IF($A36="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A36="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G36" s="292" t="str">
+      <x:c r="G36" s="344" t="str">
         <x:f>IF($A36="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A36="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H36" s="292" t="str">
+      <x:c r="H36" s="344" t="str">
         <x:f>IF($A36="Verdadero o Falso Simple","",IF($A36="Respuesta A/B/Ambas/Ninguna","",IF($A36="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I36" s="292"/>
-      <x:c r="J36" s="292" t="n">
+      <x:c r="I36" s="344"/>
+      <x:c r="J36" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K36" s="292" t="str">
+      <x:c r="K36" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L36" s="293"/>
-      <x:c r="M36" s="289"/>
+      <x:c r="L36" s="345" t="str">
+        <x:f>IF(TRIM($A36)="","",IF(COUNTIF($Q36:$AJ36,"?*")=0,"OK","Falta revisar: "&amp;$Q36&amp;$R36&amp;$S36&amp;$T36&amp;$U36&amp;$V36&amp;$W36&amp;$X36&amp;$Y36&amp;$Z36&amp;$AA36&amp;$AB36&amp;$AC36&amp;$AD36&amp;$AE36&amp;$AF36&amp;$AG36&amp;$AH36&amp;$AI36&amp;$AJ36))</x:f>
+      </x:c>
+      <x:c r="M36" s="341"/>
       <x:c r="N36"/>
       <x:c r="O36"/>
       <x:c r="P36"/>
@@ -6139,33 +6399,35 @@
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
-      <x:c r="A37" s="292"/>
-      <x:c r="B37" s="292"/>
-      <x:c r="C37" s="292"/>
-      <x:c r="D37" s="292" t="str">
+      <x:c r="A37" s="344"/>
+      <x:c r="B37" s="344"/>
+      <x:c r="C37" s="344"/>
+      <x:c r="D37" s="344" t="str">
         <x:f>IF($A37="Verdadero o Falso Simple","Verdadero",IF($A37="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A37="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E37" s="292" t="str">
+      <x:c r="E37" s="344" t="str">
         <x:f>IF($A37="Verdadero o Falso Simple","Falso",IF($A37="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A37="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F37" s="292" t="str">
+      <x:c r="F37" s="344" t="str">
         <x:f>IF($A37="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A37="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G37" s="292" t="str">
+      <x:c r="G37" s="344" t="str">
         <x:f>IF($A37="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A37="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H37" s="292" t="str">
+      <x:c r="H37" s="344" t="str">
         <x:f>IF($A37="Verdadero o Falso Simple","",IF($A37="Respuesta A/B/Ambas/Ninguna","",IF($A37="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I37" s="292"/>
-      <x:c r="J37" s="292" t="n">
+      <x:c r="I37" s="344"/>
+      <x:c r="J37" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K37" s="292" t="str">
+      <x:c r="K37" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L37" s="293"/>
-      <x:c r="M37" s="289"/>
+      <x:c r="L37" s="345" t="str">
+        <x:f>IF(TRIM($A37)="","",IF(COUNTIF($Q37:$AJ37,"?*")=0,"OK","Falta revisar: "&amp;$Q37&amp;$R37&amp;$S37&amp;$T37&amp;$U37&amp;$V37&amp;$W37&amp;$X37&amp;$Y37&amp;$Z37&amp;$AA37&amp;$AB37&amp;$AC37&amp;$AD37&amp;$AE37&amp;$AF37&amp;$AG37&amp;$AH37&amp;$AI37&amp;$AJ37))</x:f>
+      </x:c>
+      <x:c r="M37" s="341"/>
       <x:c r="N37"/>
       <x:c r="O37"/>
       <x:c r="P37"/>
@@ -6244,33 +6506,35 @@
       </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
-      <x:c r="A38" s="292"/>
-      <x:c r="B38" s="292"/>
-      <x:c r="C38" s="292"/>
-      <x:c r="D38" s="292" t="str">
+      <x:c r="A38" s="344"/>
+      <x:c r="B38" s="344"/>
+      <x:c r="C38" s="344"/>
+      <x:c r="D38" s="344" t="str">
         <x:f>IF($A38="Verdadero o Falso Simple","Verdadero",IF($A38="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A38="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E38" s="292" t="str">
+      <x:c r="E38" s="344" t="str">
         <x:f>IF($A38="Verdadero o Falso Simple","Falso",IF($A38="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A38="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F38" s="292" t="str">
+      <x:c r="F38" s="344" t="str">
         <x:f>IF($A38="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A38="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G38" s="292" t="str">
+      <x:c r="G38" s="344" t="str">
         <x:f>IF($A38="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A38="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H38" s="292" t="str">
+      <x:c r="H38" s="344" t="str">
         <x:f>IF($A38="Verdadero o Falso Simple","",IF($A38="Respuesta A/B/Ambas/Ninguna","",IF($A38="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I38" s="292"/>
-      <x:c r="J38" s="292" t="n">
+      <x:c r="I38" s="344"/>
+      <x:c r="J38" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K38" s="292" t="str">
+      <x:c r="K38" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L38" s="293"/>
-      <x:c r="M38" s="289"/>
+      <x:c r="L38" s="345" t="str">
+        <x:f>IF(TRIM($A38)="","",IF(COUNTIF($Q38:$AJ38,"?*")=0,"OK","Falta revisar: "&amp;$Q38&amp;$R38&amp;$S38&amp;$T38&amp;$U38&amp;$V38&amp;$W38&amp;$X38&amp;$Y38&amp;$Z38&amp;$AA38&amp;$AB38&amp;$AC38&amp;$AD38&amp;$AE38&amp;$AF38&amp;$AG38&amp;$AH38&amp;$AI38&amp;$AJ38))</x:f>
+      </x:c>
+      <x:c r="M38" s="341"/>
       <x:c r="N38"/>
       <x:c r="O38"/>
       <x:c r="P38"/>
@@ -6349,33 +6613,35 @@
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
-      <x:c r="A39" s="292"/>
-      <x:c r="B39" s="292"/>
-      <x:c r="C39" s="292"/>
-      <x:c r="D39" s="292" t="str">
+      <x:c r="A39" s="344"/>
+      <x:c r="B39" s="344"/>
+      <x:c r="C39" s="344"/>
+      <x:c r="D39" s="344" t="str">
         <x:f>IF($A39="Verdadero o Falso Simple","Verdadero",IF($A39="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A39="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E39" s="292" t="str">
+      <x:c r="E39" s="344" t="str">
         <x:f>IF($A39="Verdadero o Falso Simple","Falso",IF($A39="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A39="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F39" s="292" t="str">
+      <x:c r="F39" s="344" t="str">
         <x:f>IF($A39="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A39="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G39" s="292" t="str">
+      <x:c r="G39" s="344" t="str">
         <x:f>IF($A39="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A39="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H39" s="292" t="str">
+      <x:c r="H39" s="344" t="str">
         <x:f>IF($A39="Verdadero o Falso Simple","",IF($A39="Respuesta A/B/Ambas/Ninguna","",IF($A39="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I39" s="292"/>
-      <x:c r="J39" s="292" t="n">
+      <x:c r="I39" s="344"/>
+      <x:c r="J39" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K39" s="292" t="str">
+      <x:c r="K39" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L39" s="293"/>
-      <x:c r="M39" s="289"/>
+      <x:c r="L39" s="345" t="str">
+        <x:f>IF(TRIM($A39)="","",IF(COUNTIF($Q39:$AJ39,"?*")=0,"OK","Falta revisar: "&amp;$Q39&amp;$R39&amp;$S39&amp;$T39&amp;$U39&amp;$V39&amp;$W39&amp;$X39&amp;$Y39&amp;$Z39&amp;$AA39&amp;$AB39&amp;$AC39&amp;$AD39&amp;$AE39&amp;$AF39&amp;$AG39&amp;$AH39&amp;$AI39&amp;$AJ39))</x:f>
+      </x:c>
+      <x:c r="M39" s="341"/>
       <x:c r="N39"/>
       <x:c r="O39"/>
       <x:c r="P39"/>
@@ -6454,33 +6720,35 @@
       </x:c>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
-      <x:c r="A40" s="292"/>
-      <x:c r="B40" s="292"/>
-      <x:c r="C40" s="292"/>
-      <x:c r="D40" s="292" t="str">
+      <x:c r="A40" s="344"/>
+      <x:c r="B40" s="344"/>
+      <x:c r="C40" s="344"/>
+      <x:c r="D40" s="344" t="str">
         <x:f>IF($A40="Verdadero o Falso Simple","Verdadero",IF($A40="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A40="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E40" s="292" t="str">
+      <x:c r="E40" s="344" t="str">
         <x:f>IF($A40="Verdadero o Falso Simple","Falso",IF($A40="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A40="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F40" s="292" t="str">
+      <x:c r="F40" s="344" t="str">
         <x:f>IF($A40="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A40="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G40" s="292" t="str">
+      <x:c r="G40" s="344" t="str">
         <x:f>IF($A40="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A40="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H40" s="292" t="str">
+      <x:c r="H40" s="344" t="str">
         <x:f>IF($A40="Verdadero o Falso Simple","",IF($A40="Respuesta A/B/Ambas/Ninguna","",IF($A40="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I40" s="292"/>
-      <x:c r="J40" s="292" t="n">
+      <x:c r="I40" s="344"/>
+      <x:c r="J40" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K40" s="292" t="str">
+      <x:c r="K40" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L40" s="293"/>
-      <x:c r="M40" s="289"/>
+      <x:c r="L40" s="345" t="str">
+        <x:f>IF(TRIM($A40)="","",IF(COUNTIF($Q40:$AJ40,"?*")=0,"OK","Falta revisar: "&amp;$Q40&amp;$R40&amp;$S40&amp;$T40&amp;$U40&amp;$V40&amp;$W40&amp;$X40&amp;$Y40&amp;$Z40&amp;$AA40&amp;$AB40&amp;$AC40&amp;$AD40&amp;$AE40&amp;$AF40&amp;$AG40&amp;$AH40&amp;$AI40&amp;$AJ40))</x:f>
+      </x:c>
+      <x:c r="M40" s="341"/>
       <x:c r="N40"/>
       <x:c r="O40"/>
       <x:c r="P40"/>
@@ -6559,33 +6827,35 @@
       </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
-      <x:c r="A41" s="292"/>
-      <x:c r="B41" s="292"/>
-      <x:c r="C41" s="292"/>
-      <x:c r="D41" s="292" t="str">
+      <x:c r="A41" s="344"/>
+      <x:c r="B41" s="344"/>
+      <x:c r="C41" s="344"/>
+      <x:c r="D41" s="344" t="str">
         <x:f>IF($A41="Verdadero o Falso Simple","Verdadero",IF($A41="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A41="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E41" s="292" t="str">
+      <x:c r="E41" s="344" t="str">
         <x:f>IF($A41="Verdadero o Falso Simple","Falso",IF($A41="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A41="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F41" s="292" t="str">
+      <x:c r="F41" s="344" t="str">
         <x:f>IF($A41="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A41="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G41" s="292" t="str">
+      <x:c r="G41" s="344" t="str">
         <x:f>IF($A41="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A41="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H41" s="292" t="str">
+      <x:c r="H41" s="344" t="str">
         <x:f>IF($A41="Verdadero o Falso Simple","",IF($A41="Respuesta A/B/Ambas/Ninguna","",IF($A41="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I41" s="292"/>
-      <x:c r="J41" s="292" t="n">
+      <x:c r="I41" s="344"/>
+      <x:c r="J41" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K41" s="292" t="str">
+      <x:c r="K41" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L41" s="293"/>
-      <x:c r="M41" s="289"/>
+      <x:c r="L41" s="345" t="str">
+        <x:f>IF(TRIM($A41)="","",IF(COUNTIF($Q41:$AJ41,"?*")=0,"OK","Falta revisar: "&amp;$Q41&amp;$R41&amp;$S41&amp;$T41&amp;$U41&amp;$V41&amp;$W41&amp;$X41&amp;$Y41&amp;$Z41&amp;$AA41&amp;$AB41&amp;$AC41&amp;$AD41&amp;$AE41&amp;$AF41&amp;$AG41&amp;$AH41&amp;$AI41&amp;$AJ41))</x:f>
+      </x:c>
+      <x:c r="M41" s="341"/>
       <x:c r="N41"/>
       <x:c r="O41"/>
       <x:c r="P41"/>
@@ -6664,33 +6934,35 @@
       </x:c>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
-      <x:c r="A42" s="292"/>
-      <x:c r="B42" s="292"/>
-      <x:c r="C42" s="292"/>
-      <x:c r="D42" s="292" t="str">
+      <x:c r="A42" s="344"/>
+      <x:c r="B42" s="344"/>
+      <x:c r="C42" s="344"/>
+      <x:c r="D42" s="344" t="str">
         <x:f>IF($A42="Verdadero o Falso Simple","Verdadero",IF($A42="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A42="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E42" s="292" t="str">
+      <x:c r="E42" s="344" t="str">
         <x:f>IF($A42="Verdadero o Falso Simple","Falso",IF($A42="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A42="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F42" s="292" t="str">
+      <x:c r="F42" s="344" t="str">
         <x:f>IF($A42="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A42="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G42" s="292" t="str">
+      <x:c r="G42" s="344" t="str">
         <x:f>IF($A42="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A42="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H42" s="292" t="str">
+      <x:c r="H42" s="344" t="str">
         <x:f>IF($A42="Verdadero o Falso Simple","",IF($A42="Respuesta A/B/Ambas/Ninguna","",IF($A42="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I42" s="292"/>
-      <x:c r="J42" s="292" t="n">
+      <x:c r="I42" s="344"/>
+      <x:c r="J42" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K42" s="292" t="str">
+      <x:c r="K42" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L42" s="293"/>
-      <x:c r="M42" s="289"/>
+      <x:c r="L42" s="345" t="str">
+        <x:f>IF(TRIM($A42)="","",IF(COUNTIF($Q42:$AJ42,"?*")=0,"OK","Falta revisar: "&amp;$Q42&amp;$R42&amp;$S42&amp;$T42&amp;$U42&amp;$V42&amp;$W42&amp;$X42&amp;$Y42&amp;$Z42&amp;$AA42&amp;$AB42&amp;$AC42&amp;$AD42&amp;$AE42&amp;$AF42&amp;$AG42&amp;$AH42&amp;$AI42&amp;$AJ42))</x:f>
+      </x:c>
+      <x:c r="M42" s="341"/>
       <x:c r="N42"/>
       <x:c r="O42"/>
       <x:c r="P42"/>
@@ -6769,33 +7041,35 @@
       </x:c>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
-      <x:c r="A43" s="292"/>
-      <x:c r="B43" s="292"/>
-      <x:c r="C43" s="292"/>
-      <x:c r="D43" s="292" t="str">
+      <x:c r="A43" s="344"/>
+      <x:c r="B43" s="344"/>
+      <x:c r="C43" s="344"/>
+      <x:c r="D43" s="344" t="str">
         <x:f>IF($A43="Verdadero o Falso Simple","Verdadero",IF($A43="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A43="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E43" s="292" t="str">
+      <x:c r="E43" s="344" t="str">
         <x:f>IF($A43="Verdadero o Falso Simple","Falso",IF($A43="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A43="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F43" s="292" t="str">
+      <x:c r="F43" s="344" t="str">
         <x:f>IF($A43="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A43="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G43" s="292" t="str">
+      <x:c r="G43" s="344" t="str">
         <x:f>IF($A43="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A43="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H43" s="292" t="str">
+      <x:c r="H43" s="344" t="str">
         <x:f>IF($A43="Verdadero o Falso Simple","",IF($A43="Respuesta A/B/Ambas/Ninguna","",IF($A43="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I43" s="292"/>
-      <x:c r="J43" s="292" t="n">
+      <x:c r="I43" s="344"/>
+      <x:c r="J43" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K43" s="292" t="str">
+      <x:c r="K43" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L43" s="293"/>
-      <x:c r="M43" s="289"/>
+      <x:c r="L43" s="345" t="str">
+        <x:f>IF(TRIM($A43)="","",IF(COUNTIF($Q43:$AJ43,"?*")=0,"OK","Falta revisar: "&amp;$Q43&amp;$R43&amp;$S43&amp;$T43&amp;$U43&amp;$V43&amp;$W43&amp;$X43&amp;$Y43&amp;$Z43&amp;$AA43&amp;$AB43&amp;$AC43&amp;$AD43&amp;$AE43&amp;$AF43&amp;$AG43&amp;$AH43&amp;$AI43&amp;$AJ43))</x:f>
+      </x:c>
+      <x:c r="M43" s="341"/>
       <x:c r="N43"/>
       <x:c r="O43"/>
       <x:c r="P43"/>
@@ -6874,33 +7148,35 @@
       </x:c>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
-      <x:c r="A44" s="292"/>
-      <x:c r="B44" s="292"/>
-      <x:c r="C44" s="292"/>
-      <x:c r="D44" s="292" t="str">
+      <x:c r="A44" s="344"/>
+      <x:c r="B44" s="344"/>
+      <x:c r="C44" s="344"/>
+      <x:c r="D44" s="344" t="str">
         <x:f>IF($A44="Verdadero o Falso Simple","Verdadero",IF($A44="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A44="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E44" s="292" t="str">
+      <x:c r="E44" s="344" t="str">
         <x:f>IF($A44="Verdadero o Falso Simple","Falso",IF($A44="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A44="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F44" s="292" t="str">
+      <x:c r="F44" s="344" t="str">
         <x:f>IF($A44="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A44="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G44" s="292" t="str">
+      <x:c r="G44" s="344" t="str">
         <x:f>IF($A44="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A44="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H44" s="292" t="str">
+      <x:c r="H44" s="344" t="str">
         <x:f>IF($A44="Verdadero o Falso Simple","",IF($A44="Respuesta A/B/Ambas/Ninguna","",IF($A44="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I44" s="292"/>
-      <x:c r="J44" s="292" t="n">
+      <x:c r="I44" s="344"/>
+      <x:c r="J44" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K44" s="292" t="str">
+      <x:c r="K44" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L44" s="293"/>
-      <x:c r="M44" s="289"/>
+      <x:c r="L44" s="345" t="str">
+        <x:f>IF(TRIM($A44)="","",IF(COUNTIF($Q44:$AJ44,"?*")=0,"OK","Falta revisar: "&amp;$Q44&amp;$R44&amp;$S44&amp;$T44&amp;$U44&amp;$V44&amp;$W44&amp;$X44&amp;$Y44&amp;$Z44&amp;$AA44&amp;$AB44&amp;$AC44&amp;$AD44&amp;$AE44&amp;$AF44&amp;$AG44&amp;$AH44&amp;$AI44&amp;$AJ44))</x:f>
+      </x:c>
+      <x:c r="M44" s="341"/>
       <x:c r="N44"/>
       <x:c r="O44"/>
       <x:c r="P44"/>
@@ -6979,33 +7255,35 @@
       </x:c>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
-      <x:c r="A45" s="292"/>
-      <x:c r="B45" s="292"/>
-      <x:c r="C45" s="292"/>
-      <x:c r="D45" s="292" t="str">
+      <x:c r="A45" s="344"/>
+      <x:c r="B45" s="344"/>
+      <x:c r="C45" s="344"/>
+      <x:c r="D45" s="344" t="str">
         <x:f>IF($A45="Verdadero o Falso Simple","Verdadero",IF($A45="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A45="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E45" s="292" t="str">
+      <x:c r="E45" s="344" t="str">
         <x:f>IF($A45="Verdadero o Falso Simple","Falso",IF($A45="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A45="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F45" s="292" t="str">
+      <x:c r="F45" s="344" t="str">
         <x:f>IF($A45="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A45="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G45" s="292" t="str">
+      <x:c r="G45" s="344" t="str">
         <x:f>IF($A45="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A45="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H45" s="292" t="str">
+      <x:c r="H45" s="344" t="str">
         <x:f>IF($A45="Verdadero o Falso Simple","",IF($A45="Respuesta A/B/Ambas/Ninguna","",IF($A45="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I45" s="292"/>
-      <x:c r="J45" s="292" t="n">
+      <x:c r="I45" s="344"/>
+      <x:c r="J45" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K45" s="292" t="str">
+      <x:c r="K45" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L45" s="293"/>
-      <x:c r="M45" s="289"/>
+      <x:c r="L45" s="345" t="str">
+        <x:f>IF(TRIM($A45)="","",IF(COUNTIF($Q45:$AJ45,"?*")=0,"OK","Falta revisar: "&amp;$Q45&amp;$R45&amp;$S45&amp;$T45&amp;$U45&amp;$V45&amp;$W45&amp;$X45&amp;$Y45&amp;$Z45&amp;$AA45&amp;$AB45&amp;$AC45&amp;$AD45&amp;$AE45&amp;$AF45&amp;$AG45&amp;$AH45&amp;$AI45&amp;$AJ45))</x:f>
+      </x:c>
+      <x:c r="M45" s="341"/>
       <x:c r="N45"/>
       <x:c r="O45"/>
       <x:c r="P45"/>
@@ -7084,33 +7362,35 @@
       </x:c>
     </x:row>
     <x:row r="46" ht="24" customHeight="1">
-      <x:c r="A46" s="292"/>
-      <x:c r="B46" s="292"/>
-      <x:c r="C46" s="292"/>
-      <x:c r="D46" s="292" t="str">
+      <x:c r="A46" s="344"/>
+      <x:c r="B46" s="344"/>
+      <x:c r="C46" s="344"/>
+      <x:c r="D46" s="344" t="str">
         <x:f>IF($A46="Verdadero o Falso Simple","Verdadero",IF($A46="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A46="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E46" s="292" t="str">
+      <x:c r="E46" s="344" t="str">
         <x:f>IF($A46="Verdadero o Falso Simple","Falso",IF($A46="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A46="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F46" s="292" t="str">
+      <x:c r="F46" s="344" t="str">
         <x:f>IF($A46="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A46="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G46" s="292" t="str">
+      <x:c r="G46" s="344" t="str">
         <x:f>IF($A46="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A46="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H46" s="292" t="str">
+      <x:c r="H46" s="344" t="str">
         <x:f>IF($A46="Verdadero o Falso Simple","",IF($A46="Respuesta A/B/Ambas/Ninguna","",IF($A46="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I46" s="292"/>
-      <x:c r="J46" s="292" t="n">
+      <x:c r="I46" s="344"/>
+      <x:c r="J46" s="344" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K46" s="292" t="str">
+      <x:c r="K46" s="344" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L46" s="293"/>
-      <x:c r="M46" s="289"/>
+      <x:c r="L46" s="345" t="str">
+        <x:f>IF(TRIM($A46)="","",IF(COUNTIF($Q46:$AJ46,"?*")=0,"OK","Falta revisar: "&amp;$Q46&amp;$R46&amp;$S46&amp;$T46&amp;$U46&amp;$V46&amp;$W46&amp;$X46&amp;$Y46&amp;$Z46&amp;$AA46&amp;$AB46&amp;$AC46&amp;$AD46&amp;$AE46&amp;$AF46&amp;$AG46&amp;$AH46&amp;$AI46&amp;$AJ46))</x:f>
+      </x:c>
+      <x:c r="M46" s="341"/>
       <x:c r="N46"/>
       <x:c r="O46"/>
       <x:c r="P46"/>
@@ -7189,33 +7469,35 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
-      <x:c r="A47" s="294"/>
-      <x:c r="B47" s="294"/>
-      <x:c r="C47" s="294"/>
-      <x:c r="D47" s="294" t="str">
+      <x:c r="A47" s="346"/>
+      <x:c r="B47" s="346"/>
+      <x:c r="C47" s="346"/>
+      <x:c r="D47" s="346" t="str">
         <x:f>IF($A47="Verdadero o Falso Simple","Verdadero",IF($A47="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A47="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E47" s="294" t="str">
+      <x:c r="E47" s="346" t="str">
         <x:f>IF($A47="Verdadero o Falso Simple","Falso",IF($A47="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A47="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F47" s="294" t="str">
+      <x:c r="F47" s="346" t="str">
         <x:f>IF($A47="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A47="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G47" s="294" t="str">
+      <x:c r="G47" s="346" t="str">
         <x:f>IF($A47="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A47="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H47" s="294" t="str">
+      <x:c r="H47" s="346" t="str">
         <x:f>IF($A47="Verdadero o Falso Simple","",IF($A47="Respuesta A/B/Ambas/Ninguna","",IF($A47="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I47" s="294"/>
-      <x:c r="J47" s="294" t="n">
+      <x:c r="I47" s="346"/>
+      <x:c r="J47" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K47" s="294" t="str">
+      <x:c r="K47" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L47" s="295"/>
-      <x:c r="M47" s="289"/>
+      <x:c r="L47" s="347" t="str">
+        <x:f>IF(TRIM($A47)="","",IF(COUNTIF($Q47:$AJ47,"?*")=0,"OK","Falta revisar: "&amp;$Q47&amp;$R47&amp;$S47&amp;$T47&amp;$U47&amp;$V47&amp;$W47&amp;$X47&amp;$Y47&amp;$Z47&amp;$AA47&amp;$AB47&amp;$AC47&amp;$AD47&amp;$AE47&amp;$AF47&amp;$AG47&amp;$AH47&amp;$AI47&amp;$AJ47))</x:f>
+      </x:c>
+      <x:c r="M47" s="341"/>
       <x:c r="N47"/>
       <x:c r="O47"/>
       <x:c r="P47"/>
@@ -7294,33 +7576,35 @@
       </x:c>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
-      <x:c r="A48" s="294"/>
-      <x:c r="B48" s="294"/>
-      <x:c r="C48" s="294"/>
-      <x:c r="D48" s="294" t="str">
+      <x:c r="A48" s="346"/>
+      <x:c r="B48" s="346"/>
+      <x:c r="C48" s="346"/>
+      <x:c r="D48" s="346" t="str">
         <x:f>IF($A48="Verdadero o Falso Simple","Verdadero",IF($A48="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A48="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E48" s="294" t="str">
+      <x:c r="E48" s="346" t="str">
         <x:f>IF($A48="Verdadero o Falso Simple","Falso",IF($A48="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A48="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F48" s="294" t="str">
+      <x:c r="F48" s="346" t="str">
         <x:f>IF($A48="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A48="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G48" s="294" t="str">
+      <x:c r="G48" s="346" t="str">
         <x:f>IF($A48="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A48="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H48" s="294" t="str">
+      <x:c r="H48" s="346" t="str">
         <x:f>IF($A48="Verdadero o Falso Simple","",IF($A48="Respuesta A/B/Ambas/Ninguna","",IF($A48="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I48" s="294"/>
-      <x:c r="J48" s="294" t="n">
+      <x:c r="I48" s="346"/>
+      <x:c r="J48" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K48" s="294" t="str">
+      <x:c r="K48" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L48" s="295"/>
-      <x:c r="M48" s="289"/>
+      <x:c r="L48" s="347" t="str">
+        <x:f>IF(TRIM($A48)="","",IF(COUNTIF($Q48:$AJ48,"?*")=0,"OK","Falta revisar: "&amp;$Q48&amp;$R48&amp;$S48&amp;$T48&amp;$U48&amp;$V48&amp;$W48&amp;$X48&amp;$Y48&amp;$Z48&amp;$AA48&amp;$AB48&amp;$AC48&amp;$AD48&amp;$AE48&amp;$AF48&amp;$AG48&amp;$AH48&amp;$AI48&amp;$AJ48))</x:f>
+      </x:c>
+      <x:c r="M48" s="341"/>
       <x:c r="N48"/>
       <x:c r="O48"/>
       <x:c r="P48"/>
@@ -7399,33 +7683,35 @@
       </x:c>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
-      <x:c r="A49" s="294"/>
-      <x:c r="B49" s="294"/>
-      <x:c r="C49" s="294"/>
-      <x:c r="D49" s="294" t="str">
+      <x:c r="A49" s="346"/>
+      <x:c r="B49" s="346"/>
+      <x:c r="C49" s="346"/>
+      <x:c r="D49" s="346" t="str">
         <x:f>IF($A49="Verdadero o Falso Simple","Verdadero",IF($A49="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A49="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E49" s="294" t="str">
+      <x:c r="E49" s="346" t="str">
         <x:f>IF($A49="Verdadero o Falso Simple","Falso",IF($A49="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A49="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F49" s="294" t="str">
+      <x:c r="F49" s="346" t="str">
         <x:f>IF($A49="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A49="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G49" s="294" t="str">
+      <x:c r="G49" s="346" t="str">
         <x:f>IF($A49="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A49="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H49" s="294" t="str">
+      <x:c r="H49" s="346" t="str">
         <x:f>IF($A49="Verdadero o Falso Simple","",IF($A49="Respuesta A/B/Ambas/Ninguna","",IF($A49="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I49" s="294"/>
-      <x:c r="J49" s="294" t="n">
+      <x:c r="I49" s="346"/>
+      <x:c r="J49" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K49" s="294" t="str">
+      <x:c r="K49" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L49" s="295"/>
-      <x:c r="M49" s="289"/>
+      <x:c r="L49" s="347" t="str">
+        <x:f>IF(TRIM($A49)="","",IF(COUNTIF($Q49:$AJ49,"?*")=0,"OK","Falta revisar: "&amp;$Q49&amp;$R49&amp;$S49&amp;$T49&amp;$U49&amp;$V49&amp;$W49&amp;$X49&amp;$Y49&amp;$Z49&amp;$AA49&amp;$AB49&amp;$AC49&amp;$AD49&amp;$AE49&amp;$AF49&amp;$AG49&amp;$AH49&amp;$AI49&amp;$AJ49))</x:f>
+      </x:c>
+      <x:c r="M49" s="341"/>
       <x:c r="N49"/>
       <x:c r="O49"/>
       <x:c r="P49"/>
@@ -7504,33 +7790,35 @@
       </x:c>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
-      <x:c r="A50" s="294"/>
-      <x:c r="B50" s="294"/>
-      <x:c r="C50" s="294"/>
-      <x:c r="D50" s="294" t="str">
+      <x:c r="A50" s="346"/>
+      <x:c r="B50" s="346"/>
+      <x:c r="C50" s="346"/>
+      <x:c r="D50" s="346" t="str">
         <x:f>IF($A50="Verdadero o Falso Simple","Verdadero",IF($A50="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A50="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E50" s="294" t="str">
+      <x:c r="E50" s="346" t="str">
         <x:f>IF($A50="Verdadero o Falso Simple","Falso",IF($A50="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A50="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F50" s="294" t="str">
+      <x:c r="F50" s="346" t="str">
         <x:f>IF($A50="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A50="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G50" s="294" t="str">
+      <x:c r="G50" s="346" t="str">
         <x:f>IF($A50="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A50="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H50" s="294" t="str">
+      <x:c r="H50" s="346" t="str">
         <x:f>IF($A50="Verdadero o Falso Simple","",IF($A50="Respuesta A/B/Ambas/Ninguna","",IF($A50="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I50" s="294"/>
-      <x:c r="J50" s="294" t="n">
+      <x:c r="I50" s="346"/>
+      <x:c r="J50" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K50" s="294" t="str">
+      <x:c r="K50" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L50" s="295"/>
-      <x:c r="M50" s="289"/>
+      <x:c r="L50" s="347" t="str">
+        <x:f>IF(TRIM($A50)="","",IF(COUNTIF($Q50:$AJ50,"?*")=0,"OK","Falta revisar: "&amp;$Q50&amp;$R50&amp;$S50&amp;$T50&amp;$U50&amp;$V50&amp;$W50&amp;$X50&amp;$Y50&amp;$Z50&amp;$AA50&amp;$AB50&amp;$AC50&amp;$AD50&amp;$AE50&amp;$AF50&amp;$AG50&amp;$AH50&amp;$AI50&amp;$AJ50))</x:f>
+      </x:c>
+      <x:c r="M50" s="341"/>
       <x:c r="N50"/>
       <x:c r="O50"/>
       <x:c r="P50"/>
@@ -7609,33 +7897,35 @@
       </x:c>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
-      <x:c r="A51" s="294"/>
-      <x:c r="B51" s="294"/>
-      <x:c r="C51" s="294"/>
-      <x:c r="D51" s="294" t="str">
+      <x:c r="A51" s="346"/>
+      <x:c r="B51" s="346"/>
+      <x:c r="C51" s="346"/>
+      <x:c r="D51" s="346" t="str">
         <x:f>IF($A51="Verdadero o Falso Simple","Verdadero",IF($A51="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A51="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E51" s="294" t="str">
+      <x:c r="E51" s="346" t="str">
         <x:f>IF($A51="Verdadero o Falso Simple","Falso",IF($A51="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A51="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F51" s="294" t="str">
+      <x:c r="F51" s="346" t="str">
         <x:f>IF($A51="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A51="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G51" s="294" t="str">
+      <x:c r="G51" s="346" t="str">
         <x:f>IF($A51="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A51="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H51" s="294" t="str">
+      <x:c r="H51" s="346" t="str">
         <x:f>IF($A51="Verdadero o Falso Simple","",IF($A51="Respuesta A/B/Ambas/Ninguna","",IF($A51="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I51" s="294"/>
-      <x:c r="J51" s="294" t="n">
+      <x:c r="I51" s="346"/>
+      <x:c r="J51" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K51" s="294" t="str">
+      <x:c r="K51" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L51" s="295"/>
-      <x:c r="M51" s="289"/>
+      <x:c r="L51" s="347" t="str">
+        <x:f>IF(TRIM($A51)="","",IF(COUNTIF($Q51:$AJ51,"?*")=0,"OK","Falta revisar: "&amp;$Q51&amp;$R51&amp;$S51&amp;$T51&amp;$U51&amp;$V51&amp;$W51&amp;$X51&amp;$Y51&amp;$Z51&amp;$AA51&amp;$AB51&amp;$AC51&amp;$AD51&amp;$AE51&amp;$AF51&amp;$AG51&amp;$AH51&amp;$AI51&amp;$AJ51))</x:f>
+      </x:c>
+      <x:c r="M51" s="341"/>
       <x:c r="N51"/>
       <x:c r="O51"/>
       <x:c r="P51"/>
@@ -7714,33 +8004,35 @@
       </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
-      <x:c r="A52" s="294"/>
-      <x:c r="B52" s="294"/>
-      <x:c r="C52" s="294"/>
-      <x:c r="D52" s="294" t="str">
+      <x:c r="A52" s="346"/>
+      <x:c r="B52" s="346"/>
+      <x:c r="C52" s="346"/>
+      <x:c r="D52" s="346" t="str">
         <x:f>IF($A52="Verdadero o Falso Simple","Verdadero",IF($A52="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A52="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E52" s="294" t="str">
+      <x:c r="E52" s="346" t="str">
         <x:f>IF($A52="Verdadero o Falso Simple","Falso",IF($A52="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A52="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F52" s="294" t="str">
+      <x:c r="F52" s="346" t="str">
         <x:f>IF($A52="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A52="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G52" s="294" t="str">
+      <x:c r="G52" s="346" t="str">
         <x:f>IF($A52="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A52="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H52" s="294" t="str">
+      <x:c r="H52" s="346" t="str">
         <x:f>IF($A52="Verdadero o Falso Simple","",IF($A52="Respuesta A/B/Ambas/Ninguna","",IF($A52="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I52" s="294"/>
-      <x:c r="J52" s="294" t="n">
+      <x:c r="I52" s="346"/>
+      <x:c r="J52" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K52" s="294" t="str">
+      <x:c r="K52" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L52" s="295"/>
-      <x:c r="M52" s="289"/>
+      <x:c r="L52" s="347" t="str">
+        <x:f>IF(TRIM($A52)="","",IF(COUNTIF($Q52:$AJ52,"?*")=0,"OK","Falta revisar: "&amp;$Q52&amp;$R52&amp;$S52&amp;$T52&amp;$U52&amp;$V52&amp;$W52&amp;$X52&amp;$Y52&amp;$Z52&amp;$AA52&amp;$AB52&amp;$AC52&amp;$AD52&amp;$AE52&amp;$AF52&amp;$AG52&amp;$AH52&amp;$AI52&amp;$AJ52))</x:f>
+      </x:c>
+      <x:c r="M52" s="341"/>
       <x:c r="N52"/>
       <x:c r="O52"/>
       <x:c r="P52"/>
@@ -7819,33 +8111,35 @@
       </x:c>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
-      <x:c r="A53" s="294"/>
-      <x:c r="B53" s="294"/>
-      <x:c r="C53" s="294"/>
-      <x:c r="D53" s="294" t="str">
+      <x:c r="A53" s="346"/>
+      <x:c r="B53" s="346"/>
+      <x:c r="C53" s="346"/>
+      <x:c r="D53" s="346" t="str">
         <x:f>IF($A53="Verdadero o Falso Simple","Verdadero",IF($A53="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A53="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E53" s="294" t="str">
+      <x:c r="E53" s="346" t="str">
         <x:f>IF($A53="Verdadero o Falso Simple","Falso",IF($A53="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A53="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F53" s="294" t="str">
+      <x:c r="F53" s="346" t="str">
         <x:f>IF($A53="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A53="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G53" s="294" t="str">
+      <x:c r="G53" s="346" t="str">
         <x:f>IF($A53="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A53="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H53" s="294" t="str">
+      <x:c r="H53" s="346" t="str">
         <x:f>IF($A53="Verdadero o Falso Simple","",IF($A53="Respuesta A/B/Ambas/Ninguna","",IF($A53="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I53" s="294"/>
-      <x:c r="J53" s="294" t="n">
+      <x:c r="I53" s="346"/>
+      <x:c r="J53" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K53" s="294" t="str">
+      <x:c r="K53" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L53" s="295"/>
-      <x:c r="M53" s="289"/>
+      <x:c r="L53" s="347" t="str">
+        <x:f>IF(TRIM($A53)="","",IF(COUNTIF($Q53:$AJ53,"?*")=0,"OK","Falta revisar: "&amp;$Q53&amp;$R53&amp;$S53&amp;$T53&amp;$U53&amp;$V53&amp;$W53&amp;$X53&amp;$Y53&amp;$Z53&amp;$AA53&amp;$AB53&amp;$AC53&amp;$AD53&amp;$AE53&amp;$AF53&amp;$AG53&amp;$AH53&amp;$AI53&amp;$AJ53))</x:f>
+      </x:c>
+      <x:c r="M53" s="341"/>
       <x:c r="N53"/>
       <x:c r="O53"/>
       <x:c r="P53"/>
@@ -7924,33 +8218,35 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
-      <x:c r="A54" s="294"/>
-      <x:c r="B54" s="294"/>
-      <x:c r="C54" s="294"/>
-      <x:c r="D54" s="294" t="str">
+      <x:c r="A54" s="346"/>
+      <x:c r="B54" s="346"/>
+      <x:c r="C54" s="346"/>
+      <x:c r="D54" s="346" t="str">
         <x:f>IF($A54="Verdadero o Falso Simple","Verdadero",IF($A54="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A54="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E54" s="294" t="str">
+      <x:c r="E54" s="346" t="str">
         <x:f>IF($A54="Verdadero o Falso Simple","Falso",IF($A54="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A54="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F54" s="294" t="str">
+      <x:c r="F54" s="346" t="str">
         <x:f>IF($A54="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A54="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G54" s="294" t="str">
+      <x:c r="G54" s="346" t="str">
         <x:f>IF($A54="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A54="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H54" s="294" t="str">
+      <x:c r="H54" s="346" t="str">
         <x:f>IF($A54="Verdadero o Falso Simple","",IF($A54="Respuesta A/B/Ambas/Ninguna","",IF($A54="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I54" s="294"/>
-      <x:c r="J54" s="294" t="n">
+      <x:c r="I54" s="346"/>
+      <x:c r="J54" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K54" s="294" t="str">
+      <x:c r="K54" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L54" s="295"/>
-      <x:c r="M54" s="289"/>
+      <x:c r="L54" s="347" t="str">
+        <x:f>IF(TRIM($A54)="","",IF(COUNTIF($Q54:$AJ54,"?*")=0,"OK","Falta revisar: "&amp;$Q54&amp;$R54&amp;$S54&amp;$T54&amp;$U54&amp;$V54&amp;$W54&amp;$X54&amp;$Y54&amp;$Z54&amp;$AA54&amp;$AB54&amp;$AC54&amp;$AD54&amp;$AE54&amp;$AF54&amp;$AG54&amp;$AH54&amp;$AI54&amp;$AJ54))</x:f>
+      </x:c>
+      <x:c r="M54" s="341"/>
       <x:c r="N54"/>
       <x:c r="O54"/>
       <x:c r="P54"/>
@@ -8029,33 +8325,35 @@
       </x:c>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
-      <x:c r="A55" s="294"/>
-      <x:c r="B55" s="294"/>
-      <x:c r="C55" s="294"/>
-      <x:c r="D55" s="294" t="str">
+      <x:c r="A55" s="346"/>
+      <x:c r="B55" s="346"/>
+      <x:c r="C55" s="346"/>
+      <x:c r="D55" s="346" t="str">
         <x:f>IF($A55="Verdadero o Falso Simple","Verdadero",IF($A55="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A55="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E55" s="294" t="str">
+      <x:c r="E55" s="346" t="str">
         <x:f>IF($A55="Verdadero o Falso Simple","Falso",IF($A55="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A55="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F55" s="294" t="str">
+      <x:c r="F55" s="346" t="str">
         <x:f>IF($A55="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A55="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G55" s="294" t="str">
+      <x:c r="G55" s="346" t="str">
         <x:f>IF($A55="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A55="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H55" s="294" t="str">
+      <x:c r="H55" s="346" t="str">
         <x:f>IF($A55="Verdadero o Falso Simple","",IF($A55="Respuesta A/B/Ambas/Ninguna","",IF($A55="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I55" s="294"/>
-      <x:c r="J55" s="294" t="n">
+      <x:c r="I55" s="346"/>
+      <x:c r="J55" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K55" s="294" t="str">
+      <x:c r="K55" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L55" s="295"/>
-      <x:c r="M55" s="289"/>
+      <x:c r="L55" s="347" t="str">
+        <x:f>IF(TRIM($A55)="","",IF(COUNTIF($Q55:$AJ55,"?*")=0,"OK","Falta revisar: "&amp;$Q55&amp;$R55&amp;$S55&amp;$T55&amp;$U55&amp;$V55&amp;$W55&amp;$X55&amp;$Y55&amp;$Z55&amp;$AA55&amp;$AB55&amp;$AC55&amp;$AD55&amp;$AE55&amp;$AF55&amp;$AG55&amp;$AH55&amp;$AI55&amp;$AJ55))</x:f>
+      </x:c>
+      <x:c r="M55" s="341"/>
       <x:c r="N55"/>
       <x:c r="O55"/>
       <x:c r="P55"/>
@@ -8134,33 +8432,35 @@
       </x:c>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
-      <x:c r="A56" s="294"/>
-      <x:c r="B56" s="294"/>
-      <x:c r="C56" s="294"/>
-      <x:c r="D56" s="294" t="str">
+      <x:c r="A56" s="346"/>
+      <x:c r="B56" s="346"/>
+      <x:c r="C56" s="346"/>
+      <x:c r="D56" s="346" t="str">
         <x:f>IF($A56="Verdadero o Falso Simple","Verdadero",IF($A56="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A56="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E56" s="294" t="str">
+      <x:c r="E56" s="346" t="str">
         <x:f>IF($A56="Verdadero o Falso Simple","Falso",IF($A56="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A56="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F56" s="294" t="str">
+      <x:c r="F56" s="346" t="str">
         <x:f>IF($A56="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A56="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G56" s="294" t="str">
+      <x:c r="G56" s="346" t="str">
         <x:f>IF($A56="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A56="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H56" s="294" t="str">
+      <x:c r="H56" s="346" t="str">
         <x:f>IF($A56="Verdadero o Falso Simple","",IF($A56="Respuesta A/B/Ambas/Ninguna","",IF($A56="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I56" s="294"/>
-      <x:c r="J56" s="294" t="n">
+      <x:c r="I56" s="346"/>
+      <x:c r="J56" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K56" s="294" t="str">
+      <x:c r="K56" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L56" s="295"/>
-      <x:c r="M56" s="289"/>
+      <x:c r="L56" s="347" t="str">
+        <x:f>IF(TRIM($A56)="","",IF(COUNTIF($Q56:$AJ56,"?*")=0,"OK","Falta revisar: "&amp;$Q56&amp;$R56&amp;$S56&amp;$T56&amp;$U56&amp;$V56&amp;$W56&amp;$X56&amp;$Y56&amp;$Z56&amp;$AA56&amp;$AB56&amp;$AC56&amp;$AD56&amp;$AE56&amp;$AF56&amp;$AG56&amp;$AH56&amp;$AI56&amp;$AJ56))</x:f>
+      </x:c>
+      <x:c r="M56" s="341"/>
       <x:c r="N56"/>
       <x:c r="O56"/>
       <x:c r="P56"/>
@@ -8239,33 +8539,35 @@
       </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
-      <x:c r="A57" s="294"/>
-      <x:c r="B57" s="294"/>
-      <x:c r="C57" s="294"/>
-      <x:c r="D57" s="294" t="str">
+      <x:c r="A57" s="346"/>
+      <x:c r="B57" s="346"/>
+      <x:c r="C57" s="346"/>
+      <x:c r="D57" s="346" t="str">
         <x:f>IF($A57="Verdadero o Falso Simple","Verdadero",IF($A57="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A57="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E57" s="294" t="str">
+      <x:c r="E57" s="346" t="str">
         <x:f>IF($A57="Verdadero o Falso Simple","Falso",IF($A57="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A57="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F57" s="294" t="str">
+      <x:c r="F57" s="346" t="str">
         <x:f>IF($A57="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A57="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G57" s="294" t="str">
+      <x:c r="G57" s="346" t="str">
         <x:f>IF($A57="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A57="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H57" s="294" t="str">
+      <x:c r="H57" s="346" t="str">
         <x:f>IF($A57="Verdadero o Falso Simple","",IF($A57="Respuesta A/B/Ambas/Ninguna","",IF($A57="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I57" s="294"/>
-      <x:c r="J57" s="294" t="n">
+      <x:c r="I57" s="346"/>
+      <x:c r="J57" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K57" s="294" t="str">
+      <x:c r="K57" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L57" s="295"/>
-      <x:c r="M57" s="289"/>
+      <x:c r="L57" s="347" t="str">
+        <x:f>IF(TRIM($A57)="","",IF(COUNTIF($Q57:$AJ57,"?*")=0,"OK","Falta revisar: "&amp;$Q57&amp;$R57&amp;$S57&amp;$T57&amp;$U57&amp;$V57&amp;$W57&amp;$X57&amp;$Y57&amp;$Z57&amp;$AA57&amp;$AB57&amp;$AC57&amp;$AD57&amp;$AE57&amp;$AF57&amp;$AG57&amp;$AH57&amp;$AI57&amp;$AJ57))</x:f>
+      </x:c>
+      <x:c r="M57" s="341"/>
       <x:c r="N57"/>
       <x:c r="O57"/>
       <x:c r="P57"/>
@@ -8344,33 +8646,35 @@
       </x:c>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="294"/>
-      <x:c r="B58" s="294"/>
-      <x:c r="C58" s="294"/>
-      <x:c r="D58" s="294" t="str">
+      <x:c r="A58" s="346"/>
+      <x:c r="B58" s="346"/>
+      <x:c r="C58" s="346"/>
+      <x:c r="D58" s="346" t="str">
         <x:f>IF($A58="Verdadero o Falso Simple","Verdadero",IF($A58="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A58="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E58" s="294" t="str">
+      <x:c r="E58" s="346" t="str">
         <x:f>IF($A58="Verdadero o Falso Simple","Falso",IF($A58="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A58="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F58" s="294" t="str">
+      <x:c r="F58" s="346" t="str">
         <x:f>IF($A58="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A58="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G58" s="294" t="str">
+      <x:c r="G58" s="346" t="str">
         <x:f>IF($A58="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A58="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H58" s="294" t="str">
+      <x:c r="H58" s="346" t="str">
         <x:f>IF($A58="Verdadero o Falso Simple","",IF($A58="Respuesta A/B/Ambas/Ninguna","",IF($A58="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I58" s="294"/>
-      <x:c r="J58" s="294" t="n">
+      <x:c r="I58" s="346"/>
+      <x:c r="J58" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K58" s="294" t="str">
+      <x:c r="K58" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L58" s="295"/>
-      <x:c r="M58" s="289"/>
+      <x:c r="L58" s="347" t="str">
+        <x:f>IF(TRIM($A58)="","",IF(COUNTIF($Q58:$AJ58,"?*")=0,"OK","Falta revisar: "&amp;$Q58&amp;$R58&amp;$S58&amp;$T58&amp;$U58&amp;$V58&amp;$W58&amp;$X58&amp;$Y58&amp;$Z58&amp;$AA58&amp;$AB58&amp;$AC58&amp;$AD58&amp;$AE58&amp;$AF58&amp;$AG58&amp;$AH58&amp;$AI58&amp;$AJ58))</x:f>
+      </x:c>
+      <x:c r="M58" s="341"/>
       <x:c r="N58"/>
       <x:c r="O58"/>
       <x:c r="P58"/>
@@ -8449,33 +8753,35 @@
       </x:c>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
-      <x:c r="A59" s="294"/>
-      <x:c r="B59" s="294"/>
-      <x:c r="C59" s="294"/>
-      <x:c r="D59" s="294" t="str">
+      <x:c r="A59" s="346"/>
+      <x:c r="B59" s="346"/>
+      <x:c r="C59" s="346"/>
+      <x:c r="D59" s="346" t="str">
         <x:f>IF($A59="Verdadero o Falso Simple","Verdadero",IF($A59="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A59="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E59" s="294" t="str">
+      <x:c r="E59" s="346" t="str">
         <x:f>IF($A59="Verdadero o Falso Simple","Falso",IF($A59="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A59="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F59" s="294" t="str">
+      <x:c r="F59" s="346" t="str">
         <x:f>IF($A59="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A59="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G59" s="294" t="str">
+      <x:c r="G59" s="346" t="str">
         <x:f>IF($A59="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A59="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H59" s="294" t="str">
+      <x:c r="H59" s="346" t="str">
         <x:f>IF($A59="Verdadero o Falso Simple","",IF($A59="Respuesta A/B/Ambas/Ninguna","",IF($A59="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I59" s="294"/>
-      <x:c r="J59" s="294" t="n">
+      <x:c r="I59" s="346"/>
+      <x:c r="J59" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K59" s="294" t="str">
+      <x:c r="K59" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L59" s="295"/>
-      <x:c r="M59" s="289"/>
+      <x:c r="L59" s="347" t="str">
+        <x:f>IF(TRIM($A59)="","",IF(COUNTIF($Q59:$AJ59,"?*")=0,"OK","Falta revisar: "&amp;$Q59&amp;$R59&amp;$S59&amp;$T59&amp;$U59&amp;$V59&amp;$W59&amp;$X59&amp;$Y59&amp;$Z59&amp;$AA59&amp;$AB59&amp;$AC59&amp;$AD59&amp;$AE59&amp;$AF59&amp;$AG59&amp;$AH59&amp;$AI59&amp;$AJ59))</x:f>
+      </x:c>
+      <x:c r="M59" s="341"/>
       <x:c r="N59"/>
       <x:c r="O59"/>
       <x:c r="P59"/>
@@ -8554,33 +8860,35 @@
       </x:c>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="294"/>
-      <x:c r="B60" s="294"/>
-      <x:c r="C60" s="294"/>
-      <x:c r="D60" s="294" t="str">
+      <x:c r="A60" s="346"/>
+      <x:c r="B60" s="346"/>
+      <x:c r="C60" s="346"/>
+      <x:c r="D60" s="346" t="str">
         <x:f>IF($A60="Verdadero o Falso Simple","Verdadero",IF($A60="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A60="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E60" s="294" t="str">
+      <x:c r="E60" s="346" t="str">
         <x:f>IF($A60="Verdadero o Falso Simple","Falso",IF($A60="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A60="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F60" s="294" t="str">
+      <x:c r="F60" s="346" t="str">
         <x:f>IF($A60="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A60="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G60" s="294" t="str">
+      <x:c r="G60" s="346" t="str">
         <x:f>IF($A60="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A60="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H60" s="294" t="str">
+      <x:c r="H60" s="346" t="str">
         <x:f>IF($A60="Verdadero o Falso Simple","",IF($A60="Respuesta A/B/Ambas/Ninguna","",IF($A60="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I60" s="294"/>
-      <x:c r="J60" s="294" t="n">
+      <x:c r="I60" s="346"/>
+      <x:c r="J60" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K60" s="294" t="str">
+      <x:c r="K60" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L60" s="295"/>
-      <x:c r="M60" s="289"/>
+      <x:c r="L60" s="347" t="str">
+        <x:f>IF(TRIM($A60)="","",IF(COUNTIF($Q60:$AJ60,"?*")=0,"OK","Falta revisar: "&amp;$Q60&amp;$R60&amp;$S60&amp;$T60&amp;$U60&amp;$V60&amp;$W60&amp;$X60&amp;$Y60&amp;$Z60&amp;$AA60&amp;$AB60&amp;$AC60&amp;$AD60&amp;$AE60&amp;$AF60&amp;$AG60&amp;$AH60&amp;$AI60&amp;$AJ60))</x:f>
+      </x:c>
+      <x:c r="M60" s="341"/>
       <x:c r="N60"/>
       <x:c r="O60"/>
       <x:c r="P60"/>
@@ -8659,33 +8967,35 @@
       </x:c>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
-      <x:c r="A61" s="294"/>
-      <x:c r="B61" s="294"/>
-      <x:c r="C61" s="294"/>
-      <x:c r="D61" s="294" t="str">
+      <x:c r="A61" s="346"/>
+      <x:c r="B61" s="346"/>
+      <x:c r="C61" s="346"/>
+      <x:c r="D61" s="346" t="str">
         <x:f>IF($A61="Verdadero o Falso Simple","Verdadero",IF($A61="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A61="Verdadero o Falso Complejas","1. ","")))</x:f>
       </x:c>
-      <x:c r="E61" s="294" t="str">
+      <x:c r="E61" s="346" t="str">
         <x:f>IF($A61="Verdadero o Falso Simple","Falso",IF($A61="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A61="Verdadero o Falso Complejas","2. ","")))</x:f>
       </x:c>
-      <x:c r="F61" s="294" t="str">
+      <x:c r="F61" s="346" t="str">
         <x:f>IF($A61="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A61="Verdadero o Falso Complejas","3. ",""))</x:f>
       </x:c>
-      <x:c r="G61" s="294" t="str">
+      <x:c r="G61" s="346" t="str">
         <x:f>IF($A61="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A61="Verdadero o Falso Complejas","4. ",""))</x:f>
       </x:c>
-      <x:c r="H61" s="294" t="str">
+      <x:c r="H61" s="346" t="str">
         <x:f>IF($A61="Verdadero o Falso Simple","",IF($A61="Respuesta A/B/Ambas/Ninguna","",IF($A61="Verdadero o Falso Complejas","","")))</x:f>
       </x:c>
-      <x:c r="I61" s="294"/>
-      <x:c r="J61" s="294" t="n">
+      <x:c r="I61" s="346"/>
+      <x:c r="J61" s="346" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K61" s="294" t="str">
+      <x:c r="K61" s="346" t="str">
         <x:v>1P</x:v>
       </x:c>
-      <x:c r="L61" s="295"/>
-      <x:c r="M61" s="289"/>
+      <x:c r="L61" s="347" t="str">
+        <x:f>IF(TRIM($A61)="","",IF(COUNTIF($Q61:$AJ61,"?*")=0,"OK","Falta revisar: "&amp;$Q61&amp;$R61&amp;$S61&amp;$T61&amp;$U61&amp;$V61&amp;$W61&amp;$X61&amp;$Y61&amp;$Z61&amp;$AA61&amp;$AB61&amp;$AC61&amp;$AD61&amp;$AE61&amp;$AF61&amp;$AG61&amp;$AH61&amp;$AI61&amp;$AJ61))</x:f>
+      </x:c>
+      <x:c r="M61" s="341"/>
       <x:c r="N61"/>
       <x:c r="O61"/>
       <x:c r="P61"/>
@@ -13319,7 +13629,7 @@
     <x:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." sqref="J9">
       <x:formula1>INDIRECT(IF(ISNUMBER(MATCH($A9,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tipo de pregunta" prompt="Seleccione un tipo. Las columnas de incisos se completan automÃ¡ticamente segÃºn la tipologÃ­a." errorTitle="Tipo no vÃ¡lido" error="Seleccione un tipo desde la lista del formato oficial." sqref="A2:A61">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tipo de pregunta" prompt="Seleccione un tipo. Las columnas de incisos se completan automáticamente según la tipología." errorTitle="Tipo no válido" error="Seleccione un tipo desde la lista del formato oficial." sqref="A2:A61">
       <x:formula1>LISTA_TIPOS_2P</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
